--- a/research/traditional_assets/database/data/cambodia/cambodia_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/cambodia/cambodia_hotel_gaming.xlsx
@@ -644,10 +644,10 @@
         <v>0.04860355458832064</v>
       </c>
       <c r="X2">
-        <v>0.1582217910264148</v>
+        <v>0.1582293023892101</v>
       </c>
       <c r="Y2">
-        <v>-0.1096182364380941</v>
+        <v>-0.1096257478008895</v>
       </c>
       <c r="Z2">
         <v>0.2388921466913257</v>
@@ -656,10 +656,10 @@
         <v>0.07217625148400633</v>
       </c>
       <c r="AB2">
-        <v>0.1439491701096149</v>
+        <v>0.143954696162162</v>
       </c>
       <c r="AC2">
-        <v>-0.07177291862560856</v>
+        <v>-0.07177844467815567</v>
       </c>
       <c r="AD2">
         <v>595.3</v>
@@ -775,10 +775,10 @@
         <v>0.04860355458832064</v>
       </c>
       <c r="X3">
-        <v>0.1582217910264148</v>
+        <v>0.1582293023892101</v>
       </c>
       <c r="Y3">
-        <v>-0.1096182364380941</v>
+        <v>-0.1096257478008895</v>
       </c>
       <c r="Z3">
         <v>0.2388921466913257</v>
@@ -787,10 +787,10 @@
         <v>0.07217625148400633</v>
       </c>
       <c r="AB3">
-        <v>0.1439491701096149</v>
+        <v>0.143954696162162</v>
       </c>
       <c r="AC3">
-        <v>-0.07177291862560856</v>
+        <v>-0.07177844467815567</v>
       </c>
       <c r="AD3">
         <v>595.3</v>
@@ -1145,13 +1145,13 @@
         <v>1657</v>
       </c>
       <c r="L2">
-        <v>2521.62947599345</v>
+        <v>2521.60380930022</v>
       </c>
       <c r="M2">
         <v>2172.6</v>
       </c>
       <c r="N2">
-        <v>2441.92947599345</v>
+        <v>2441.90380930022</v>
       </c>
       <c r="O2">
         <v>595.3</v>
@@ -1160,16 +1160,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.143949170109615</v>
+        <v>0.143954696162162</v>
       </c>
       <c r="R2">
-        <v>0.133123933420885</v>
+        <v>0.133129767892465</v>
       </c>
       <c r="S2">
         <v>0.104221750557897</v>
       </c>
       <c r="T2">
-        <v>0.08494175055789741</v>
+        <v>0.0838217505578974</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.158221791026415</v>
+        <v>0.15822930238921</v>
       </c>
       <c r="X2">
-        <v>0.133123933420885</v>
+        <v>0.133129767892465</v>
       </c>
       <c r="Y2">
         <v>0.9630450888248639</v>
@@ -1224,7 +1224,7 @@
         <v>1657</v>
       </c>
       <c r="AK2">
-        <v>0.1167357503100869</v>
+        <v>0.1167435499062663</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1331239334208852</v>
+        <v>0.1331297678924646</v>
       </c>
       <c r="C2">
-        <v>2521.629475993451</v>
+        <v>2521.603809300218</v>
       </c>
       <c r="D2">
-        <v>2441.929475993451</v>
+        <v>2441.903809300219</v>
       </c>
       <c r="E2">
         <v>-595.3</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1331239334208852</v>
+        <v>0.1331297678924646</v>
       </c>
       <c r="T2">
         <v>0.7480479046815168</v>
       </c>
       <c r="U2">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.08494175055789736</v>
+        <v>0.08382175055789737</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1333407030596225</v>
+        <v>0.1333353258622586</v>
       </c>
       <c r="C3">
-        <v>2493.059732572024</v>
+        <v>2493.346521062554</v>
       </c>
       <c r="D3">
-        <v>2435.882732572024</v>
+        <v>2436.169521062554</v>
       </c>
       <c r="E3">
         <v>-572.7769999999999</v>
@@ -1527,37 +1527,37 @@
         <v>160.4</v>
       </c>
       <c r="M3">
-        <v>2.391428809769403</v>
+        <v>2.359896609769403</v>
       </c>
       <c r="N3">
-        <v>158.0085711902306</v>
+        <v>158.0401033902306</v>
       </c>
       <c r="O3">
-        <v>31.60171423804612</v>
+        <v>31.60802067804612</v>
       </c>
       <c r="P3">
-        <v>126.4068569521845</v>
+        <v>126.4320827121845</v>
       </c>
       <c r="Q3">
-        <v>214.3068569521845</v>
+        <v>214.3320827121845</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1338295813677207</v>
+        <v>0.1338354629865451</v>
       </c>
       <c r="T3">
         <v>0.7540927362344988</v>
       </c>
       <c r="U3">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.08494175055789736</v>
+        <v>0.08382175055789737</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>67.07287264615115</v>
+        <v>67.9690793808435</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1335574726983597</v>
+        <v>0.1335408838320527</v>
       </c>
       <c r="C4">
-        <v>2464.519861259416</v>
+        <v>2465.116101226411</v>
       </c>
       <c r="D4">
-        <v>2429.865861259416</v>
+        <v>2430.462101226411</v>
       </c>
       <c r="E4">
         <v>-550.2539999999999</v>
@@ -1609,37 +1609,37 @@
         <v>160.4</v>
       </c>
       <c r="M4">
-        <v>4.782857619538806</v>
+        <v>4.719793219538806</v>
       </c>
       <c r="N4">
-        <v>155.6171423804612</v>
+        <v>155.6802067804612</v>
       </c>
       <c r="O4">
-        <v>31.12342847609224</v>
+        <v>31.13604135609224</v>
       </c>
       <c r="P4">
-        <v>124.4937139043689</v>
+        <v>124.544165424369</v>
       </c>
       <c r="Q4">
-        <v>212.393713904369</v>
+        <v>212.444165424369</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.134549630293063</v>
+        <v>0.1345555600213212</v>
       </c>
       <c r="T4">
         <v>0.7602609316967253</v>
       </c>
       <c r="U4">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.08494175055789736</v>
+        <v>0.08382175055789737</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.53643632307558</v>
+        <v>33.98453969042175</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1337742423370968</v>
+        <v>0.1337464418018467</v>
       </c>
       <c r="C5">
-        <v>2436.00964123987</v>
+        <v>2436.912361392558</v>
       </c>
       <c r="D5">
-        <v>2423.87864123987</v>
+        <v>2424.781361392558</v>
       </c>
       <c r="E5">
         <v>-527.731</v>
@@ -1691,37 +1691,37 @@
         <v>160.4</v>
       </c>
       <c r="M5">
-        <v>7.174286429308208</v>
+        <v>7.079689829308208</v>
       </c>
       <c r="N5">
-        <v>153.2257135706918</v>
+        <v>153.3203101706918</v>
       </c>
       <c r="O5">
-        <v>30.64514271413836</v>
+        <v>30.66406203413836</v>
       </c>
       <c r="P5">
-        <v>122.5805708565534</v>
+        <v>122.6562481365534</v>
       </c>
       <c r="Q5">
-        <v>210.4805708565534</v>
+        <v>210.5562481365534</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1352845255879999</v>
+        <v>0.135290504417639</v>
       </c>
       <c r="T5">
         <v>0.7665563064468326</v>
       </c>
       <c r="U5">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.08494175055789736</v>
+        <v>0.08382175055789737</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.35762421538372</v>
+        <v>22.65635979361451</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1339910119758341</v>
+        <v>0.1339519997716408</v>
       </c>
       <c r="C6">
-        <v>2407.528853868653</v>
+        <v>2408.735114919039</v>
       </c>
       <c r="D6">
-        <v>2417.920853868653</v>
+        <v>2419.127114919039</v>
       </c>
       <c r="E6">
         <v>-505.208</v>
@@ -1773,37 +1773,37 @@
         <v>160.4</v>
       </c>
       <c r="M6">
-        <v>9.565715239077612</v>
+        <v>9.439586439077612</v>
       </c>
       <c r="N6">
-        <v>150.8342847609224</v>
+        <v>150.9604135609224</v>
       </c>
       <c r="O6">
-        <v>30.16685695218448</v>
+        <v>30.19208271218448</v>
       </c>
       <c r="P6">
-        <v>120.6674278087379</v>
+        <v>120.7683308487379</v>
       </c>
       <c r="Q6">
-        <v>208.5674278087379</v>
+        <v>208.6683308487379</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1360347312015814</v>
+        <v>0.1360407601555468</v>
       </c>
       <c r="T6">
         <v>0.7729828348375675</v>
       </c>
       <c r="U6">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.08494175055789736</v>
+        <v>0.08382175055789737</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.76821816153779</v>
+        <v>16.99226984521088</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1342077816145713</v>
+        <v>0.1341575577414348</v>
       </c>
       <c r="C7">
-        <v>2379.07728264544</v>
+        <v>2380.584176900748</v>
       </c>
       <c r="D7">
-        <v>2411.992282645441</v>
+        <v>2413.499176900748</v>
       </c>
       <c r="E7">
         <v>-482.6849999999999</v>
@@ -1855,37 +1855,37 @@
         <v>160.4</v>
       </c>
       <c r="M7">
-        <v>11.95714404884701</v>
+        <v>11.79948304884701</v>
       </c>
       <c r="N7">
-        <v>148.442855951153</v>
+        <v>148.600516951153</v>
       </c>
       <c r="O7">
-        <v>29.6885711902306</v>
+        <v>29.7201033902306</v>
       </c>
       <c r="P7">
-        <v>118.7542847609224</v>
+        <v>118.8804135609224</v>
       </c>
       <c r="Q7">
-        <v>206.6542847609224</v>
+        <v>206.7804135609224</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1368007306175541</v>
+        <v>0.1368068107510947</v>
       </c>
       <c r="T7">
         <v>0.7795446585628438</v>
       </c>
       <c r="U7">
-        <v>0.1061771881973717</v>
+        <v>0.1047771881973717</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.08494175055789736</v>
+        <v>0.08382175055789737</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>13.41457452923023</v>
+        <v>13.5938158761687</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1344773512533085</v>
+        <v>0.1344351157112288</v>
       </c>
       <c r="C8">
-        <v>2349.222084749584</v>
+        <v>2350.503383059505</v>
       </c>
       <c r="D8">
-        <v>2404.660084749584</v>
+        <v>2405.941383059505</v>
       </c>
       <c r="E8">
         <v>-460.1619999999999</v>
@@ -1937,37 +1937,37 @@
         <v>160.4</v>
       </c>
       <c r="M8">
-        <v>14.49722465861642</v>
+        <v>14.36208665861642</v>
       </c>
       <c r="N8">
-        <v>145.9027753413836</v>
+        <v>146.0379133413836</v>
       </c>
       <c r="O8">
-        <v>29.18055506827672</v>
+        <v>29.20758266827672</v>
       </c>
       <c r="P8">
-        <v>116.7222202731069</v>
+        <v>116.8303306731069</v>
       </c>
       <c r="Q8">
-        <v>204.6222202731068</v>
+        <v>204.7303306731069</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1375830278934411</v>
+        <v>0.1375891602954841</v>
       </c>
       <c r="T8">
         <v>0.7862460955588709</v>
       </c>
       <c r="U8">
-        <v>0.1072771881973717</v>
+        <v>0.1062771881973717</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.08582175055789737</v>
+        <v>0.08502175055789736</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.06418668242589</v>
+        <v>11.16829356434563</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1348261208920457</v>
+        <v>0.1347478736810229</v>
       </c>
       <c r="C9">
-        <v>2317.278563888511</v>
+        <v>2319.520626673337</v>
       </c>
       <c r="D9">
-        <v>2395.239563888511</v>
+        <v>2397.481626673337</v>
       </c>
       <c r="E9">
         <v>-437.6389999999999</v>
@@ -2019,37 +2019,37 @@
         <v>160.4</v>
       </c>
       <c r="M9">
-        <v>17.26028296838582</v>
+        <v>17.02379146838582</v>
       </c>
       <c r="N9">
-        <v>143.1397170316142</v>
+        <v>143.3762085316142</v>
       </c>
       <c r="O9">
-        <v>28.62794340632284</v>
+        <v>28.67524170632284</v>
       </c>
       <c r="P9">
-        <v>114.5117736252913</v>
+        <v>114.7009668252914</v>
       </c>
       <c r="Q9">
-        <v>202.4117736252913</v>
+        <v>202.6009668252914</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.138382148766659</v>
+        <v>0.1383883345612582</v>
       </c>
       <c r="T9">
         <v>0.7930916494795437</v>
       </c>
       <c r="U9">
-        <v>0.1094771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.08758175055789737</v>
+        <v>0.08638175055789736</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.293011029644815</v>
+        <v>9.422107895169665</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1350692905307829</v>
+        <v>0.134979031650817</v>
       </c>
       <c r="C10">
-        <v>2288.230928865909</v>
+        <v>2290.783195150796</v>
       </c>
       <c r="D10">
-        <v>2388.71492886591</v>
+        <v>2391.267195150797</v>
       </c>
       <c r="E10">
         <v>-415.1159999999999</v>
@@ -2101,37 +2101,37 @@
         <v>160.4</v>
       </c>
       <c r="M10">
-        <v>19.72603767815523</v>
+        <v>19.45576167815522</v>
       </c>
       <c r="N10">
-        <v>140.6739623218448</v>
+        <v>140.9442383218448</v>
       </c>
       <c r="O10">
-        <v>28.13479246436896</v>
+        <v>28.18884766436896</v>
       </c>
       <c r="P10">
-        <v>112.5391698574758</v>
+        <v>112.7553906574758</v>
       </c>
       <c r="Q10">
-        <v>200.4391698574758</v>
+        <v>200.6553906574758</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1391986418327729</v>
+        <v>0.139204882180636</v>
       </c>
       <c r="T10">
         <v>0.8000860197897963</v>
       </c>
       <c r="U10">
-        <v>0.1094771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.08758175055789737</v>
+        <v>0.08638175055789736</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.131384650939214</v>
+        <v>8.244344408273456</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1354204601695201</v>
+        <v>0.135267789620611</v>
       </c>
       <c r="C11">
-        <v>2256.347966229819</v>
+        <v>2260.542362135866</v>
       </c>
       <c r="D11">
-        <v>2379.354966229819</v>
+        <v>2383.549362135866</v>
       </c>
       <c r="E11">
         <v>-392.593</v>
@@ -2183,37 +2183,37 @@
         <v>160.4</v>
       </c>
       <c r="M11">
-        <v>22.49585288792462</v>
+        <v>22.04989748792463</v>
       </c>
       <c r="N11">
-        <v>137.9041471120754</v>
+        <v>138.3501025120754</v>
       </c>
       <c r="O11">
-        <v>27.58082942241508</v>
+        <v>27.67002050241508</v>
       </c>
       <c r="P11">
-        <v>110.3233176896603</v>
+        <v>110.6800820096603</v>
       </c>
       <c r="Q11">
-        <v>198.2233176896603</v>
+        <v>198.5800820096603</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1400330798014388</v>
+        <v>0.1400393759015387</v>
       </c>
       <c r="T11">
         <v>0.80723411252445</v>
       </c>
       <c r="U11">
-        <v>0.1109771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.08878175055789735</v>
+        <v>0.08702175055789736</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.130203100061162</v>
+        <v>7.274410236502969</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1356756298082573</v>
+        <v>0.135505347590405</v>
       </c>
       <c r="C12">
-        <v>2227.069640581969</v>
+        <v>2231.707239585956</v>
       </c>
       <c r="D12">
-        <v>2372.599640581969</v>
+        <v>2377.237239585957</v>
       </c>
       <c r="E12">
         <v>-370.0699999999999</v>
@@ -2265,37 +2265,37 @@
         <v>160.4</v>
       </c>
       <c r="M12">
-        <v>24.99539209769403</v>
+        <v>24.49988609769403</v>
       </c>
       <c r="N12">
-        <v>135.404607902306</v>
+        <v>135.900113902306</v>
       </c>
       <c r="O12">
-        <v>27.08092158046119</v>
+        <v>27.1800227804612</v>
       </c>
       <c r="P12">
-        <v>108.3236863218448</v>
+        <v>108.7200911218448</v>
       </c>
       <c r="Q12">
-        <v>196.2236863218448</v>
+        <v>196.6200911218448</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1408860608360751</v>
+        <v>0.1408924139273503</v>
       </c>
       <c r="T12">
         <v>0.8145410517643185</v>
       </c>
       <c r="U12">
-        <v>0.1109771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.08878175055789735</v>
+        <v>0.08702175055789736</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.417182790055046</v>
+        <v>6.546969212852672</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1360539994469945</v>
+        <v>0.1358309055601991</v>
       </c>
       <c r="C13">
-        <v>2194.600049025078</v>
+        <v>2200.587985614914</v>
       </c>
       <c r="D13">
-        <v>2362.653049025078</v>
+        <v>2368.640985614914</v>
       </c>
       <c r="E13">
         <v>-347.5469999999999</v>
@@ -2347,37 +2347,37 @@
         <v>160.4</v>
       </c>
       <c r="M13">
-        <v>27.84178550746343</v>
+        <v>27.19762770746343</v>
       </c>
       <c r="N13">
-        <v>132.5582144925366</v>
+        <v>133.2023722925366</v>
       </c>
       <c r="O13">
-        <v>26.51164289850731</v>
+        <v>26.64047445850732</v>
       </c>
       <c r="P13">
-        <v>106.0465715940292</v>
+        <v>106.5618978340293</v>
       </c>
       <c r="Q13">
-        <v>193.9465715940293</v>
+        <v>194.4618978340293</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1417582099838492</v>
+        <v>0.1417646213470004</v>
       </c>
       <c r="T13">
         <v>0.8220121918859814</v>
       </c>
       <c r="U13">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.08990175055789736</v>
+        <v>0.08782175055789737</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.761124765399915</v>
+        <v>5.897573190031713</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1363203690857317</v>
+        <v>0.1360764635299931</v>
       </c>
       <c r="C14">
-        <v>2165.124591302176</v>
+        <v>2171.622124997038</v>
       </c>
       <c r="D14">
-        <v>2355.700591302176</v>
+        <v>2362.198124997038</v>
       </c>
       <c r="E14">
         <v>-325.0239999999999</v>
@@ -2429,37 +2429,37 @@
         <v>160.4</v>
       </c>
       <c r="M14">
-        <v>30.37285691723283</v>
+        <v>29.67013931723283</v>
       </c>
       <c r="N14">
-        <v>130.0271430827672</v>
+        <v>130.7298606827672</v>
       </c>
       <c r="O14">
-        <v>26.00542861655343</v>
+        <v>26.14597213655344</v>
       </c>
       <c r="P14">
-        <v>104.0217144662137</v>
+        <v>104.5838885462137</v>
       </c>
       <c r="Q14">
-        <v>191.9217144662138</v>
+        <v>192.4838885462137</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1426501807031637</v>
+        <v>0.1426566516625516</v>
       </c>
       <c r="T14">
         <v>0.8296531306467733</v>
       </c>
       <c r="U14">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.08990175055789736</v>
+        <v>0.08782175055789737</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.281031034949923</v>
+        <v>5.406108757529069</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1365867387244689</v>
+        <v>0.1363220214997872</v>
       </c>
       <c r="C15">
-        <v>2135.689930807547</v>
+        <v>2142.691219316021</v>
       </c>
       <c r="D15">
-        <v>2348.788930807547</v>
+        <v>2355.790219316021</v>
       </c>
       <c r="E15">
         <v>-302.5009999999999</v>
@@ -2511,37 +2511,37 @@
         <v>160.4</v>
       </c>
       <c r="M15">
-        <v>32.90392832700224</v>
+        <v>32.14265092700224</v>
       </c>
       <c r="N15">
-        <v>127.4960716729978</v>
+        <v>128.2573490729978</v>
       </c>
       <c r="O15">
-        <v>25.49921433459956</v>
+        <v>25.65146981459955</v>
       </c>
       <c r="P15">
-        <v>101.9968573383982</v>
+        <v>102.6058792583982</v>
       </c>
       <c r="Q15">
-        <v>189.8968573383982</v>
+        <v>190.5058792583982</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1435626564964853</v>
+        <v>0.1435691884221385</v>
       </c>
       <c r="T15">
         <v>0.8374697231721808</v>
       </c>
       <c r="U15">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.08990175055789736</v>
+        <v>0.08782175055789737</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.874797878415312</v>
+        <v>4.990254237719141</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1368531083632061</v>
+        <v>0.1365675794695812</v>
       </c>
       <c r="C16">
-        <v>2106.29570949269</v>
+        <v>2113.794984875966</v>
       </c>
       <c r="D16">
-        <v>2341.91770949269</v>
+        <v>2349.416984875967</v>
       </c>
       <c r="E16">
         <v>-279.9779999999999</v>
@@ -2593,37 +2593,37 @@
         <v>160.4</v>
       </c>
       <c r="M16">
-        <v>35.43499973677164</v>
+        <v>34.61516253677165</v>
       </c>
       <c r="N16">
-        <v>124.9650002632284</v>
+        <v>125.7848374632284</v>
       </c>
       <c r="O16">
-        <v>24.99300005264567</v>
+        <v>25.15696749264567</v>
       </c>
       <c r="P16">
-        <v>99.97200021058269</v>
+        <v>100.6278699705827</v>
       </c>
       <c r="Q16">
-        <v>187.8720002105827</v>
+        <v>188.5278699705827</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1444963526570936</v>
+        <v>0.1445029469668321</v>
       </c>
       <c r="T16">
         <v>0.8454680969191097</v>
       </c>
       <c r="U16">
-        <v>0.1123771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.08990175055789736</v>
+        <v>0.08782175055789737</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.526598029957075</v>
+        <v>4.633807506453487</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1374314780019433</v>
+        <v>0.1371131374393753</v>
       </c>
       <c r="C17">
-        <v>2068.990735774414</v>
+        <v>2077.235196781597</v>
       </c>
       <c r="D17">
-        <v>2327.135735774415</v>
+        <v>2335.380196781597</v>
       </c>
       <c r="E17">
         <v>-257.4549999999999</v>
@@ -2675,37 +2675,37 @@
         <v>160.4</v>
       </c>
       <c r="M17">
-        <v>38.84446814654104</v>
+        <v>37.93228664654104</v>
       </c>
       <c r="N17">
-        <v>121.555531853459</v>
+        <v>122.467713353459</v>
       </c>
       <c r="O17">
-        <v>24.3111063706918</v>
+        <v>24.4935426706918</v>
       </c>
       <c r="P17">
-        <v>97.24442548276718</v>
+        <v>97.97417068276717</v>
       </c>
       <c r="Q17">
-        <v>185.1444254827672</v>
+        <v>185.8741706827672</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1454520181391279</v>
+        <v>0.1454586763008125</v>
       </c>
       <c r="T17">
         <v>0.853654667695378</v>
       </c>
       <c r="U17">
-        <v>0.1149771881973717</v>
+        <v>0.1122771881973717</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.09198175055789735</v>
+        <v>0.08982175055789737</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.129288098240652</v>
+        <v>4.228587680321837</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1380642476406805</v>
+        <v>0.1378266954091693</v>
       </c>
       <c r="C18">
-        <v>2030.507698420041</v>
+        <v>2036.604090818394</v>
       </c>
       <c r="D18">
-        <v>2311.175698420041</v>
+        <v>2317.272090818394</v>
       </c>
       <c r="E18">
         <v>-234.9319999999999</v>
@@ -2757,37 +2757,37 @@
         <v>160.4</v>
       </c>
       <c r="M18">
-        <v>42.40709295631045</v>
+        <v>41.72239375631045</v>
       </c>
       <c r="N18">
-        <v>117.9929070436896</v>
+        <v>118.6776062436896</v>
       </c>
       <c r="O18">
-        <v>23.59858140873791</v>
+        <v>23.73552124873791</v>
       </c>
       <c r="P18">
-        <v>94.39432563495164</v>
+        <v>94.94208499495164</v>
       </c>
       <c r="Q18">
-        <v>182.2943256349516</v>
+        <v>182.8420849949516</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1464304375612106</v>
+        <v>0.1464371610951258</v>
       </c>
       <c r="T18">
         <v>0.8620361568234621</v>
       </c>
       <c r="U18">
-        <v>0.1176771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.09414175055789736</v>
+        <v>0.09262175055789737</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.782386125010992</v>
+        <v>3.844458228759699</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1383730172794177</v>
+        <v>0.1381202533789633</v>
       </c>
       <c r="C19">
-        <v>2000.275963127278</v>
+        <v>2006.712678519429</v>
       </c>
       <c r="D19">
-        <v>2303.466963127278</v>
+        <v>2309.903678519429</v>
       </c>
       <c r="E19">
         <v>-212.4089999999999</v>
@@ -2839,37 +2839,37 @@
         <v>160.4</v>
       </c>
       <c r="M19">
-        <v>45.05753626607985</v>
+        <v>44.33004336607986</v>
       </c>
       <c r="N19">
-        <v>115.3424637339202</v>
+        <v>116.0699566339202</v>
       </c>
       <c r="O19">
-        <v>23.06849274678403</v>
+        <v>23.21399132678403</v>
       </c>
       <c r="P19">
-        <v>92.27397098713612</v>
+        <v>92.85596530713613</v>
       </c>
       <c r="Q19">
-        <v>180.1739709871361</v>
+        <v>180.7559653071361</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1474324333549098</v>
+        <v>0.1474392238362901</v>
       </c>
       <c r="T19">
         <v>0.8706196095449943</v>
       </c>
       <c r="U19">
-        <v>0.1176771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.09414175055789736</v>
+        <v>0.09262175055789737</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.559892823539757</v>
+        <v>3.618313627067952</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1393585869181549</v>
+        <v>0.1388170113487574</v>
       </c>
       <c r="C20">
-        <v>1953.487663944442</v>
+        <v>1966.886996202207</v>
       </c>
       <c r="D20">
-        <v>2279.201663944442</v>
+        <v>2292.600996202207</v>
       </c>
       <c r="E20">
         <v>-189.8859999999999</v>
@@ -2921,37 +2921,37 @@
         <v>160.4</v>
       </c>
       <c r="M20">
-        <v>49.61342537584925</v>
+        <v>48.07285217584926</v>
       </c>
       <c r="N20">
-        <v>110.7865746241507</v>
+        <v>112.3271478241508</v>
       </c>
       <c r="O20">
-        <v>22.15731492483015</v>
+        <v>22.46542956483015</v>
       </c>
       <c r="P20">
-        <v>88.6292596993206</v>
+        <v>89.86171825932061</v>
       </c>
       <c r="Q20">
-        <v>176.5292596993206</v>
+        <v>177.7617182593206</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1484588680704066</v>
+        <v>0.1484657271321169</v>
       </c>
       <c r="T20">
         <v>0.8794124147719294</v>
       </c>
       <c r="U20">
-        <v>0.1223771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.09790175055789736</v>
+        <v>0.09486175055789736</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.232995883369893</v>
+        <v>3.336602525959162</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1397049565568921</v>
+        <v>0.1391329693185515</v>
       </c>
       <c r="C21">
-        <v>1922.557799324133</v>
+        <v>1936.602906400857</v>
       </c>
       <c r="D21">
-        <v>2270.794799324133</v>
+        <v>2284.839906400857</v>
       </c>
       <c r="E21">
         <v>-167.3629999999999</v>
@@ -3003,37 +3003,37 @@
         <v>160.4</v>
       </c>
       <c r="M21">
-        <v>52.36972678561865</v>
+        <v>50.74356618561865</v>
       </c>
       <c r="N21">
-        <v>108.0302732143814</v>
+        <v>109.6564338143814</v>
       </c>
       <c r="O21">
-        <v>21.60605464287627</v>
+        <v>21.93128676287627</v>
       </c>
       <c r="P21">
-        <v>86.42421857150508</v>
+        <v>87.72514705150509</v>
       </c>
       <c r="Q21">
-        <v>174.3242185715051</v>
+        <v>175.6251470515051</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1495106468529526</v>
+        <v>0.1495175761883345</v>
       </c>
       <c r="T21">
         <v>0.8884223263007646</v>
       </c>
       <c r="U21">
-        <v>0.1223771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.09790175055789736</v>
+        <v>0.09486175055789736</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.062838205297793</v>
+        <v>3.160991866698153</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1415393261956293</v>
+        <v>0.1394489272883455</v>
       </c>
       <c r="C22">
-        <v>1856.526272565015</v>
+        <v>1906.371186194079</v>
       </c>
       <c r="D22">
-        <v>2227.286272565016</v>
+        <v>2277.131186194079</v>
       </c>
       <c r="E22">
         <v>-144.8399999999999</v>
@@ -3085,45 +3085,45 @@
         <v>160.4</v>
       </c>
       <c r="M22">
-        <v>59.31530619538806</v>
+        <v>53.41428019538806</v>
       </c>
       <c r="N22">
-        <v>101.0846938046119</v>
+        <v>106.9857198046119</v>
       </c>
       <c r="O22">
-        <v>20.21693876092239</v>
+        <v>21.39714396092239</v>
       </c>
       <c r="P22">
-        <v>80.86775504368956</v>
+        <v>85.58857584368955</v>
       </c>
       <c r="Q22">
-        <v>168.7677550436896</v>
+        <v>173.4885758436895</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1505887201050623</v>
+        <v>0.1505957214709575</v>
       </c>
       <c r="T22">
         <v>0.8976574856178202</v>
       </c>
       <c r="U22">
-        <v>0.1316771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.1053417505578974</v>
+        <v>0.09486175055789736</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.704192396337517</v>
+        <v>3.002942273363246</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1419600958343665</v>
+        <v>0.1410752852581395</v>
       </c>
       <c r="C23">
-        <v>1824.257291842556</v>
+        <v>1844.977345315469</v>
       </c>
       <c r="D23">
-        <v>2217.540291842557</v>
+        <v>2238.260345315469</v>
       </c>
       <c r="E23">
         <v>-122.317</v>
@@ -3167,37 +3167,37 @@
         <v>160.4</v>
       </c>
       <c r="M23">
-        <v>62.28107150515746</v>
+        <v>59.77426160515746</v>
       </c>
       <c r="N23">
-        <v>98.11892849484255</v>
+        <v>100.6257383948425</v>
       </c>
       <c r="O23">
-        <v>19.62378569896851</v>
+        <v>20.12514767896851</v>
       </c>
       <c r="P23">
-        <v>78.49514279587405</v>
+        <v>80.50059071587404</v>
       </c>
       <c r="Q23">
-        <v>166.3951427958741</v>
+        <v>168.400590715874</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1516940863508963</v>
+        <v>0.1517011615708621</v>
       </c>
       <c r="T23">
         <v>0.9071264464365736</v>
       </c>
       <c r="U23">
-        <v>0.1316771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.1053417505578974</v>
+        <v>0.1011017505578974</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.575421329845255</v>
+        <v>2.68342921673432</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1432080654731037</v>
+        <v>0.1414536432279336</v>
       </c>
       <c r="C24">
-        <v>1773.323677757832</v>
+        <v>1813.600906893828</v>
       </c>
       <c r="D24">
-        <v>2189.129677757832</v>
+        <v>2229.406906893828</v>
       </c>
       <c r="E24">
         <v>-99.79399999999993</v>
@@ -3249,45 +3249,45 @@
         <v>160.4</v>
       </c>
       <c r="M24">
-        <v>67.57571501492686</v>
+        <v>62.62065501492687</v>
       </c>
       <c r="N24">
-        <v>92.82428498507315</v>
+        <v>97.77934498507314</v>
       </c>
       <c r="O24">
-        <v>18.56485699701463</v>
+        <v>19.55586899701463</v>
       </c>
       <c r="P24">
-        <v>74.25942798805852</v>
+        <v>78.22347598805851</v>
       </c>
       <c r="Q24">
-        <v>162.1594279880585</v>
+        <v>166.1234759880585</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1528277953209825</v>
+        <v>0.152834946288713</v>
       </c>
       <c r="T24">
         <v>0.9168382011224745</v>
       </c>
       <c r="U24">
-        <v>0.1363771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.1091017505578974</v>
+        <v>0.1011017505578974</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.373633781966926</v>
+        <v>2.561455161428214</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1436664351118409</v>
+        <v>0.1425496011977276</v>
       </c>
       <c r="C25">
-        <v>1740.54761624194</v>
+        <v>1765.823681168073</v>
       </c>
       <c r="D25">
-        <v>2178.87661624194</v>
+        <v>2204.152681168073</v>
       </c>
       <c r="E25">
         <v>-77.27099999999984</v>
@@ -3331,37 +3331,37 @@
         <v>160.4</v>
       </c>
       <c r="M25">
-        <v>70.64733842469627</v>
+        <v>67.48736152469627</v>
       </c>
       <c r="N25">
-        <v>89.75266157530373</v>
+        <v>92.91263847530374</v>
       </c>
       <c r="O25">
-        <v>17.95053231506075</v>
+        <v>18.58252769506075</v>
       </c>
       <c r="P25">
-        <v>71.80212926024299</v>
+        <v>74.33011078024299</v>
       </c>
       <c r="Q25">
-        <v>159.702129260243</v>
+        <v>162.230110780243</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1539909512773046</v>
+        <v>0.1539981799602743</v>
       </c>
       <c r="T25">
         <v>0.9268022091768404</v>
       </c>
       <c r="U25">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.1091017505578974</v>
+        <v>0.1042217505578974</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.270432313185755</v>
+        <v>2.376741309427297</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1441248047505781</v>
+        <v>0.1429591591675217</v>
       </c>
       <c r="C26">
-        <v>1707.86714997518</v>
+        <v>1734.009449080949</v>
       </c>
       <c r="D26">
-        <v>2168.71914997518</v>
+        <v>2194.861449080949</v>
       </c>
       <c r="E26">
         <v>-54.74799999999993</v>
@@ -3413,37 +3413,37 @@
         <v>160.4</v>
       </c>
       <c r="M26">
-        <v>73.71896183446566</v>
+        <v>70.42159463446566</v>
       </c>
       <c r="N26">
-        <v>86.68103816553435</v>
+        <v>89.97840536553434</v>
       </c>
       <c r="O26">
-        <v>17.33620763310687</v>
+        <v>17.99568107310687</v>
       </c>
       <c r="P26">
-        <v>69.34483053242748</v>
+        <v>71.98272429242748</v>
       </c>
       <c r="Q26">
-        <v>157.2448305324275</v>
+        <v>159.8827242924275</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1551847166008984</v>
+        <v>0.1551920250442451</v>
       </c>
       <c r="T26">
         <v>0.9370284279694789</v>
       </c>
       <c r="U26">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.1091017505578974</v>
+        <v>0.1042217505578974</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.175830966803015</v>
+        <v>2.277710421534493</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1445831743893153</v>
+        <v>0.1433687171373157</v>
       </c>
       <c r="C27">
-        <v>1675.280948226076</v>
+        <v>1702.273219416367</v>
       </c>
       <c r="D27">
-        <v>2158.655948226076</v>
+        <v>2185.648219416367</v>
       </c>
       <c r="E27">
         <v>-32.22499999999991</v>
@@ -3495,37 +3495,37 @@
         <v>160.4</v>
       </c>
       <c r="M27">
-        <v>76.79058524423506</v>
+        <v>73.35582774423507</v>
       </c>
       <c r="N27">
-        <v>83.60941475576494</v>
+        <v>87.04417225576493</v>
       </c>
       <c r="O27">
-        <v>16.72188295115299</v>
+        <v>17.40883445115299</v>
       </c>
       <c r="P27">
-        <v>66.88753180461195</v>
+        <v>69.63533780461195</v>
       </c>
       <c r="Q27">
-        <v>154.7875318046119</v>
+        <v>157.535337804612</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1564103156664547</v>
+        <v>0.1564177059971218</v>
       </c>
       <c r="T27">
         <v>0.9475273459299213</v>
       </c>
       <c r="U27">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.1091017505578974</v>
+        <v>0.1042217505578974</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.088797728130895</v>
+        <v>2.186602004673114</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1450415440280525</v>
+        <v>0.1437782751071097</v>
       </c>
       <c r="C28">
-        <v>1642.787704848297</v>
+        <v>1670.614014002977</v>
       </c>
       <c r="D28">
-        <v>2148.685704848297</v>
+        <v>2176.512014002977</v>
       </c>
       <c r="E28">
         <v>-9.701999999999884</v>
@@ -3577,37 +3577,37 @@
         <v>160.4</v>
       </c>
       <c r="M28">
-        <v>79.86220865400448</v>
+        <v>76.29006085400448</v>
       </c>
       <c r="N28">
-        <v>80.53779134599553</v>
+        <v>84.10993914599553</v>
       </c>
       <c r="O28">
-        <v>16.10755826919911</v>
+        <v>16.82198782919911</v>
       </c>
       <c r="P28">
-        <v>64.43023307679643</v>
+        <v>67.28795131679642</v>
       </c>
       <c r="Q28">
-        <v>152.3302330767964</v>
+        <v>155.1879513167964</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.15766903903108</v>
+        <v>0.1576765134622384</v>
       </c>
       <c r="T28">
         <v>0.9583100184298351</v>
       </c>
       <c r="U28">
-        <v>0.1363771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.1091017505578974</v>
+        <v>0.1042217505578974</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.008459353972014</v>
+        <v>2.102501927570302</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1490207136667898</v>
+        <v>0.1441878330769038</v>
       </c>
       <c r="C29">
-        <v>1537.432639304538</v>
+        <v>1639.030870956726</v>
       </c>
       <c r="D29">
-        <v>2065.853639304538</v>
+        <v>2167.451870956726</v>
       </c>
       <c r="E29">
         <v>12.82100000000014</v>
@@ -3659,45 +3659,45 @@
         <v>160.4</v>
       </c>
       <c r="M29">
-        <v>92.84620436377389</v>
+        <v>79.22429396377389</v>
       </c>
       <c r="N29">
-        <v>67.55379563622611</v>
+        <v>81.17570603622612</v>
       </c>
       <c r="O29">
-        <v>13.51075912724522</v>
+        <v>16.23514120724522</v>
       </c>
       <c r="P29">
-        <v>54.04303650898089</v>
+        <v>64.9405648289809</v>
       </c>
       <c r="Q29">
-        <v>141.9430365089809</v>
+        <v>152.8405648289809</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.158962247967339</v>
+        <v>0.1589698088031117</v>
       </c>
       <c r="T29">
         <v>0.9693881066146781</v>
       </c>
       <c r="U29">
-        <v>0.1526771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.1221417505578974</v>
+        <v>0.1042217505578974</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.727588123813318</v>
+        <v>2.024631485808438</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1496094833055269</v>
+        <v>0.1477781910466978</v>
       </c>
       <c r="C30">
-        <v>1503.192868715117</v>
+        <v>1540.198142188631</v>
       </c>
       <c r="D30">
-        <v>2054.136868715118</v>
+        <v>2091.142142188631</v>
       </c>
       <c r="E30">
         <v>35.34400000000016</v>
@@ -3741,37 +3741,37 @@
         <v>160.4</v>
       </c>
       <c r="M30">
-        <v>96.28495267354329</v>
+        <v>91.1136718735433</v>
       </c>
       <c r="N30">
-        <v>64.11504732645672</v>
+        <v>69.28632812645671</v>
       </c>
       <c r="O30">
-        <v>12.82300946529134</v>
+        <v>13.85726562529134</v>
       </c>
       <c r="P30">
-        <v>51.29203786116538</v>
+        <v>55.42906250116537</v>
       </c>
       <c r="Q30">
-        <v>139.1920378611654</v>
+        <v>143.3290625011654</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1602913793740496</v>
+        <v>0.1602990290145647</v>
       </c>
       <c r="T30">
         <v>0.9807739194713221</v>
       </c>
       <c r="U30">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.1221417505578974</v>
+        <v>0.1155817505578974</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.665888547962842</v>
+        <v>1.76043832612321</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1501982529442641</v>
+        <v>0.1483013490164919</v>
       </c>
       <c r="C31">
-        <v>1469.085255103279</v>
+        <v>1507.002134582828</v>
       </c>
       <c r="D31">
-        <v>2042.55225510328</v>
+        <v>2080.469134582828</v>
       </c>
       <c r="E31">
         <v>57.86700000000008</v>
@@ -3823,37 +3823,37 @@
         <v>160.4</v>
       </c>
       <c r="M31">
-        <v>99.72370098331268</v>
+        <v>94.36773158331269</v>
       </c>
       <c r="N31">
-        <v>60.67629901668732</v>
+        <v>66.03226841668732</v>
       </c>
       <c r="O31">
-        <v>12.13525980333747</v>
+        <v>13.20645368333746</v>
       </c>
       <c r="P31">
-        <v>48.54103921334986</v>
+        <v>52.82581473334985</v>
       </c>
       <c r="Q31">
-        <v>136.4410392133499</v>
+        <v>140.7258147333499</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1616579511020759</v>
+        <v>0.1616656920488755</v>
       </c>
       <c r="T31">
         <v>0.9924804594506885</v>
       </c>
       <c r="U31">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.1221417505578974</v>
+        <v>0.1155817505578974</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.608444115274468</v>
+        <v>1.699733556256893</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1507870225830013</v>
+        <v>0.1488245069862859</v>
       </c>
       <c r="C32">
-        <v>1435.107575050912</v>
+        <v>1473.914521943503</v>
       </c>
       <c r="D32">
-        <v>2031.097575050912</v>
+        <v>2069.904521943503</v>
       </c>
       <c r="E32">
         <v>80.3900000000001</v>
@@ -3905,37 +3905,37 @@
         <v>160.4</v>
       </c>
       <c r="M32">
-        <v>103.1624492930821</v>
+        <v>97.6217912930821</v>
       </c>
       <c r="N32">
-        <v>57.23755070691792</v>
+        <v>62.77820870691791</v>
       </c>
       <c r="O32">
-        <v>11.44751014138358</v>
+        <v>12.55564174138358</v>
       </c>
       <c r="P32">
-        <v>45.79004056553433</v>
+        <v>50.22256696553433</v>
       </c>
       <c r="Q32">
-        <v>133.6900405655343</v>
+        <v>138.1225669655343</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1630635677366173</v>
+        <v>0.1630714025984525</v>
       </c>
       <c r="T32">
         <v>1.004521472000894</v>
       </c>
       <c r="U32">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.1221417505578974</v>
+        <v>0.1155817505578974</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.554829311431986</v>
+        <v>1.64307577104833</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1513757922217385</v>
+        <v>0.14934766495608</v>
       </c>
       <c r="C33">
-        <v>1401.257654737673</v>
+        <v>1440.933661326107</v>
       </c>
       <c r="D33">
-        <v>2019.770654737673</v>
+        <v>2059.446661326107</v>
       </c>
       <c r="E33">
         <v>102.9130000000001</v>
@@ -3987,37 +3987,37 @@
         <v>160.4</v>
       </c>
       <c r="M33">
-        <v>106.6011976028515</v>
+        <v>100.8758510028515</v>
       </c>
       <c r="N33">
-        <v>53.79880239714851</v>
+        <v>59.5241489971485</v>
       </c>
       <c r="O33">
-        <v>10.7597604794297</v>
+        <v>11.9048297994297</v>
       </c>
       <c r="P33">
-        <v>43.03904191771881</v>
+        <v>47.6193191977188</v>
       </c>
       <c r="Q33">
-        <v>130.9390419177188</v>
+        <v>135.5193191977188</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1645099268823049</v>
+        <v>0.1645178583813504</v>
       </c>
       <c r="T33">
         <v>1.016911499407627</v>
       </c>
       <c r="U33">
-        <v>0.1526771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.1221417505578974</v>
+        <v>0.1155817505578974</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.504673527192244</v>
+        <v>1.590073326820964</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1687069618604757</v>
+        <v>0.149870822925874</v>
       </c>
       <c r="C34">
-        <v>1093.92582602104</v>
+        <v>1408.057942822036</v>
       </c>
       <c r="D34">
-        <v>1734.96182602104</v>
+        <v>2049.093942822037</v>
       </c>
       <c r="E34">
         <v>125.4360000000001</v>
@@ -4069,45 +4069,45 @@
         <v>160.4</v>
       </c>
       <c r="M34">
-        <v>157.1760803126209</v>
+        <v>104.1299107126209</v>
       </c>
       <c r="N34">
-        <v>3.223919687379095</v>
+        <v>56.27008928737909</v>
       </c>
       <c r="O34">
-        <v>0.644783937475819</v>
+        <v>11.25401785747582</v>
       </c>
       <c r="P34">
-        <v>2.579135749903275</v>
+        <v>45.01607142990328</v>
       </c>
       <c r="Q34">
-        <v>90.47913574990328</v>
+        <v>132.9160714299033</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1659988260028656</v>
+        <v>0.1660068569813924</v>
       </c>
       <c r="T34">
         <v>1.029665939385147</v>
       </c>
       <c r="U34">
-        <v>0.2180771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.1744617505578974</v>
+        <v>0.1155817505578974</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.020511516007822</v>
+        <v>1.540383535357809</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1700288223827772</v>
+        <v>0.165389180895668</v>
       </c>
       <c r="C35">
-        <v>1052.94191251056</v>
+        <v>1119.636530605377</v>
       </c>
       <c r="D35">
-        <v>1716.50091251056</v>
+        <v>1783.195530605377</v>
       </c>
       <c r="E35">
         <v>147.9590000000002</v>
@@ -4151,37 +4151,37 @@
         <v>160.4</v>
       </c>
       <c r="M35">
-        <v>162.0878328223903</v>
+        <v>149.6010816223903</v>
       </c>
       <c r="N35">
-        <v>-1.687832822390334</v>
+        <v>10.79891837760968</v>
       </c>
       <c r="O35">
-        <v>-0.3375665644780668</v>
+        <v>2.159783675521936</v>
       </c>
       <c r="P35">
-        <v>-1.350266257912267</v>
+        <v>8.639134702087745</v>
       </c>
       <c r="Q35">
-        <v>86.54973374208774</v>
+        <v>96.53913470208775</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1676217437633164</v>
+        <v>0.1675403033008387</v>
       </c>
       <c r="T35">
-        <v>1.043568430748245</v>
+        <v>1.042801108914234</v>
       </c>
       <c r="U35">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V35">
-        <v>0.1979173849227291</v>
+        <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.174915921398046</v>
+        <v>0.1610217505578974</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.9895869246136457</v>
+        <v>1.072184761370024</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1717515942647509</v>
+        <v>0.1663667388654621</v>
       </c>
       <c r="C36">
-        <v>1006.940531591939</v>
+        <v>1082.655339075542</v>
       </c>
       <c r="D36">
-        <v>1693.022531591939</v>
+        <v>1768.737339075542</v>
       </c>
       <c r="E36">
         <v>170.4820000000002</v>
@@ -4233,37 +4233,37 @@
         <v>160.4</v>
       </c>
       <c r="M36">
-        <v>166.9995853321597</v>
+        <v>154.1344477321597</v>
       </c>
       <c r="N36">
-        <v>-6.599585332159734</v>
+        <v>6.265552267840292</v>
       </c>
       <c r="O36">
-        <v>-1.319917066431947</v>
+        <v>1.253110453568058</v>
       </c>
       <c r="P36">
-        <v>-5.279668265727787</v>
+        <v>5.012441814272234</v>
       </c>
       <c r="Q36">
-        <v>82.62033173427221</v>
+        <v>92.91244181427224</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1694675277597303</v>
+        <v>0.1691202176905712</v>
       </c>
       <c r="T36">
-        <v>1.05938007363837</v>
+        <v>1.056334313883597</v>
       </c>
       <c r="U36">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V36">
-        <v>0.1920962853661783</v>
+        <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.1761853704215556</v>
+        <v>0.1610217505578974</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.9604814268308915</v>
+        <v>1.040649915447376</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1734743661467246</v>
+        <v>0.1673442968352561</v>
       </c>
       <c r="C37">
-        <v>961.5727609382699</v>
+        <v>1045.906716588053</v>
       </c>
       <c r="D37">
-        <v>1670.17776093827</v>
+        <v>1754.511716588054</v>
       </c>
       <c r="E37">
         <v>193.0050000000002</v>
@@ -4315,37 +4315,37 @@
         <v>160.4</v>
       </c>
       <c r="M37">
-        <v>171.9113378419291</v>
+        <v>158.6678138419291</v>
       </c>
       <c r="N37">
-        <v>-11.51133784192913</v>
+        <v>1.732186158070874</v>
       </c>
       <c r="O37">
-        <v>-2.302267568385827</v>
+        <v>0.3464372316141748</v>
       </c>
       <c r="P37">
-        <v>-9.209070273543308</v>
+        <v>1.385748926456699</v>
       </c>
       <c r="Q37">
-        <v>78.6909297264567</v>
+        <v>89.28574892645671</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.17137010510988</v>
+        <v>0.170748744830757</v>
       </c>
       <c r="T37">
-        <v>1.075678228617422</v>
+        <v>1.070283925159709</v>
       </c>
       <c r="U37">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V37">
-        <v>0.1866078200700018</v>
+        <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.1773822795008647</v>
+        <v>0.1610217505578974</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9330391003500089</v>
+        <v>1.010917060720308</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1751971380286983</v>
+        <v>0.1686785169407543</v>
       </c>
       <c r="C38">
-        <v>916.813293205853</v>
+        <v>1004.333154570508</v>
       </c>
       <c r="D38">
-        <v>1647.941293205853</v>
+        <v>1735.461154570508</v>
       </c>
       <c r="E38">
         <v>215.5280000000001</v>
@@ -4397,37 +4397,37 @@
         <v>160.4</v>
       </c>
       <c r="M38">
-        <v>176.8230903516985</v>
+        <v>163.2011799516985</v>
       </c>
       <c r="N38">
-        <v>-16.42309035169853</v>
+        <v>-2.801179951698515</v>
       </c>
       <c r="O38">
-        <v>-3.284618070339707</v>
+        <v>-0.5602359903397031</v>
       </c>
       <c r="P38">
-        <v>-13.13847228135883</v>
+        <v>-2.240943961358812</v>
       </c>
       <c r="Q38">
-        <v>74.76152771864118</v>
+        <v>85.6590560386412</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1733321380022218</v>
+        <v>0.1725967925523094</v>
       </c>
       <c r="T38">
-        <v>1.092485700939569</v>
+        <v>1.086113902259396</v>
       </c>
       <c r="U38">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V38">
-        <v>0.1814242695125018</v>
+        <v>0.1965672062511711</v>
       </c>
       <c r="W38">
-        <v>0.1785126936313232</v>
+        <v>0.1617126936313232</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9071213475625086</v>
+        <v>0.9828360312558552</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.176919909910672</v>
+        <v>0.1702332888227281</v>
       </c>
       <c r="C39">
-        <v>872.6381510940057</v>
+        <v>960.1258751392381</v>
       </c>
       <c r="D39">
-        <v>1626.289151094006</v>
+        <v>1713.776875139238</v>
       </c>
       <c r="E39">
         <v>238.0510000000002</v>
@@ -4479,37 +4479,37 @@
         <v>160.4</v>
       </c>
       <c r="M39">
-        <v>181.7348428614679</v>
+        <v>167.7345460614679</v>
       </c>
       <c r="N39">
-        <v>-21.33484286146793</v>
+        <v>-7.334546061467933</v>
       </c>
       <c r="O39">
-        <v>-4.266968572293587</v>
+        <v>-1.466909212293587</v>
       </c>
       <c r="P39">
-        <v>-17.06787428917435</v>
+        <v>-5.867636849174346</v>
       </c>
       <c r="Q39">
-        <v>70.83212571082566</v>
+        <v>82.03236315082566</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1753564576530507</v>
+        <v>0.1746094400531397</v>
       </c>
       <c r="T39">
-        <v>1.109826743811626</v>
+        <v>1.103353805469862</v>
       </c>
       <c r="U39">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V39">
-        <v>0.1765209108770287</v>
+        <v>0.1912545790551934</v>
       </c>
       <c r="W39">
-        <v>0.1795820042952704</v>
+        <v>0.1627820042952704</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8826045543851436</v>
+        <v>0.956272895275967</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1786426817926458</v>
+        <v>0.1717880607047018</v>
       </c>
       <c r="C40">
-        <v>829.0246011016709</v>
+        <v>916.4537909915862</v>
       </c>
       <c r="D40">
-        <v>1605.198601101671</v>
+        <v>1692.627790991586</v>
       </c>
       <c r="E40">
         <v>260.5740000000001</v>
@@ -4561,37 +4561,37 @@
         <v>160.4</v>
       </c>
       <c r="M40">
-        <v>186.6465953712373</v>
+        <v>172.2679121712373</v>
       </c>
       <c r="N40">
-        <v>-26.24659537123731</v>
+        <v>-11.86791217123729</v>
       </c>
       <c r="O40">
-        <v>-5.249319074247461</v>
+        <v>-2.373582434247459</v>
       </c>
       <c r="P40">
-        <v>-20.99727629698985</v>
+        <v>-9.494329736989835</v>
       </c>
       <c r="Q40">
-        <v>66.90272370301017</v>
+        <v>78.40567026301017</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1774460779377774</v>
+        <v>0.1766870116669</v>
       </c>
       <c r="T40">
-        <v>1.127727175163426</v>
+        <v>1.121149834590344</v>
       </c>
       <c r="U40">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V40">
-        <v>0.1718756237486859</v>
+        <v>0.1862215638168989</v>
       </c>
       <c r="W40">
-        <v>0.1805950354505889</v>
+        <v>0.1637950354505889</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8593781187434295</v>
+        <v>0.9311078190844945</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1803654536746195</v>
+        <v>0.1733428325866755</v>
       </c>
       <c r="C41">
-        <v>785.9510739087979</v>
+        <v>873.2973297244263</v>
       </c>
       <c r="D41">
-        <v>1584.648073908798</v>
+        <v>1671.994329724426</v>
       </c>
       <c r="E41">
         <v>283.0970000000001</v>
@@ -4643,37 +4643,37 @@
         <v>160.4</v>
       </c>
       <c r="M41">
-        <v>191.5583478810067</v>
+        <v>176.8012782810067</v>
       </c>
       <c r="N41">
-        <v>-31.15834788100673</v>
+        <v>-16.40127828100671</v>
       </c>
       <c r="O41">
-        <v>-6.231669576201347</v>
+        <v>-3.280255656201343</v>
       </c>
       <c r="P41">
-        <v>-24.92667830480539</v>
+        <v>-13.12102262480537</v>
       </c>
       <c r="Q41">
-        <v>62.97332169519462</v>
+        <v>74.77897737519464</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1796042103629868</v>
+        <v>0.1788327003827508</v>
       </c>
       <c r="T41">
-        <v>1.14621450590381</v>
+        <v>1.139529340075431</v>
       </c>
       <c r="U41">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V41">
-        <v>0.1674685564730786</v>
+        <v>0.1814466519241579</v>
       </c>
       <c r="W41">
-        <v>0.18155611629025</v>
+        <v>0.16475611629025</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8373427823653927</v>
+        <v>0.9072332596207895</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1820882255565932</v>
+        <v>0.1748976044686492</v>
       </c>
       <c r="C42">
-        <v>743.3970907963185</v>
+        <v>830.637861806415</v>
       </c>
       <c r="D42">
-        <v>1564.617090796319</v>
+        <v>1651.857861806415</v>
       </c>
       <c r="E42">
         <v>305.6200000000001</v>
@@ -4725,37 +4725,37 @@
         <v>160.4</v>
       </c>
       <c r="M42">
-        <v>196.4701003907761</v>
+        <v>181.3346443907761</v>
       </c>
       <c r="N42">
-        <v>-36.07010039077613</v>
+        <v>-20.93464439077613</v>
       </c>
       <c r="O42">
-        <v>-7.214020078155227</v>
+        <v>-4.186928878155226</v>
       </c>
       <c r="P42">
-        <v>-28.85608031262091</v>
+        <v>-16.7477155126209</v>
       </c>
       <c r="Q42">
-        <v>59.0439196873791</v>
+        <v>71.15228448737911</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1818342805357033</v>
+        <v>0.1810499120557967</v>
       </c>
       <c r="T42">
-        <v>1.165318081002207</v>
+        <v>1.158521495743355</v>
       </c>
       <c r="U42">
-        <v>0.2180771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V42">
-        <v>0.1632818425612516</v>
+        <v>0.1769104856260539</v>
       </c>
       <c r="W42">
-        <v>0.182469143087928</v>
+        <v>0.165669143087928</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8164092128062579</v>
+        <v>0.8845524281302696</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.2063145171790142</v>
+        <v>0.1764523763506229</v>
       </c>
       <c r="C43">
-        <v>484.7280363133958</v>
+        <v>788.457644476808</v>
       </c>
       <c r="D43">
-        <v>1328.471036313396</v>
+        <v>1632.200644476808</v>
       </c>
       <c r="E43">
         <v>328.1430000000001</v>
@@ -4807,45 +4807,45 @@
         <v>160.4</v>
       </c>
       <c r="M43">
-        <v>249.5855775005455</v>
+        <v>185.8680105005455</v>
       </c>
       <c r="N43">
-        <v>-89.18557750054552</v>
+        <v>-25.46801050054552</v>
       </c>
       <c r="O43">
-        <v>-17.8371155001091</v>
+        <v>-5.093602100109104</v>
       </c>
       <c r="P43">
-        <v>-71.34846200043641</v>
+        <v>-20.37440840043642</v>
       </c>
       <c r="Q43">
-        <v>16.55153799956359</v>
+        <v>67.5255915995636</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1860069289184224</v>
+        <v>0.1833422834465729</v>
       </c>
       <c r="T43">
-        <v>1.201062472687147</v>
+        <v>1.178157453298327</v>
       </c>
       <c r="U43">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V43">
-        <v>0.1285330679811812</v>
+        <v>0.1725955957327356</v>
       </c>
       <c r="W43">
-        <v>0.2355376319930364</v>
+        <v>0.1665376319930364</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.6426653399059064</v>
+        <v>0.8629779786636778</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.2085592890609879</v>
+        <v>0.1780071482325966</v>
       </c>
       <c r="C44">
-        <v>443.8827983290843</v>
+        <v>746.7397696028166</v>
       </c>
       <c r="D44">
-        <v>1310.148798329084</v>
+        <v>1613.005769602817</v>
       </c>
       <c r="E44">
         <v>350.6660000000001</v>
@@ -4889,45 +4889,45 @@
         <v>160.4</v>
       </c>
       <c r="M44">
-        <v>255.6730306103149</v>
+        <v>190.4013766103149</v>
       </c>
       <c r="N44">
-        <v>-95.27303061031489</v>
+        <v>-30.00137661031491</v>
       </c>
       <c r="O44">
-        <v>-19.05460612206298</v>
+        <v>-6.000275322062982</v>
       </c>
       <c r="P44">
-        <v>-76.21842448825191</v>
+        <v>-24.00110128825192</v>
       </c>
       <c r="Q44">
-        <v>11.68157551174809</v>
+        <v>63.89889871174808</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1884242897618435</v>
+        <v>0.1857137021266862</v>
       </c>
       <c r="T44">
-        <v>1.221770446354167</v>
+        <v>1.198470512837954</v>
       </c>
       <c r="U44">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V44">
-        <v>0.1254727568387722</v>
+        <v>0.1684861767867181</v>
       </c>
       <c r="W44">
-        <v>0.2363647642836158</v>
+        <v>0.1673647642836158</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.627363784193861</v>
+        <v>0.8424308839335902</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.2108040609429616</v>
+        <v>0.1795619201145703</v>
       </c>
       <c r="C45">
-        <v>403.5360843739027</v>
+        <v>705.4681151734262</v>
       </c>
       <c r="D45">
-        <v>1292.325084373903</v>
+        <v>1594.257115173426</v>
       </c>
       <c r="E45">
         <v>373.1890000000001</v>
@@ -4971,45 +4971,45 @@
         <v>160.4</v>
       </c>
       <c r="M45">
-        <v>261.7604837200843</v>
+        <v>194.9347427200843</v>
       </c>
       <c r="N45">
-        <v>-101.3604837200843</v>
+        <v>-34.53474272008432</v>
       </c>
       <c r="O45">
-        <v>-20.27209674401686</v>
+        <v>-6.906948544016865</v>
       </c>
       <c r="P45">
-        <v>-81.08838697606745</v>
+        <v>-27.62779417606746</v>
       </c>
       <c r="Q45">
-        <v>6.811613023932551</v>
+        <v>60.27220582393254</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1909264702839811</v>
+        <v>0.188168328479786</v>
       </c>
       <c r="T45">
-        <v>1.24320501558845</v>
+        <v>1.219496311308795</v>
       </c>
       <c r="U45">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V45">
-        <v>0.1225547857494984</v>
+        <v>0.1645678936056316</v>
       </c>
       <c r="W45">
-        <v>0.2371534253048659</v>
+        <v>0.1681534253048659</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.612773928747492</v>
+        <v>0.8228394680281579</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.2130488328249353</v>
+        <v>0.1811166919965441</v>
       </c>
       <c r="C46">
-        <v>363.6678212544376</v>
+        <v>664.6273001371884</v>
       </c>
       <c r="D46">
-        <v>1274.979821254438</v>
+        <v>1575.939300137188</v>
       </c>
       <c r="E46">
         <v>395.7120000000001</v>
@@ -5053,45 +5053,45 @@
         <v>160.4</v>
       </c>
       <c r="M46">
-        <v>267.8479368298537</v>
+        <v>199.4681088298537</v>
       </c>
       <c r="N46">
-        <v>-107.4479368298537</v>
+        <v>-39.06810882985371</v>
       </c>
       <c r="O46">
-        <v>-21.48958736597075</v>
+        <v>-7.813621765970743</v>
       </c>
       <c r="P46">
-        <v>-85.95834946388297</v>
+        <v>-31.25448706388297</v>
       </c>
       <c r="Q46">
-        <v>1.941650536117038</v>
+        <v>56.64551293611704</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1935180143961951</v>
+        <v>0.1907106200597821</v>
       </c>
       <c r="T46">
-        <v>1.26540510515253</v>
+        <v>1.241273031153595</v>
       </c>
       <c r="U46">
-        <v>0.2702771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V46">
-        <v>0.1197694497097371</v>
+        <v>0.1608277142055036</v>
       </c>
       <c r="W46">
-        <v>0.2379062380978774</v>
+        <v>0.1689062380978774</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.5988472485486854</v>
+        <v>0.804138571027518</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.215293604706909</v>
+        <v>0.2082787107889909</v>
       </c>
       <c r="C47">
-        <v>324.2589991741006</v>
+        <v>378.6501363380121</v>
       </c>
       <c r="D47">
-        <v>1258.093999174101</v>
+        <v>1312.485136338012</v>
       </c>
       <c r="E47">
         <v>418.2350000000001</v>
@@ -5135,37 +5135,37 @@
         <v>160.4</v>
       </c>
       <c r="M47">
-        <v>273.9353899396231</v>
+        <v>258.7323649396231</v>
       </c>
       <c r="N47">
-        <v>-113.5353899396231</v>
+        <v>-98.33236493962309</v>
       </c>
       <c r="O47">
-        <v>-22.70707798792462</v>
+        <v>-19.66647298792462</v>
       </c>
       <c r="P47">
-        <v>-90.8283119516985</v>
+        <v>-78.66589195169847</v>
       </c>
       <c r="Q47">
-        <v>-2.92831195169849</v>
+        <v>9.234108048301536</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1962037964761259</v>
+        <v>0.1957221711708202</v>
       </c>
       <c r="T47">
-        <v>1.288412470700758</v>
+        <v>1.284200894106724</v>
       </c>
       <c r="U47">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V47">
-        <v>0.1171079063828541</v>
+        <v>0.1239891267854568</v>
       </c>
       <c r="W47">
-        <v>0.2386255925445328</v>
+        <v>0.2236255925445328</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5855395319142702</v>
+        <v>0.619945633927284</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.2175383765888828</v>
+        <v>0.2103734826709646</v>
       </c>
       <c r="C48">
-        <v>285.2916022354566</v>
+        <v>339.4211827755773</v>
       </c>
       <c r="D48">
-        <v>1241.649602235457</v>
+        <v>1295.779182775578</v>
       </c>
       <c r="E48">
         <v>440.7580000000003</v>
@@ -5217,37 +5217,37 @@
         <v>160.4</v>
       </c>
       <c r="M48">
-        <v>280.0228430493926</v>
+        <v>264.4819730493925</v>
       </c>
       <c r="N48">
-        <v>-119.6228430493926</v>
+        <v>-104.0819730493925</v>
       </c>
       <c r="O48">
-        <v>-23.92456860987852</v>
+        <v>-20.81639460987851</v>
       </c>
       <c r="P48">
-        <v>-95.69827443951405</v>
+        <v>-83.26557843951403</v>
       </c>
       <c r="Q48">
-        <v>-7.798274439514046</v>
+        <v>4.634421560485976</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1989890519664245</v>
+        <v>0.1984985076739835</v>
       </c>
       <c r="T48">
-        <v>1.31227196089892</v>
+        <v>1.307982392145738</v>
       </c>
       <c r="U48">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V48">
-        <v>0.1145620823310529</v>
+        <v>0.1212937109857729</v>
       </c>
       <c r="W48">
-        <v>0.2393136707108989</v>
+        <v>0.2243136707108989</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5728104116552641</v>
+        <v>0.6064685549288646</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.2197831484708565</v>
+        <v>0.2124682545529383</v>
       </c>
       <c r="C49">
-        <v>246.7485443226128</v>
+        <v>300.6121671536703</v>
       </c>
       <c r="D49">
-        <v>1225.629544322613</v>
+        <v>1279.49316715367</v>
       </c>
       <c r="E49">
         <v>463.2810000000002</v>
@@ -5299,37 +5299,37 @@
         <v>160.4</v>
       </c>
       <c r="M49">
-        <v>286.1102961591619</v>
+        <v>270.2315811591619</v>
       </c>
       <c r="N49">
-        <v>-125.7102961591619</v>
+        <v>-109.8315811591619</v>
       </c>
       <c r="O49">
-        <v>-25.14205923183238</v>
+        <v>-21.96631623183238</v>
       </c>
       <c r="P49">
-        <v>-100.5682369273295</v>
+        <v>-87.86526492732953</v>
       </c>
       <c r="Q49">
-        <v>-12.66823692732953</v>
+        <v>0.03473507267047182</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.2018794114374891</v>
+        <v>0.2013796115923606</v>
       </c>
       <c r="T49">
-        <v>1.337031809217768</v>
+        <v>1.332661305205092</v>
       </c>
       <c r="U49">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V49">
-        <v>0.1121245912176262</v>
+        <v>0.1187129937307565</v>
       </c>
       <c r="W49">
-        <v>0.239972468955292</v>
+        <v>0.2249724689552919</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5606229560881311</v>
+        <v>0.5935649686537825</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.2220279203528301</v>
+        <v>0.214563026434912</v>
       </c>
       <c r="C50">
-        <v>208.6136098839424</v>
+        <v>262.2074520271362</v>
       </c>
       <c r="D50">
-        <v>1210.017609883942</v>
+        <v>1263.611452027136</v>
       </c>
       <c r="E50">
         <v>485.8040000000001</v>
@@ -5381,37 +5381,37 @@
         <v>160.4</v>
       </c>
       <c r="M50">
-        <v>292.1977492689313</v>
+        <v>275.9811892689313</v>
       </c>
       <c r="N50">
-        <v>-131.7977492689313</v>
+        <v>-115.5811892689313</v>
       </c>
       <c r="O50">
-        <v>-26.35954985378626</v>
+        <v>-23.11623785378626</v>
       </c>
       <c r="P50">
-        <v>-105.438199415145</v>
+        <v>-92.46495141514504</v>
       </c>
       <c r="Q50">
-        <v>-17.53819941514504</v>
+        <v>-4.564951415145032</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.2048809385805177</v>
+        <v>0.204371527199906</v>
       </c>
       <c r="T50">
-        <v>1.362743959395032</v>
+        <v>1.358289407228266</v>
       </c>
       <c r="U50">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V50">
-        <v>0.1097886622339257</v>
+        <v>0.1162398063613657</v>
       </c>
       <c r="W50">
-        <v>0.2406038172728353</v>
+        <v>0.2256038172728353</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5489433111696284</v>
+        <v>0.5811990318068286</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.2242726922348039</v>
+        <v>0.2166577983168858</v>
       </c>
       <c r="C51">
-        <v>170.8713991837026</v>
+        <v>224.1921668313669</v>
       </c>
       <c r="D51">
-        <v>1194.798399183703</v>
+        <v>1248.119166831367</v>
       </c>
       <c r="E51">
         <v>508.3270000000002</v>
@@ -5463,37 +5463,37 @@
         <v>160.4</v>
       </c>
       <c r="M51">
-        <v>298.2852023787008</v>
+        <v>281.7307973787007</v>
       </c>
       <c r="N51">
-        <v>-137.8852023787008</v>
+        <v>-121.3307973787007</v>
       </c>
       <c r="O51">
-        <v>-27.57704047574016</v>
+        <v>-24.26615947574015</v>
       </c>
       <c r="P51">
-        <v>-110.3081619029606</v>
+        <v>-97.06463790296058</v>
       </c>
       <c r="Q51">
-        <v>-22.40816190296061</v>
+        <v>-9.164637902960578</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.2080001726703318</v>
+        <v>0.2074807728312767</v>
       </c>
       <c r="T51">
-        <v>1.389464429187092</v>
+        <v>1.384922532860193</v>
       </c>
       <c r="U51">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V51">
-        <v>0.1075480772903761</v>
+        <v>0.1138675654152154</v>
       </c>
       <c r="W51">
-        <v>0.2412093962712952</v>
+        <v>0.2262093962712952</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5377403864518807</v>
+        <v>0.5693378270760769</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.2265174641167776</v>
+        <v>0.2187525701988595</v>
       </c>
       <c r="C52">
-        <v>133.5072776339798</v>
+        <v>186.5521614406714</v>
       </c>
       <c r="D52">
-        <v>1179.95727763398</v>
+        <v>1233.002161440671</v>
       </c>
       <c r="E52">
         <v>530.8500000000001</v>
@@ -5545,37 +5545,37 @@
         <v>160.4</v>
       </c>
       <c r="M52">
-        <v>304.3726554884701</v>
+        <v>287.4804054884701</v>
       </c>
       <c r="N52">
-        <v>-143.9726554884701</v>
+        <v>-127.0804054884701</v>
       </c>
       <c r="O52">
-        <v>-28.79453109769402</v>
+        <v>-25.41608109769403</v>
       </c>
       <c r="P52">
-        <v>-115.1781243907761</v>
+        <v>-101.6643243907761</v>
       </c>
       <c r="Q52">
-        <v>-27.27812439077609</v>
+        <v>-13.7643243907761</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.2112441761237385</v>
+        <v>0.2107143882879022</v>
       </c>
       <c r="T52">
-        <v>1.417253717770834</v>
+        <v>1.412620983517397</v>
       </c>
       <c r="U52">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V52">
-        <v>0.1053971157445687</v>
+        <v>0.1115902141069111</v>
       </c>
       <c r="W52">
-        <v>0.2417907521098167</v>
+        <v>0.2267907521098167</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5269855787228432</v>
+        <v>0.5579510705345555</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.2287622359987513</v>
+        <v>0.2208473420808332</v>
       </c>
       <c r="C53">
-        <v>96.50732885652246</v>
+        <v>149.2739630612182</v>
       </c>
       <c r="D53">
-        <v>1165.480328856522</v>
+        <v>1218.246963061218</v>
       </c>
       <c r="E53">
         <v>553.373</v>
@@ -5627,37 +5627,37 @@
         <v>160.4</v>
       </c>
       <c r="M53">
-        <v>310.4601085982395</v>
+        <v>293.2300135982395</v>
       </c>
       <c r="N53">
-        <v>-150.0601085982395</v>
+        <v>-132.8300135982395</v>
       </c>
       <c r="O53">
-        <v>-30.0120217196479</v>
+        <v>-26.5660027196479</v>
       </c>
       <c r="P53">
-        <v>-120.0480868785916</v>
+        <v>-106.2640108785916</v>
       </c>
       <c r="Q53">
-        <v>-32.1480868785916</v>
+        <v>-18.3640108785916</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.2146205878813658</v>
+        <v>0.2140799880488798</v>
       </c>
       <c r="T53">
-        <v>1.446177263031463</v>
+        <v>1.441449983181017</v>
       </c>
       <c r="U53">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V53">
-        <v>0.1033305056319301</v>
+        <v>0.1094021706930501</v>
       </c>
       <c r="W53">
-        <v>0.2423493096801609</v>
+        <v>0.2273493096801609</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5166525281596502</v>
+        <v>0.5470108534652505</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.231007007880725</v>
+        <v>0.2229421139628069</v>
       </c>
       <c r="C54">
-        <v>59.85831115801557</v>
+        <v>112.3447361825192</v>
       </c>
       <c r="D54">
-        <v>1151.354311158016</v>
+        <v>1203.840736182519</v>
       </c>
       <c r="E54">
         <v>575.8960000000002</v>
@@ -5709,37 +5709,37 @@
         <v>160.4</v>
       </c>
       <c r="M54">
-        <v>316.547561708009</v>
+        <v>298.9796217080089</v>
       </c>
       <c r="N54">
-        <v>-156.147561708009</v>
+        <v>-138.5796217080089</v>
       </c>
       <c r="O54">
-        <v>-31.22951234160179</v>
+        <v>-27.71592434160179</v>
       </c>
       <c r="P54">
-        <v>-124.9180493664072</v>
+        <v>-110.8636973664072</v>
       </c>
       <c r="Q54">
-        <v>-37.01804936640717</v>
+        <v>-22.96369736640715</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.2181376834622276</v>
+        <v>0.2175858211332315</v>
       </c>
       <c r="T54">
-        <v>1.476305956011285</v>
+        <v>1.471480191163955</v>
       </c>
       <c r="U54">
-        <v>0.2702771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V54">
-        <v>0.1013433805236237</v>
+        <v>0.1072982827951068</v>
       </c>
       <c r="W54">
-        <v>0.2428863842670304</v>
+        <v>0.2278863842670304</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5067169026181184</v>
+        <v>0.5364914139755341</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.2496115394986922</v>
+        <v>0.2250368858447806</v>
       </c>
       <c r="C55">
-        <v>-67.7637805720658</v>
+        <v>75.75224533723917</v>
       </c>
       <c r="D55">
-        <v>1046.255219427934</v>
+        <v>1189.771245337239</v>
       </c>
       <c r="E55">
         <v>598.4190000000001</v>
@@ -5791,45 +5791,45 @@
         <v>160.4</v>
       </c>
       <c r="M55">
-        <v>358.4465848177784</v>
+        <v>304.7292298177783</v>
       </c>
       <c r="N55">
-        <v>-198.0465848177784</v>
+        <v>-144.3292298177783</v>
       </c>
       <c r="O55">
-        <v>-39.60931696355568</v>
+        <v>-28.86584596355567</v>
       </c>
       <c r="P55">
-        <v>-158.4372678542227</v>
+        <v>-115.4633838542227</v>
       </c>
       <c r="Q55">
-        <v>-70.5372678542227</v>
+        <v>-27.56338385422265</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.2227826548890696</v>
+        <v>0.2212408386041513</v>
       </c>
       <c r="T55">
-        <v>1.516096435059079</v>
+        <v>1.502788280337656</v>
       </c>
       <c r="U55">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V55">
-        <v>0.08949729571648268</v>
+        <v>0.1052737868933123</v>
       </c>
       <c r="W55">
-        <v>0.2734031918883576</v>
+        <v>0.2284031918883576</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.4474864785824134</v>
+        <v>0.5263689344665619</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.252156311380666</v>
+        <v>0.2271316577267543</v>
       </c>
       <c r="C56">
-        <v>-103.1891281957205</v>
+        <v>39.4848204422276</v>
       </c>
       <c r="D56">
-        <v>1033.35287180428</v>
+        <v>1176.026820442228</v>
       </c>
       <c r="E56">
         <v>620.9420000000002</v>
@@ -5873,45 +5873,45 @@
         <v>160.4</v>
       </c>
       <c r="M56">
-        <v>365.2097279275478</v>
+        <v>310.4788379275478</v>
       </c>
       <c r="N56">
-        <v>-204.8097279275478</v>
+        <v>-150.0788379275478</v>
       </c>
       <c r="O56">
-        <v>-40.96194558550957</v>
+        <v>-30.01576758550955</v>
       </c>
       <c r="P56">
-        <v>-163.8477823420382</v>
+        <v>-120.0630703420382</v>
       </c>
       <c r="Q56">
-        <v>-75.94778234203824</v>
+        <v>-32.16307034203821</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.2266301039083972</v>
+        <v>0.2250547698781546</v>
       </c>
       <c r="T56">
-        <v>1.549055053212537</v>
+        <v>1.535457590779779</v>
       </c>
       <c r="U56">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V56">
-        <v>0.08783993838839965</v>
+        <v>0.103324272321214</v>
       </c>
       <c r="W56">
-        <v>0.2739008584866727</v>
+        <v>0.2289008584866726</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.4391996919419983</v>
+        <v>0.5166213616060698</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.2547010832626396</v>
+        <v>0.229226429608728</v>
       </c>
       <c r="C57">
-        <v>-138.3001305710752</v>
+        <v>3.531324514436164</v>
       </c>
       <c r="D57">
-        <v>1020.764869428925</v>
+        <v>1162.596324514436</v>
       </c>
       <c r="E57">
         <v>643.4650000000001</v>
@@ -5955,45 +5955,45 @@
         <v>160.4</v>
       </c>
       <c r="M57">
-        <v>371.9728710373172</v>
+        <v>316.2284460373172</v>
       </c>
       <c r="N57">
-        <v>-211.5728710373172</v>
+        <v>-155.8284460373171</v>
       </c>
       <c r="O57">
-        <v>-42.31457420746344</v>
+        <v>-31.16568920746343</v>
       </c>
       <c r="P57">
-        <v>-169.2582968298537</v>
+        <v>-124.6627568298537</v>
       </c>
       <c r="Q57">
-        <v>-81.35829682985374</v>
+        <v>-36.76275682985371</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.2306485506619171</v>
+        <v>0.2290382092087802</v>
       </c>
       <c r="T57">
-        <v>1.583478498839483</v>
+        <v>1.569578870574886</v>
       </c>
       <c r="U57">
-        <v>0.3002771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V57">
-        <v>0.08624284859951968</v>
+        <v>0.101445649188101</v>
       </c>
       <c r="W57">
-        <v>0.2743804281177763</v>
+        <v>0.2293804281177762</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.4312142429975984</v>
+        <v>0.507228245940505</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2572458551446134</v>
+        <v>0.2515087091838037</v>
       </c>
       <c r="C58">
-        <v>-173.1081372270478</v>
+        <v>-144.9236131199561</v>
       </c>
       <c r="D58">
-        <v>1008.479862772953</v>
+        <v>1036.664386880044</v>
       </c>
       <c r="E58">
         <v>665.9880000000003</v>
@@ -6037,37 +6037,37 @@
         <v>160.4</v>
       </c>
       <c r="M58">
-        <v>378.7360141470866</v>
+        <v>366.1231341470866</v>
       </c>
       <c r="N58">
-        <v>-218.3360141470866</v>
+        <v>-205.7231341470866</v>
       </c>
       <c r="O58">
-        <v>-43.66720282941733</v>
+        <v>-41.14462682941732</v>
       </c>
       <c r="P58">
-        <v>-174.6688113176693</v>
+        <v>-164.5785073176693</v>
       </c>
       <c r="Q58">
-        <v>-86.76881131766928</v>
+        <v>-76.67850731766927</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.2348496540860515</v>
+        <v>0.2345379587205752</v>
       </c>
       <c r="T58">
-        <v>1.61946664654038</v>
+        <v>1.616688535444686</v>
       </c>
       <c r="U58">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V58">
-        <v>0.08470279773167111</v>
+        <v>0.08762079477641574</v>
       </c>
       <c r="W58">
-        <v>0.2748428702620548</v>
+        <v>0.2648428702620548</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4235139886583554</v>
+        <v>0.4381039738820787</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2597906270265871</v>
+        <v>0.2539534810657775</v>
       </c>
       <c r="C59">
-        <v>-207.6239578191494</v>
+        <v>-179.6222823958738</v>
       </c>
       <c r="D59">
-        <v>996.4870421808507</v>
+        <v>1024.488717604126</v>
       </c>
       <c r="E59">
         <v>688.5110000000002</v>
@@ -6119,37 +6119,37 @@
         <v>160.4</v>
       </c>
       <c r="M59">
-        <v>385.499157256856</v>
+        <v>372.661047256856</v>
       </c>
       <c r="N59">
-        <v>-225.099157256856</v>
+        <v>-212.261047256856</v>
       </c>
       <c r="O59">
-        <v>-45.0198314513712</v>
+        <v>-42.4522094513712</v>
       </c>
       <c r="P59">
-        <v>-180.0793258054848</v>
+        <v>-169.8088378054848</v>
       </c>
       <c r="Q59">
-        <v>-92.17932580548478</v>
+        <v>-81.90883780548481</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.2392461576694482</v>
+        <v>0.2389272135745421</v>
       </c>
       <c r="T59">
-        <v>1.657128661576203</v>
+        <v>1.654285943245725</v>
       </c>
       <c r="U59">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V59">
-        <v>0.08321678373637864</v>
+        <v>0.0860835878505137</v>
       </c>
       <c r="W59">
-        <v>0.2752890863661832</v>
+        <v>0.2652890863661831</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4160839186818931</v>
+        <v>0.4304179392525684</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2623353989085608</v>
+        <v>0.2563982529477512</v>
       </c>
       <c r="C60">
-        <v>-241.8578938530486</v>
+        <v>-214.0382642945376</v>
       </c>
       <c r="D60">
-        <v>984.7761061469514</v>
+        <v>1012.595735705462</v>
       </c>
       <c r="E60">
         <v>711.0340000000001</v>
@@ -6201,37 +6201,37 @@
         <v>160.4</v>
       </c>
       <c r="M60">
-        <v>392.2623003666254</v>
+        <v>379.1989603666254</v>
       </c>
       <c r="N60">
-        <v>-231.8623003666254</v>
+        <v>-218.7989603666254</v>
       </c>
       <c r="O60">
-        <v>-46.37246007332507</v>
+        <v>-43.75979207332508</v>
       </c>
       <c r="P60">
-        <v>-185.4898402933003</v>
+        <v>-175.0391682933003</v>
       </c>
       <c r="Q60">
-        <v>-97.58984029330028</v>
+        <v>-87.13916829330029</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.2438520185663397</v>
+        <v>0.2435254805644121</v>
       </c>
       <c r="T60">
-        <v>1.696584105899445</v>
+        <v>1.693673703799194</v>
       </c>
       <c r="U60">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V60">
-        <v>0.08178201160299281</v>
+        <v>0.08459938805998761</v>
       </c>
       <c r="W60">
-        <v>0.2757199157081002</v>
+        <v>0.2657199157081002</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4089100580149639</v>
+        <v>0.4229969402999381</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2648801707905345</v>
+        <v>0.2588430248297249</v>
       </c>
       <c r="C61">
-        <v>-275.8197681971733</v>
+        <v>-248.1812907396081</v>
       </c>
       <c r="D61">
-        <v>973.3372318028266</v>
+        <v>1000.975709260392</v>
       </c>
       <c r="E61">
         <v>733.557</v>
@@ -6283,37 +6283,37 @@
         <v>160.4</v>
       </c>
       <c r="M61">
-        <v>399.0254434763947</v>
+        <v>385.7368734763947</v>
       </c>
       <c r="N61">
-        <v>-238.6254434763947</v>
+        <v>-225.3368734763947</v>
       </c>
       <c r="O61">
-        <v>-47.72508869527895</v>
+        <v>-45.06737469527895</v>
       </c>
       <c r="P61">
-        <v>-190.9003547811158</v>
+        <v>-180.2694987811158</v>
       </c>
       <c r="Q61">
-        <v>-103.0003547811158</v>
+        <v>-92.36949878111579</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.2486825556045431</v>
+        <v>0.2483480532611051</v>
       </c>
       <c r="T61">
-        <v>1.737964206043334</v>
+        <v>1.734982818526004</v>
       </c>
       <c r="U61">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V61">
-        <v>0.08039587581311158</v>
+        <v>0.08316550012676749</v>
       </c>
       <c r="W61">
-        <v>0.2761361406655455</v>
+        <v>0.2661361406655455</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4019793790655578</v>
+        <v>0.4158275006338374</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2674249426725083</v>
+        <v>0.2612877967116987</v>
       </c>
       <c r="C62">
-        <v>-309.5189525620808</v>
+        <v>-282.0606520086992</v>
       </c>
       <c r="D62">
-        <v>962.1610474379193</v>
+        <v>989.6193479913009</v>
       </c>
       <c r="E62">
         <v>756.0800000000002</v>
@@ -6365,37 +6365,37 @@
         <v>160.4</v>
       </c>
       <c r="M62">
-        <v>405.7885865861642</v>
+        <v>392.2747865861642</v>
       </c>
       <c r="N62">
-        <v>-245.3885865861642</v>
+        <v>-231.8747865861642</v>
       </c>
       <c r="O62">
-        <v>-49.07771731723285</v>
+        <v>-46.37495731723283</v>
       </c>
       <c r="P62">
-        <v>-196.3108692689314</v>
+        <v>-185.4998292689313</v>
       </c>
       <c r="Q62">
-        <v>-108.4108692689314</v>
+        <v>-97.59982926893133</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2537546194946567</v>
+        <v>0.2534117545926327</v>
       </c>
       <c r="T62">
-        <v>1.781413311194417</v>
+        <v>1.778357388989154</v>
       </c>
       <c r="U62">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V62">
-        <v>0.07905594454955969</v>
+        <v>0.08177940845798803</v>
       </c>
       <c r="W62">
-        <v>0.2765384914577426</v>
+        <v>0.2665384914577426</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3952797227477984</v>
+        <v>0.4088970422899402</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2699697145544819</v>
+        <v>0.2637325685936724</v>
       </c>
       <c r="C63">
-        <v>-342.9643931081487</v>
+        <v>-315.6852215053502</v>
       </c>
       <c r="D63">
-        <v>951.2386068918513</v>
+        <v>978.5177784946497</v>
       </c>
       <c r="E63">
         <v>778.6030000000001</v>
@@ -6447,37 +6447,37 @@
         <v>160.4</v>
       </c>
       <c r="M63">
-        <v>412.5517296959336</v>
+        <v>398.8126996959336</v>
       </c>
       <c r="N63">
-        <v>-252.1517296959336</v>
+        <v>-238.4126996959336</v>
       </c>
       <c r="O63">
-        <v>-50.43034593918672</v>
+        <v>-47.68253993918672</v>
       </c>
       <c r="P63">
-        <v>-201.7213837567469</v>
+        <v>-190.7301597567469</v>
       </c>
       <c r="Q63">
-        <v>-113.8213837567469</v>
+        <v>-102.8301597567469</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2590867892252889</v>
+        <v>0.2587351329155207</v>
       </c>
       <c r="T63">
-        <v>1.827090575584018</v>
+        <v>1.823956296399132</v>
       </c>
       <c r="U63">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V63">
-        <v>0.07775994545858332</v>
+        <v>0.08043876241769314</v>
       </c>
       <c r="W63">
-        <v>0.2769276504206873</v>
+        <v>0.2669276504206873</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3887997272929166</v>
+        <v>0.4021938120884657</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2725144864364557</v>
+        <v>0.2661773404756461</v>
       </c>
       <c r="C64">
-        <v>-376.1646343286599</v>
+        <v>-349.0634788821383</v>
       </c>
       <c r="D64">
-        <v>940.5613656713402</v>
+        <v>967.662521117862</v>
       </c>
       <c r="E64">
         <v>801.1260000000002</v>
@@ -6529,37 +6529,37 @@
         <v>160.4</v>
       </c>
       <c r="M64">
-        <v>419.314872805703</v>
+        <v>405.350612805703</v>
       </c>
       <c r="N64">
-        <v>-258.914872805703</v>
+        <v>-244.950612805703</v>
       </c>
       <c r="O64">
-        <v>-51.78297456114061</v>
+        <v>-48.9901225611406</v>
       </c>
       <c r="P64">
-        <v>-207.1318982445624</v>
+        <v>-195.9604902445624</v>
       </c>
       <c r="Q64">
-        <v>-119.2318982445624</v>
+        <v>-108.0604902445624</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2646995994680597</v>
+        <v>0.2643386890448766</v>
       </c>
       <c r="T64">
-        <v>1.87517190652044</v>
+        <v>1.871955146304373</v>
       </c>
       <c r="U64">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V64">
-        <v>0.07650575278989648</v>
+        <v>0.07914136302385938</v>
       </c>
       <c r="W64">
-        <v>0.2773042558686984</v>
+        <v>0.2673042558686984</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3825287639494824</v>
+        <v>0.3957068151192968</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2750592583184294</v>
+        <v>0.2686221123576198</v>
       </c>
       <c r="C65">
-        <v>-409.1278413422701</v>
+        <v>-382.203531641569</v>
       </c>
       <c r="D65">
-        <v>930.1211586577299</v>
+        <v>957.045468358431</v>
       </c>
       <c r="E65">
         <v>823.6490000000001</v>
@@ -6611,37 +6611,37 @@
         <v>160.4</v>
       </c>
       <c r="M65">
-        <v>426.0780159154724</v>
+        <v>411.8885259154724</v>
       </c>
       <c r="N65">
-        <v>-265.6780159154724</v>
+        <v>-251.4885259154724</v>
       </c>
       <c r="O65">
-        <v>-53.13560318309449</v>
+        <v>-50.29770518309448</v>
       </c>
       <c r="P65">
-        <v>-212.542412732378</v>
+        <v>-201.1908207323779</v>
       </c>
       <c r="Q65">
-        <v>-124.6424127323779</v>
+        <v>-113.2908207323779</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2706158048590883</v>
+        <v>0.2702451401001434</v>
       </c>
       <c r="T65">
-        <v>1.925852228318289</v>
+        <v>1.922548528636923</v>
       </c>
       <c r="U65">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V65">
-        <v>0.07529137576148542</v>
+        <v>0.07788515091236956</v>
       </c>
       <c r="W65">
-        <v>0.2776689055882011</v>
+        <v>0.2676689055882011</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3764568788074271</v>
+        <v>0.3894257545618477</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2776040302004031</v>
+        <v>0.2710668842395935</v>
       </c>
       <c r="C66">
-        <v>-441.8618207171099</v>
+        <v>-415.1131353303942</v>
       </c>
       <c r="D66">
-        <v>919.9101792828902</v>
+        <v>946.658864669606</v>
       </c>
       <c r="E66">
         <v>846.1720000000003</v>
@@ -6693,37 +6693,37 @@
         <v>160.4</v>
       </c>
       <c r="M66">
-        <v>432.8411590252418</v>
+        <v>418.4264390252418</v>
       </c>
       <c r="N66">
-        <v>-272.4411590252419</v>
+        <v>-258.0264390252419</v>
       </c>
       <c r="O66">
-        <v>-54.48823180504837</v>
+        <v>-51.60528780504838</v>
       </c>
       <c r="P66">
-        <v>-217.9529272201935</v>
+        <v>-206.4211512201935</v>
       </c>
       <c r="Q66">
-        <v>-130.0529272201935</v>
+        <v>-118.5211512201935</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2768606883273964</v>
+        <v>0.2764797273251475</v>
       </c>
       <c r="T66">
-        <v>1.979348123549353</v>
+        <v>1.975952654432394</v>
       </c>
       <c r="U66">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V66">
-        <v>0.07411494801521222</v>
+        <v>0.07666819542936376</v>
       </c>
       <c r="W66">
-        <v>0.2780221600039694</v>
+        <v>0.2680221600039694</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3705747400760609</v>
+        <v>0.3833409771468187</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2801488020823769</v>
+        <v>0.2735116561215672</v>
       </c>
       <c r="C67">
-        <v>-474.3740399381138</v>
+        <v>-447.7997124330516</v>
       </c>
       <c r="D67">
-        <v>909.9209600618863</v>
+        <v>936.4952875669485</v>
       </c>
       <c r="E67">
         <v>868.6950000000002</v>
@@ -6775,37 +6775,37 @@
         <v>160.4</v>
       </c>
       <c r="M67">
-        <v>439.6043021350112</v>
+        <v>424.9643521350112</v>
       </c>
       <c r="N67">
-        <v>-279.2043021350112</v>
+        <v>-264.5643521350112</v>
       </c>
       <c r="O67">
-        <v>-55.84086042700224</v>
+        <v>-52.91287042700224</v>
       </c>
       <c r="P67">
-        <v>-223.3634417080089</v>
+        <v>-211.6514817080089</v>
       </c>
       <c r="Q67">
-        <v>-135.4634417080089</v>
+        <v>-123.7514817080089</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2834624222796077</v>
+        <v>0.2830705766772946</v>
       </c>
       <c r="T67">
-        <v>2.035900927079335</v>
+        <v>2.032408444559034</v>
       </c>
       <c r="U67">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V67">
-        <v>0.07297471804574741</v>
+        <v>0.07548868473045049</v>
       </c>
       <c r="W67">
-        <v>0.2783645450530987</v>
+        <v>0.2683645450530986</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3648735902287371</v>
+        <v>0.3774434236522525</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2826935739643506</v>
+        <v>0.2759564280035409</v>
       </c>
       <c r="C68">
-        <v>-506.6716456196191</v>
+        <v>-480.2703700609731</v>
       </c>
       <c r="D68">
-        <v>900.1463543803811</v>
+        <v>926.5476299390272</v>
       </c>
       <c r="E68">
         <v>891.2180000000003</v>
@@ -6857,37 +6857,37 @@
         <v>160.4</v>
       </c>
       <c r="M68">
-        <v>446.3674452447806</v>
+        <v>431.5022652447806</v>
       </c>
       <c r="N68">
-        <v>-285.9674452447806</v>
+        <v>-271.1022652447806</v>
       </c>
       <c r="O68">
-        <v>-57.19348904895612</v>
+        <v>-54.22045304895612</v>
       </c>
       <c r="P68">
-        <v>-228.7739561958245</v>
+        <v>-216.8818121958245</v>
       </c>
       <c r="Q68">
-        <v>-140.8739561958245</v>
+        <v>-128.9818121958245</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2904524935231256</v>
+        <v>0.2900491230501561</v>
       </c>
       <c r="T68">
-        <v>2.09578036611108</v>
+        <v>2.092185163516652</v>
       </c>
       <c r="U68">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V68">
-        <v>0.07186904049959973</v>
+        <v>0.0743449167799891</v>
       </c>
       <c r="W68">
-        <v>0.2786965547977089</v>
+        <v>0.2686965547977089</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3593452024979987</v>
+        <v>0.3717245838999456</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2852383458463242</v>
+        <v>0.2784011998855147</v>
       </c>
       <c r="C69">
-        <v>-538.7614805565696</v>
+        <v>-512.5319165263365</v>
       </c>
       <c r="D69">
-        <v>890.5795194434305</v>
+        <v>916.8090834736636</v>
       </c>
       <c r="E69">
         <v>913.7410000000002</v>
@@ -6939,37 +6939,37 @@
         <v>160.4</v>
       </c>
       <c r="M69">
-        <v>453.13058835455</v>
+        <v>438.0401783545501</v>
       </c>
       <c r="N69">
-        <v>-292.73058835455</v>
+        <v>-277.64017835455</v>
       </c>
       <c r="O69">
-        <v>-58.54611767091001</v>
+        <v>-55.52803567091001</v>
       </c>
       <c r="P69">
-        <v>-234.18447068364</v>
+        <v>-222.11214268364</v>
       </c>
       <c r="Q69">
-        <v>-146.28447068364</v>
+        <v>-134.21214268364</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2978662054480687</v>
+        <v>0.2974506116274337</v>
       </c>
       <c r="T69">
-        <v>2.15928886205384</v>
+        <v>2.155584713926248</v>
       </c>
       <c r="U69">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V69">
-        <v>0.07079636825333706</v>
+        <v>0.07323529115640719</v>
       </c>
       <c r="W69">
-        <v>0.279018653803674</v>
+        <v>0.269018653803674</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3539818412666852</v>
+        <v>0.3661764557820359</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.287783117728298</v>
+        <v>0.2808459717674884</v>
       </c>
       <c r="C70">
-        <v>-570.6500996998277</v>
+        <v>-544.590876881495</v>
       </c>
       <c r="D70">
-        <v>881.2139003001726</v>
+        <v>907.2731231185053</v>
       </c>
       <c r="E70">
         <v>936.2640000000004</v>
@@ -7021,37 +7021,37 @@
         <v>160.4</v>
       </c>
       <c r="M70">
-        <v>459.8937314643195</v>
+        <v>444.5780914643195</v>
       </c>
       <c r="N70">
-        <v>-299.4937314643195</v>
+        <v>-284.1780914643194</v>
       </c>
       <c r="O70">
-        <v>-59.8987462928639</v>
+        <v>-56.83561829286389</v>
       </c>
       <c r="P70">
-        <v>-239.5949851714556</v>
+        <v>-227.3424731714555</v>
       </c>
       <c r="Q70">
-        <v>-151.6949851714556</v>
+        <v>-139.4424731714555</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.3057432743683209</v>
+        <v>0.305314693240791</v>
       </c>
       <c r="T70">
-        <v>2.226766638993023</v>
+        <v>2.222946736236443</v>
       </c>
       <c r="U70">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V70">
-        <v>0.06975524519078796</v>
+        <v>0.07215830158057766</v>
       </c>
       <c r="W70">
-        <v>0.2793312793094637</v>
+        <v>0.2693312793094637</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3487762259539399</v>
+        <v>0.3607915079028884</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2903278896102717</v>
+        <v>0.2832907436494622</v>
       </c>
       <c r="C71">
-        <v>-602.3437851339608</v>
+        <v>-576.453507498613</v>
       </c>
       <c r="D71">
-        <v>872.0432148660394</v>
+        <v>897.9334925013871</v>
       </c>
       <c r="E71">
         <v>958.7870000000003</v>
@@ -7103,37 +7103,37 @@
         <v>160.4</v>
       </c>
       <c r="M71">
-        <v>466.6568745740889</v>
+        <v>451.1160045740888</v>
       </c>
       <c r="N71">
-        <v>-306.2568745740889</v>
+        <v>-290.7160045740889</v>
       </c>
       <c r="O71">
-        <v>-61.25137491481778</v>
+        <v>-58.14320091481778</v>
       </c>
       <c r="P71">
-        <v>-245.0054996592711</v>
+        <v>-232.5728036592711</v>
       </c>
       <c r="Q71">
-        <v>-157.1054996592711</v>
+        <v>-144.6728036592711</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.3141285412834281</v>
+        <v>0.3136861349582359</v>
       </c>
       <c r="T71">
-        <v>2.298597820896023</v>
+        <v>2.294654695469877</v>
       </c>
       <c r="U71">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V71">
-        <v>0.06874429960831278</v>
+        <v>0.07111252909390263</v>
       </c>
       <c r="W71">
-        <v>0.2796348432063899</v>
+        <v>0.2696348432063899</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3437214980415638</v>
+        <v>0.3555626454695131</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2928726614922454</v>
+        <v>0.2857355155314358</v>
       </c>
       <c r="C72">
-        <v>-633.8485601294382</v>
+        <v>-608.1258097579621</v>
       </c>
       <c r="D72">
-        <v>863.0614398705621</v>
+        <v>888.7841902420382</v>
       </c>
       <c r="E72">
         <v>981.3100000000004</v>
@@ -7185,37 +7185,37 @@
         <v>160.4</v>
       </c>
       <c r="M72">
-        <v>473.4200176838583</v>
+        <v>457.6539176838583</v>
       </c>
       <c r="N72">
-        <v>-313.0200176838583</v>
+        <v>-297.2539176838583</v>
       </c>
       <c r="O72">
-        <v>-62.60400353677167</v>
+        <v>-59.45078353677166</v>
       </c>
       <c r="P72">
-        <v>-250.4160141470867</v>
+        <v>-237.8031341470866</v>
       </c>
       <c r="Q72">
-        <v>-162.5160141470867</v>
+        <v>-149.9031341470866</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.3230728259928756</v>
+        <v>0.3226156727901771</v>
       </c>
       <c r="T72">
-        <v>2.375217748259224</v>
+        <v>2.371143185318873</v>
       </c>
       <c r="U72">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V72">
-        <v>0.06776223818533687</v>
+        <v>0.07009663582113258</v>
       </c>
       <c r="W72">
-        <v>0.2799297338491182</v>
+        <v>0.2699297338491182</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3388111909266843</v>
+        <v>0.350483179105663</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2954174333742191</v>
+        <v>0.2881802874134095</v>
       </c>
       <c r="C73">
-        <v>-665.1702023352717</v>
+        <v>-639.6135429078171</v>
       </c>
       <c r="D73">
-        <v>854.2627976647283</v>
+        <v>879.8194570921829</v>
       </c>
       <c r="E73">
         <v>1003.833</v>
@@ -7267,37 +7267,37 @@
         <v>160.4</v>
       </c>
       <c r="M73">
-        <v>480.1831607936276</v>
+        <v>464.1918307936276</v>
       </c>
       <c r="N73">
-        <v>-319.7831607936276</v>
+        <v>-303.7918307936276</v>
       </c>
       <c r="O73">
-        <v>-63.95663215872553</v>
+        <v>-60.75836615872552</v>
       </c>
       <c r="P73">
-        <v>-255.8265286349021</v>
+        <v>-243.0334646349021</v>
       </c>
       <c r="Q73">
-        <v>-167.9265286349021</v>
+        <v>-155.1334646349021</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.3326339579236644</v>
+        <v>0.3321610408174245</v>
       </c>
       <c r="T73">
-        <v>2.457121808544024</v>
+        <v>2.452906743433316</v>
       </c>
       <c r="U73">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V73">
-        <v>0.06680784046441665</v>
+        <v>0.06910935926027156</v>
       </c>
       <c r="W73">
-        <v>0.2802163177131781</v>
+        <v>0.2702163177131781</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3340392023220832</v>
+        <v>0.3455467963013579</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2979622052561929</v>
+        <v>0.2906250592953832</v>
       </c>
       <c r="C74">
-        <v>-696.3142561728395</v>
+        <v>-670.9222361538555</v>
       </c>
       <c r="D74">
-        <v>845.6417438271607</v>
+        <v>871.0337638461447</v>
       </c>
       <c r="E74">
         <v>1026.356</v>
@@ -7349,37 +7349,37 @@
         <v>160.4</v>
       </c>
       <c r="M74">
-        <v>486.9463039033971</v>
+        <v>470.729743903397</v>
       </c>
       <c r="N74">
-        <v>-326.5463039033971</v>
+        <v>-310.329743903397</v>
       </c>
       <c r="O74">
-        <v>-65.30926078067942</v>
+        <v>-62.06594878067941</v>
       </c>
       <c r="P74">
-        <v>-261.2370431227176</v>
+        <v>-248.2637951227176</v>
       </c>
       <c r="Q74">
-        <v>-173.3370431227176</v>
+        <v>-160.3637951227176</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.3428780278495096</v>
+        <v>0.3423882208466182</v>
       </c>
       <c r="T74">
-        <v>2.544876158849168</v>
+        <v>2.540510555698792</v>
       </c>
       <c r="U74">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V74">
-        <v>0.06587995379129975</v>
+        <v>0.06814950704832334</v>
       </c>
       <c r="W74">
-        <v>0.2804949409143475</v>
+        <v>0.2704949409143474</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3293997689564987</v>
+        <v>0.3407475352416168</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.3005069771381665</v>
+        <v>0.293069831177357</v>
       </c>
       <c r="C75">
-        <v>-727.2860444867428</v>
+        <v>-702.0572000313791</v>
       </c>
       <c r="D75">
-        <v>837.1929555132573</v>
+        <v>862.4217999686209</v>
       </c>
       <c r="E75">
         <v>1048.879</v>
@@ -7431,37 +7431,37 @@
         <v>160.4</v>
       </c>
       <c r="M75">
-        <v>493.7094470131664</v>
+        <v>477.2676570131664</v>
       </c>
       <c r="N75">
-        <v>-333.3094470131664</v>
+        <v>-316.8676570131664</v>
       </c>
       <c r="O75">
-        <v>-66.66188940263328</v>
+        <v>-63.37353140263329</v>
       </c>
       <c r="P75">
-        <v>-266.6475576105331</v>
+        <v>-253.4941256105331</v>
       </c>
       <c r="Q75">
-        <v>-178.7475576105331</v>
+        <v>-165.5941256105331</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.3538809177698617</v>
+        <v>0.3533729697668633</v>
       </c>
       <c r="T75">
-        <v>2.639130831399137</v>
+        <v>2.634603539243191</v>
       </c>
       <c r="U75">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V75">
-        <v>0.06497748867087098</v>
+        <v>0.06721595215725044</v>
       </c>
       <c r="W75">
-        <v>0.280765930603156</v>
+        <v>0.270765930603156</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.324887443354355</v>
+        <v>0.3360797607862521</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.3030517490201403</v>
+        <v>0.2955146030593306</v>
       </c>
       <c r="C76">
-        <v>-758.0906795041585</v>
+        <v>-733.0235371095216</v>
       </c>
       <c r="D76">
-        <v>828.9113204958417</v>
+        <v>853.9784628904786</v>
       </c>
       <c r="E76">
         <v>1071.402</v>
@@ -7513,37 +7513,37 @@
         <v>160.4</v>
       </c>
       <c r="M76">
-        <v>500.4725901229359</v>
+        <v>483.8055701229359</v>
       </c>
       <c r="N76">
-        <v>-340.0725901229358</v>
+        <v>-323.4055701229358</v>
       </c>
       <c r="O76">
-        <v>-68.01451802458716</v>
+        <v>-64.68111402458717</v>
       </c>
       <c r="P76">
-        <v>-272.0580720983486</v>
+        <v>-258.7244560983487</v>
       </c>
       <c r="Q76">
-        <v>-184.1580720983486</v>
+        <v>-170.8244560983487</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.3657301838379334</v>
+        <v>0.3652026993732811</v>
       </c>
       <c r="T76">
-        <v>2.740635863376027</v>
+        <v>2.735934444598699</v>
       </c>
       <c r="U76">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V76">
-        <v>0.064099414499643</v>
+        <v>0.06630762847944975</v>
       </c>
       <c r="W76">
-        <v>0.2810295962463211</v>
+        <v>0.2710295962463211</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.320497072498215</v>
+        <v>0.3315381423972488</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.305596520902114</v>
+        <v>0.2979593749413044</v>
       </c>
       <c r="C77">
-        <v>-788.7330731500891</v>
+        <v>-763.8261520727636</v>
       </c>
       <c r="D77">
-        <v>820.791926849911</v>
+        <v>845.6988479272364</v>
       </c>
       <c r="E77">
         <v>1093.925</v>
@@ -7595,37 +7595,37 @@
         <v>160.4</v>
       </c>
       <c r="M77">
-        <v>507.2357332327052</v>
+        <v>490.3434832327052</v>
       </c>
       <c r="N77">
-        <v>-346.8357332327053</v>
+        <v>-329.9434832327053</v>
       </c>
       <c r="O77">
-        <v>-69.36714664654106</v>
+        <v>-65.98869664654106</v>
       </c>
       <c r="P77">
-        <v>-277.4685865861642</v>
+        <v>-263.9547865861642</v>
       </c>
       <c r="Q77">
-        <v>-189.5685865861642</v>
+        <v>-176.0547865861642</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.3785273911914507</v>
+        <v>0.3779788073482124</v>
       </c>
       <c r="T77">
-        <v>2.850261297911068</v>
+        <v>2.845371822382647</v>
       </c>
       <c r="U77">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V77">
-        <v>0.06324475563964777</v>
+        <v>0.06542352676639042</v>
       </c>
       <c r="W77">
-        <v>0.2812862308056684</v>
+        <v>0.2712862308056684</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3162237781982388</v>
+        <v>0.327117633831952</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.3081412927840877</v>
+        <v>0.3004041468232781</v>
       </c>
       <c r="C78">
-        <v>-819.2179467622532</v>
+        <v>-794.4697612216207</v>
       </c>
       <c r="D78">
-        <v>812.8300532377468</v>
+        <v>837.5782387783793</v>
       </c>
       <c r="E78">
         <v>1116.448</v>
@@ -7677,37 +7677,37 @@
         <v>160.4</v>
       </c>
       <c r="M78">
-        <v>513.9988763424747</v>
+        <v>496.8813963424746</v>
       </c>
       <c r="N78">
-        <v>-353.5988763424747</v>
+        <v>-336.4813963424746</v>
       </c>
       <c r="O78">
-        <v>-70.71977526849494</v>
+        <v>-67.29627926849491</v>
       </c>
       <c r="P78">
-        <v>-282.8791010739798</v>
+        <v>-269.1851170739797</v>
       </c>
       <c r="Q78">
-        <v>-194.9791010739798</v>
+        <v>-181.2851170739796</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3923910324910945</v>
+        <v>0.3918195909877212</v>
       </c>
       <c r="T78">
-        <v>2.969022185324029</v>
+        <v>2.963928981648591</v>
       </c>
       <c r="U78">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V78">
-        <v>0.06241258780228397</v>
+        <v>0.06456269088788529</v>
       </c>
       <c r="W78">
-        <v>0.2815361118239803</v>
+        <v>0.2715361118239803</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3120629390114198</v>
+        <v>0.3228134544394264</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.3106860646660614</v>
+        <v>0.3028489187052519</v>
       </c>
       <c r="C79">
-        <v>-849.5498402459867</v>
+        <v>-824.9589014311678</v>
       </c>
       <c r="D79">
-        <v>805.0211597540134</v>
+        <v>829.6120985688324</v>
       </c>
       <c r="E79">
         <v>1138.971</v>
@@ -7759,37 +7759,37 @@
         <v>160.4</v>
       </c>
       <c r="M79">
-        <v>520.7620194522441</v>
+        <v>503.4193094522441</v>
       </c>
       <c r="N79">
-        <v>-360.3620194522441</v>
+        <v>-343.0193094522441</v>
       </c>
       <c r="O79">
-        <v>-72.07240389044883</v>
+        <v>-68.60386189044883</v>
       </c>
       <c r="P79">
-        <v>-288.2896155617953</v>
+        <v>-274.4154475617953</v>
       </c>
       <c r="Q79">
-        <v>-200.3896155617953</v>
+        <v>-186.5154475617953</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.4074602078167943</v>
+        <v>0.4068639210306657</v>
       </c>
       <c r="T79">
-        <v>3.098110106425074</v>
+        <v>3.092795459111573</v>
       </c>
       <c r="U79">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V79">
-        <v>0.06160203471394263</v>
+        <v>0.0637242143828478</v>
       </c>
       <c r="W79">
-        <v>0.2817795024262321</v>
+        <v>0.2717795024262321</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3080101735697131</v>
+        <v>0.3186210719142389</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.3132308365480351</v>
+        <v>0.3052936905872256</v>
       </c>
       <c r="C80">
-        <v>-879.7331207064561</v>
+        <v>-855.2979386031562</v>
       </c>
       <c r="D80">
-        <v>797.3608792935439</v>
+        <v>821.7960613968438</v>
       </c>
       <c r="E80">
         <v>1161.494</v>
@@ -7841,37 +7841,37 @@
         <v>160.4</v>
       </c>
       <c r="M80">
-        <v>527.5251625620134</v>
+        <v>509.9572225620134</v>
       </c>
       <c r="N80">
-        <v>-367.1251625620134</v>
+        <v>-349.5572225620134</v>
       </c>
       <c r="O80">
-        <v>-73.42503251240269</v>
+        <v>-69.91144451240268</v>
       </c>
       <c r="P80">
-        <v>-293.7001300496107</v>
+        <v>-279.6457780496107</v>
       </c>
       <c r="Q80">
-        <v>-205.8001300496107</v>
+        <v>-191.7457780496107</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.4238993081721031</v>
+        <v>0.4232759174411505</v>
       </c>
       <c r="T80">
-        <v>3.238933293080759</v>
+        <v>3.233377070889372</v>
       </c>
       <c r="U80">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V80">
-        <v>0.06081226503812285</v>
+        <v>0.06290723727537541</v>
       </c>
       <c r="W80">
-        <v>0.2820166522438108</v>
+        <v>0.2720166522438108</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3040613251906142</v>
+        <v>0.3145361863768771</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.3157756084300089</v>
+        <v>0.3077384624691992</v>
       </c>
       <c r="C81">
-        <v>-909.7719905926726</v>
+        <v>-885.4910756448136</v>
       </c>
       <c r="D81">
-        <v>789.8450094073276</v>
+        <v>814.1259243551866</v>
       </c>
       <c r="E81">
         <v>1184.017</v>
@@ -7923,37 +7923,37 @@
         <v>160.4</v>
       </c>
       <c r="M81">
-        <v>534.288305671783</v>
+        <v>516.4951356717829</v>
       </c>
       <c r="N81">
-        <v>-373.888305671783</v>
+        <v>-356.0951356717829</v>
       </c>
       <c r="O81">
-        <v>-74.77766113435659</v>
+        <v>-71.21902713435659</v>
       </c>
       <c r="P81">
-        <v>-299.1106445374264</v>
+        <v>-284.8761085374264</v>
       </c>
       <c r="Q81">
-        <v>-211.2106445374264</v>
+        <v>-196.9761085374264</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.4419040371326796</v>
+        <v>0.4412509611288243</v>
       </c>
       <c r="T81">
-        <v>3.393168211798891</v>
+        <v>3.387347407598389</v>
       </c>
       <c r="U81">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V81">
-        <v>0.06004248953131115</v>
+        <v>0.06211094313264912</v>
       </c>
       <c r="W81">
-        <v>0.2822477982685395</v>
+        <v>0.2722477982685395</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3002124476565557</v>
+        <v>0.3105547156632456</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.3183203803119826</v>
+        <v>0.310183234351173</v>
       </c>
       <c r="C82">
-        <v>-939.6704953852169</v>
+        <v>-915.5423600049547</v>
       </c>
       <c r="D82">
-        <v>782.4695046147832</v>
+        <v>806.5976399950454</v>
       </c>
       <c r="E82">
         <v>1206.54</v>
@@ -8005,37 +8005,37 @@
         <v>160.4</v>
       </c>
       <c r="M82">
-        <v>541.0514487815523</v>
+        <v>523.0330487815522</v>
       </c>
       <c r="N82">
-        <v>-380.6514487815523</v>
+        <v>-362.6330487815522</v>
       </c>
       <c r="O82">
-        <v>-76.13028975631046</v>
+        <v>-72.52660975631045</v>
       </c>
       <c r="P82">
-        <v>-304.5211590252418</v>
+        <v>-290.1064390252418</v>
       </c>
       <c r="Q82">
-        <v>-216.6211590252418</v>
+        <v>-202.2064390252418</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.4617092389893135</v>
+        <v>0.4610235091852656</v>
       </c>
       <c r="T82">
-        <v>3.562826622388836</v>
+        <v>3.556714777978309</v>
       </c>
       <c r="U82">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V82">
-        <v>0.05929195841216978</v>
+        <v>0.06133455634349103</v>
       </c>
       <c r="W82">
-        <v>0.2824731656426498</v>
+        <v>0.2724731656426498</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2964597920608488</v>
+        <v>0.306672781717455</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3208651521939563</v>
+        <v>0.3126280062331467</v>
       </c>
       <c r="C83">
-        <v>-969.4325308572261</v>
+        <v>-945.4556907958058</v>
       </c>
       <c r="D83">
-        <v>775.2304691427742</v>
+        <v>799.2073092041944</v>
       </c>
       <c r="E83">
         <v>1229.063</v>
@@ -8087,37 +8087,37 @@
         <v>160.4</v>
       </c>
       <c r="M83">
-        <v>547.8145918913217</v>
+        <v>529.5709618913216</v>
       </c>
       <c r="N83">
-        <v>-387.4145918913217</v>
+        <v>-369.1709618913217</v>
       </c>
       <c r="O83">
-        <v>-77.48291837826434</v>
+        <v>-73.83419237826433</v>
       </c>
       <c r="P83">
-        <v>-309.9316735130574</v>
+        <v>-295.3367695130573</v>
       </c>
       <c r="Q83">
-        <v>-222.0316735130574</v>
+        <v>-207.4367695130573</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.4835991989361195</v>
+        <v>0.4828773780897532</v>
       </c>
       <c r="T83">
-        <v>3.75034381304088</v>
+        <v>3.743910292608747</v>
       </c>
       <c r="U83">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V83">
-        <v>0.05855995892559978</v>
+        <v>0.06057733959850965</v>
       </c>
       <c r="W83">
-        <v>0.2826929683902391</v>
+        <v>0.272692968390239</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2927997946279988</v>
+        <v>0.3028866979925482</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.32340992407593</v>
+        <v>0.3150727781151205</v>
       </c>
       <c r="C84">
-        <v>-999.0618499360215</v>
+        <v>-975.2348255268664</v>
       </c>
       <c r="D84">
-        <v>768.1241500639786</v>
+        <v>791.9511744731337</v>
       </c>
       <c r="E84">
         <v>1251.586</v>
@@ -8169,37 +8169,37 @@
         <v>160.4</v>
       </c>
       <c r="M84">
-        <v>554.5777350010911</v>
+        <v>536.1088750010911</v>
       </c>
       <c r="N84">
-        <v>-394.1777350010912</v>
+        <v>-375.7088750010911</v>
       </c>
       <c r="O84">
-        <v>-78.83554700021824</v>
+        <v>-75.14177500021822</v>
       </c>
       <c r="P84">
-        <v>-315.3421880008729</v>
+        <v>-300.5671000008729</v>
       </c>
       <c r="Q84">
-        <v>-227.4421880008729</v>
+        <v>-212.6671000008729</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.5079213766547929</v>
+        <v>0.5071594546502951</v>
       </c>
       <c r="T84">
-        <v>3.958696247098707</v>
+        <v>3.951905308864788</v>
       </c>
       <c r="U84">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V84">
-        <v>0.05784581308504368</v>
+        <v>0.05983859155462538</v>
       </c>
       <c r="W84">
-        <v>0.282907410095204</v>
+        <v>0.2729074100952041</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2892290654252183</v>
+        <v>0.2991929577731268</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3259546959579037</v>
+        <v>0.3175175499970941</v>
       </c>
       <c r="C85">
-        <v>-1028.562069190778</v>
+        <v>-1004.883386475243</v>
       </c>
       <c r="D85">
-        <v>761.1469308092226</v>
+        <v>784.8256135247568</v>
       </c>
       <c r="E85">
         <v>1274.109</v>
@@ -8251,37 +8251,37 @@
         <v>160.4</v>
       </c>
       <c r="M85">
-        <v>561.3408781108606</v>
+        <v>542.6467881108605</v>
       </c>
       <c r="N85">
-        <v>-400.9408781108606</v>
+        <v>-382.2467881108605</v>
       </c>
       <c r="O85">
-        <v>-80.18817562217212</v>
+        <v>-76.4493576221721</v>
       </c>
       <c r="P85">
-        <v>-320.7527024886884</v>
+        <v>-305.7974304886884</v>
       </c>
       <c r="Q85">
-        <v>-232.8527024886884</v>
+        <v>-217.8974304886884</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.5351049870462513</v>
+        <v>0.5342982461003125</v>
       </c>
       <c r="T85">
-        <v>4.191560732222161</v>
+        <v>4.184370327033306</v>
       </c>
       <c r="U85">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V85">
-        <v>0.05714887557799495</v>
+        <v>0.05911764466842508</v>
       </c>
       <c r="W85">
-        <v>0.2831166845301699</v>
+        <v>0.2731166845301699</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2857443778899748</v>
+        <v>0.2955882233421253</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.3284994678398774</v>
+        <v>0.3199623218790678</v>
       </c>
       <c r="C86">
-        <v>-1057.936674969784</v>
+        <v>-1034.404866715152</v>
       </c>
       <c r="D86">
-        <v>754.2953250302157</v>
+        <v>777.8271332848483</v>
       </c>
       <c r="E86">
         <v>1296.632</v>
@@ -8333,37 +8333,37 @@
         <v>160.4</v>
       </c>
       <c r="M86">
-        <v>568.1040212206299</v>
+        <v>549.1847012206298</v>
       </c>
       <c r="N86">
-        <v>-407.7040212206299</v>
+        <v>-388.7847012206298</v>
       </c>
       <c r="O86">
-        <v>-81.54080424412598</v>
+        <v>-77.75694024412597</v>
       </c>
       <c r="P86">
-        <v>-326.1632169765039</v>
+        <v>-311.0277609765038</v>
       </c>
       <c r="Q86">
-        <v>-238.2632169765039</v>
+        <v>-223.1277609765038</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.5656865487366417</v>
+        <v>0.5648293864815817</v>
       </c>
       <c r="T86">
-        <v>4.453533277986043</v>
+        <v>4.445893472472885</v>
       </c>
       <c r="U86">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V86">
-        <v>0.05646853182111407</v>
+        <v>0.05841386318427717</v>
       </c>
       <c r="W86">
-        <v>0.2833209762404937</v>
+        <v>0.2733209762404937</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2823426591055703</v>
+        <v>0.2920693159213857</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.3310442397218512</v>
+        <v>0.3224070937610416</v>
       </c>
       <c r="C87">
-        <v>-1087.1890292092</v>
+        <v>-1063.802635827667</v>
       </c>
       <c r="D87">
-        <v>747.5659707908</v>
+        <v>770.952364172333</v>
       </c>
       <c r="E87">
         <v>1319.155</v>
@@ -8415,37 +8415,37 @@
         <v>160.4</v>
       </c>
       <c r="M87">
-        <v>574.8671643303993</v>
+        <v>555.7226143303993</v>
       </c>
       <c r="N87">
-        <v>-414.4671643303993</v>
+        <v>-395.3226143303993</v>
       </c>
       <c r="O87">
-        <v>-82.89343286607988</v>
+        <v>-79.06452286607987</v>
       </c>
       <c r="P87">
-        <v>-331.5737314643195</v>
+        <v>-316.2580914643195</v>
       </c>
       <c r="Q87">
-        <v>-243.6737314643194</v>
+        <v>-228.3580914643195</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.6003456519857512</v>
+        <v>0.5994313455803539</v>
       </c>
       <c r="T87">
-        <v>4.750435496518447</v>
+        <v>4.742286370637744</v>
       </c>
       <c r="U87">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V87">
-        <v>0.05580419615263037</v>
+        <v>0.05772664126446213</v>
       </c>
       <c r="W87">
-        <v>0.2835204610870453</v>
+        <v>0.2735204610870453</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2790209807631518</v>
+        <v>0.2886332063223106</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.3335890116038249</v>
+        <v>0.3248518656430153</v>
       </c>
       <c r="C88">
-        <v>-1116.322374933615</v>
+        <v>-1093.079945310338</v>
       </c>
       <c r="D88">
-        <v>740.9556250663854</v>
+        <v>764.1980546896618</v>
       </c>
       <c r="E88">
         <v>1341.678</v>
@@ -8497,37 +8497,37 @@
         <v>160.4</v>
       </c>
       <c r="M88">
-        <v>581.6303074401686</v>
+        <v>562.2605274401686</v>
       </c>
       <c r="N88">
-        <v>-421.2303074401686</v>
+        <v>-401.8605274401687</v>
       </c>
       <c r="O88">
-        <v>-84.24606148803373</v>
+        <v>-80.37210548803374</v>
       </c>
       <c r="P88">
-        <v>-336.9842459521349</v>
+        <v>-321.4884219521349</v>
       </c>
       <c r="Q88">
-        <v>-249.0842459521349</v>
+        <v>-233.5884219521349</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.639956055699019</v>
+        <v>0.6389764416932363</v>
       </c>
       <c r="T88">
-        <v>5.089752317698335</v>
+        <v>5.081021111397583</v>
       </c>
       <c r="U88">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V88">
-        <v>0.05515531015085561</v>
+        <v>0.05705540124975909</v>
       </c>
       <c r="W88">
-        <v>0.2837153067511188</v>
+        <v>0.2737153067511188</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.275776550754278</v>
+        <v>0.2852770062487954</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.3361337834857986</v>
+        <v>0.3272966375249889</v>
       </c>
       <c r="C89">
-        <v>-1145.339841467343</v>
+        <v>-1122.23993370491</v>
       </c>
       <c r="D89">
-        <v>734.4611585326574</v>
+        <v>757.5610662950903</v>
       </c>
       <c r="E89">
         <v>1364.201</v>
@@ -8579,37 +8579,37 @@
         <v>160.4</v>
       </c>
       <c r="M89">
-        <v>588.3934505499382</v>
+        <v>568.7984405499381</v>
       </c>
       <c r="N89">
-        <v>-427.9934505499382</v>
+        <v>-408.3984405499381</v>
       </c>
       <c r="O89">
-        <v>-85.59869010998764</v>
+        <v>-81.67968810998762</v>
       </c>
       <c r="P89">
-        <v>-342.3947604399506</v>
+        <v>-326.7187524399504</v>
       </c>
       <c r="Q89">
-        <v>-254.4947604399506</v>
+        <v>-238.8187524399504</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.6856603676758668</v>
+        <v>0.6846053987465621</v>
       </c>
       <c r="T89">
-        <v>5.481271726752055</v>
+        <v>5.471868889197397</v>
       </c>
       <c r="U89">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V89">
-        <v>0.05452134106866185</v>
+        <v>0.05639959203999174</v>
       </c>
       <c r="W89">
-        <v>0.283905673204524</v>
+        <v>0.273905673204524</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2726067053433092</v>
+        <v>0.2819979601999586</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.3386785553677722</v>
+        <v>0.3297414094069627</v>
       </c>
       <c r="C90">
-        <v>-1174.244449374035</v>
+        <v>-1151.285631460142</v>
       </c>
       <c r="D90">
-        <v>728.0795506259647</v>
+        <v>751.0383685398581</v>
       </c>
       <c r="E90">
         <v>1386.724</v>
@@ -8661,37 +8661,37 @@
         <v>160.4</v>
       </c>
       <c r="M90">
-        <v>595.1565936597075</v>
+        <v>575.3363536597075</v>
       </c>
       <c r="N90">
-        <v>-434.7565936597075</v>
+        <v>-414.9363536597075</v>
       </c>
       <c r="O90">
-        <v>-86.95131873194151</v>
+        <v>-82.98727073194151</v>
       </c>
       <c r="P90">
-        <v>-347.805274927766</v>
+        <v>-331.949082927766</v>
       </c>
       <c r="Q90">
-        <v>-259.905274927766</v>
+        <v>-244.049082927766</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.738982064982189</v>
+        <v>0.7378391819754424</v>
       </c>
       <c r="T90">
-        <v>5.938044370648059</v>
+        <v>5.927857963297181</v>
       </c>
       <c r="U90">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V90">
-        <v>0.0539017803746998</v>
+        <v>0.05575868758499183</v>
       </c>
       <c r="W90">
-        <v>0.2840917131476245</v>
+        <v>0.2740917131476246</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.269508901873499</v>
+        <v>0.2787934379249591</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.341223327249746</v>
+        <v>0.3321861812889364</v>
       </c>
       <c r="C91">
-        <v>-1203.039115140994</v>
+        <v>-1180.219965545557</v>
       </c>
       <c r="D91">
-        <v>721.8078848590067</v>
+        <v>744.6270344544429</v>
       </c>
       <c r="E91">
         <v>1409.247</v>
@@ -8743,37 +8743,37 @@
         <v>160.4</v>
       </c>
       <c r="M91">
-        <v>601.9197367694769</v>
+        <v>581.8742667694769</v>
       </c>
       <c r="N91">
-        <v>-441.5197367694769</v>
+        <v>-421.4742667694769</v>
       </c>
       <c r="O91">
-        <v>-88.3039473538954</v>
+        <v>-84.29485335389539</v>
       </c>
       <c r="P91">
-        <v>-353.2157894155815</v>
+        <v>-337.1794134155815</v>
       </c>
       <c r="Q91">
-        <v>-265.3157894155815</v>
+        <v>-249.2794134155815</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.8019986163442063</v>
+        <v>0.8007518348823008</v>
       </c>
       <c r="T91">
-        <v>6.47786658616152</v>
+        <v>6.466754141778743</v>
       </c>
       <c r="U91">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V91">
-        <v>0.05329614239296159</v>
+        <v>0.05513218547729529</v>
       </c>
       <c r="W91">
-        <v>0.2842735724178465</v>
+        <v>0.2742735724178464</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2664807119648079</v>
+        <v>0.2756609273864764</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.3437680991317197</v>
+        <v>0.3346309531709102</v>
       </c>
       <c r="C92">
-        <v>-1231.726655623443</v>
+        <v>-1209.045763830873</v>
       </c>
       <c r="D92">
-        <v>715.6433443765569</v>
+        <v>738.3242361691269</v>
       </c>
       <c r="E92">
         <v>1431.77</v>
@@ -8825,37 +8825,37 @@
         <v>160.4</v>
       </c>
       <c r="M92">
-        <v>608.6828798792463</v>
+        <v>588.4121798792463</v>
       </c>
       <c r="N92">
-        <v>-448.2828798792464</v>
+        <v>-428.0121798792463</v>
       </c>
       <c r="O92">
-        <v>-89.65657597584928</v>
+        <v>-85.60243597584927</v>
       </c>
       <c r="P92">
-        <v>-358.6263039033971</v>
+        <v>-342.409743903397</v>
       </c>
       <c r="Q92">
-        <v>-270.7263039033971</v>
+        <v>-254.509743903397</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.8776184779786269</v>
+        <v>0.8762470183705311</v>
       </c>
       <c r="T92">
-        <v>7.125653244777672</v>
+        <v>7.113429555956619</v>
       </c>
       <c r="U92">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V92">
-        <v>0.05270396303303979</v>
+        <v>0.05451960563865868</v>
       </c>
       <c r="W92">
-        <v>0.2844513903709523</v>
+        <v>0.2744513903709523</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.263519815165199</v>
+        <v>0.2725980281932934</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.3463128710136935</v>
+        <v>0.3370757250528839</v>
       </c>
       <c r="C93">
-        <v>-1260.309792263009</v>
+        <v>-1237.765759244886</v>
       </c>
       <c r="D93">
-        <v>709.5832077369914</v>
+        <v>732.1272407551143</v>
       </c>
       <c r="E93">
         <v>1454.293</v>
@@ -8907,37 +8907,37 @@
         <v>160.4</v>
       </c>
       <c r="M93">
-        <v>615.4460229890158</v>
+        <v>594.9500929890157</v>
       </c>
       <c r="N93">
-        <v>-455.0460229890158</v>
+        <v>-434.5500929890158</v>
       </c>
       <c r="O93">
-        <v>-91.00920459780316</v>
+        <v>-86.91001859780316</v>
       </c>
       <c r="P93">
-        <v>-364.0368183912126</v>
+        <v>-347.6400743912126</v>
       </c>
       <c r="Q93">
-        <v>-276.1368183912126</v>
+        <v>-259.7400743912126</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.9700427533095857</v>
+        <v>0.9685189093005901</v>
       </c>
       <c r="T93">
-        <v>7.917392494197414</v>
+        <v>7.903810617729577</v>
       </c>
       <c r="U93">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V93">
-        <v>0.05212479860410529</v>
+        <v>0.05392048909317892</v>
       </c>
       <c r="W93">
-        <v>0.2846253002371766</v>
+        <v>0.2746253002371767</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2606239930205264</v>
+        <v>0.2696024454658945</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.3488576428956672</v>
+        <v>0.3395204969348576</v>
       </c>
       <c r="C94">
-        <v>-1288.791155093646</v>
+        <v>-1266.382593726659</v>
       </c>
       <c r="D94">
-        <v>703.6248449063547</v>
+        <v>726.0334062733415</v>
       </c>
       <c r="E94">
         <v>1476.816</v>
@@ -8989,37 +8989,37 @@
         <v>160.4</v>
       </c>
       <c r="M94">
-        <v>622.2091660987852</v>
+        <v>601.4880060987851</v>
       </c>
       <c r="N94">
-        <v>-461.8091660987852</v>
+        <v>-441.0880060987852</v>
       </c>
       <c r="O94">
-        <v>-92.36183321975705</v>
+        <v>-88.21760121975704</v>
       </c>
       <c r="P94">
-        <v>-369.4473328790282</v>
+        <v>-352.8704048790281</v>
       </c>
       <c r="Q94">
-        <v>-281.5473328790282</v>
+        <v>-264.9704048790281</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>1.085573097473284</v>
+        <v>1.083858772963164</v>
       </c>
       <c r="T94">
-        <v>8.907066555972092</v>
+        <v>8.891786944945776</v>
       </c>
       <c r="U94">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V94">
-        <v>0.05155822470623458</v>
+        <v>0.05333439682042697</v>
       </c>
       <c r="W94">
-        <v>0.2847954294541353</v>
+        <v>0.2747954294541353</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2577911235311728</v>
+        <v>0.2666719841021348</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.3514024147776409</v>
+        <v>0.3419652688168313</v>
       </c>
       <c r="C95">
-        <v>-1317.173286547429</v>
+        <v>-1294.89882198101</v>
       </c>
       <c r="D95">
-        <v>697.7657134525715</v>
+        <v>720.0401780189896</v>
       </c>
       <c r="E95">
         <v>1499.339</v>
@@ -9071,37 +9071,37 @@
         <v>160.4</v>
       </c>
       <c r="M95">
-        <v>628.9723092085545</v>
+        <v>608.0259192085545</v>
       </c>
       <c r="N95">
-        <v>-468.5723092085545</v>
+        <v>-447.6259192085545</v>
       </c>
       <c r="O95">
-        <v>-93.71446184171091</v>
+        <v>-89.5251838417109</v>
       </c>
       <c r="P95">
-        <v>-374.8578473668437</v>
+        <v>-358.1007353668436</v>
       </c>
       <c r="Q95">
-        <v>-286.9578473668437</v>
+        <v>-270.2007353668436</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>1.234112111398039</v>
+        <v>1.232152883386474</v>
       </c>
       <c r="T95">
-        <v>10.17950463539668</v>
+        <v>10.16204222279517</v>
       </c>
       <c r="U95">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V95">
-        <v>0.05100383519326433</v>
+        <v>0.05276090868257292</v>
       </c>
       <c r="W95">
-        <v>0.2849618999782562</v>
+        <v>0.2749618999782562</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2550191759663215</v>
+        <v>0.2638045434128645</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3539471866596147</v>
+        <v>0.3444100406988051</v>
       </c>
       <c r="C96">
-        <v>-1345.458645071769</v>
+        <v>-1323.316915049525</v>
       </c>
       <c r="D96">
-        <v>692.0033549282315</v>
+        <v>714.1450849504757</v>
       </c>
       <c r="E96">
         <v>1521.862</v>
@@ -9153,37 +9153,37 @@
         <v>160.4</v>
       </c>
       <c r="M96">
-        <v>635.735452318324</v>
+        <v>614.5638323183239</v>
       </c>
       <c r="N96">
-        <v>-475.335452318324</v>
+        <v>-454.1638323183239</v>
       </c>
       <c r="O96">
-        <v>-95.0670904636648</v>
+        <v>-90.83276646366478</v>
       </c>
       <c r="P96">
-        <v>-380.2683618546592</v>
+        <v>-363.3310658546591</v>
       </c>
       <c r="Q96">
-        <v>-292.3683618546592</v>
+        <v>-275.4310658546591</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.432164129964379</v>
+        <v>1.429878363950886</v>
       </c>
       <c r="T96">
-        <v>11.87608874129613</v>
+        <v>11.85571592659437</v>
       </c>
       <c r="U96">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V96">
-        <v>0.05046124120184661</v>
+        <v>0.05219962241999235</v>
       </c>
       <c r="W96">
-        <v>0.2851248285763319</v>
+        <v>0.2751248285763319</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.252306206009233</v>
+        <v>0.2609981120999617</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3564919585415884</v>
+        <v>0.3468548125807788</v>
       </c>
       <c r="C97">
-        <v>-1373.649608568858</v>
+        <v>-1351.639263707564</v>
       </c>
       <c r="D97">
-        <v>686.3353914311425</v>
+        <v>708.3457362924363</v>
       </c>
       <c r="E97">
         <v>1544.385</v>
@@ -9235,37 +9235,37 @@
         <v>160.4</v>
       </c>
       <c r="M97">
-        <v>642.4985954280934</v>
+        <v>621.1017454280934</v>
       </c>
       <c r="N97">
-        <v>-482.0985954280934</v>
+        <v>-460.7017454280934</v>
       </c>
       <c r="O97">
-        <v>-96.41971908561868</v>
+        <v>-92.14034908561869</v>
       </c>
       <c r="P97">
-        <v>-385.6788763424747</v>
+        <v>-368.5613963424747</v>
       </c>
       <c r="Q97">
-        <v>-297.7788763424747</v>
+        <v>-280.6613963424747</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.709436955957256</v>
+        <v>1.706694036741064</v>
       </c>
       <c r="T97">
-        <v>14.25130648955536</v>
+        <v>14.22685911191325</v>
       </c>
       <c r="U97">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V97">
-        <v>0.04993007024182718</v>
+        <v>0.05165015271030822</v>
       </c>
       <c r="W97">
-        <v>0.2852843270986586</v>
+        <v>0.2752843270986586</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2496503512091358</v>
+        <v>0.258250763551541</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.359036730423562</v>
+        <v>0.3492995844627524</v>
       </c>
       <c r="C98">
-        <v>-1401.748477667464</v>
+        <v>-1379.868181697103</v>
       </c>
       <c r="D98">
-        <v>680.7595223325358</v>
+        <v>702.6398183028973</v>
       </c>
       <c r="E98">
         <v>1566.908</v>
@@ -9317,37 +9317,37 @@
         <v>160.4</v>
       </c>
       <c r="M98">
-        <v>649.2617385378627</v>
+        <v>627.6396585378627</v>
       </c>
       <c r="N98">
-        <v>-488.8617385378627</v>
+        <v>-467.2396585378627</v>
       </c>
       <c r="O98">
-        <v>-97.77234770757255</v>
+        <v>-93.44793170757255</v>
       </c>
       <c r="P98">
-        <v>-391.0893908302902</v>
+        <v>-373.7917268302902</v>
       </c>
       <c r="Q98">
-        <v>-303.1893908302902</v>
+        <v>-285.8917268302902</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>2.125346194946566</v>
+        <v>2.121917545926325</v>
       </c>
       <c r="T98">
-        <v>17.81413311194416</v>
+        <v>17.78357388989153</v>
       </c>
       <c r="U98">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V98">
-        <v>0.04940996534347482</v>
+        <v>0.05111213028624251</v>
       </c>
       <c r="W98">
-        <v>0.2854405027351035</v>
+        <v>0.2754405027351035</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.247049826717374</v>
+        <v>0.2555606514312125</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.3615815023055358</v>
+        <v>0.3517443563447261</v>
       </c>
       <c r="C99">
-        <v>-1429.757478836531</v>
+        <v>-1408.005908804559</v>
       </c>
       <c r="D99">
-        <v>675.2735211634694</v>
+        <v>697.0250911954408</v>
       </c>
       <c r="E99">
         <v>1589.431</v>
@@ -9399,37 +9399,37 @@
         <v>160.4</v>
       </c>
       <c r="M99">
-        <v>656.0248816476321</v>
+        <v>634.1775716476321</v>
       </c>
       <c r="N99">
-        <v>-495.6248816476322</v>
+        <v>-473.7775716476322</v>
       </c>
       <c r="O99">
-        <v>-99.12497632952643</v>
+        <v>-94.75551432952643</v>
       </c>
       <c r="P99">
-        <v>-396.4999053181057</v>
+        <v>-379.0220573181057</v>
       </c>
       <c r="Q99">
-        <v>-308.5999053181057</v>
+        <v>-291.1220573181057</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.818528259928754</v>
+        <v>2.813956727901767</v>
       </c>
       <c r="T99">
-        <v>23.75217748259222</v>
+        <v>23.7114318531887</v>
       </c>
       <c r="U99">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V99">
-        <v>0.04890058425745961</v>
+        <v>0.05058520110803383</v>
       </c>
       <c r="W99">
-        <v>0.2855934582553331</v>
+        <v>0.275593458255333</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.244502921287298</v>
+        <v>0.2529260055401691</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.3641262741875095</v>
+        <v>0.3541891282266999</v>
       </c>
       <c r="C100">
-        <v>-1457.678767349423</v>
+        <v>-1436.054613792227</v>
       </c>
       <c r="D100">
-        <v>669.8752326505769</v>
+        <v>691.499386207773</v>
       </c>
       <c r="E100">
         <v>1611.954</v>
@@ -9481,37 +9481,37 @@
         <v>160.4</v>
       </c>
       <c r="M100">
-        <v>662.7880247574016</v>
+        <v>640.7154847574016</v>
       </c>
       <c r="N100">
-        <v>-502.3880247574016</v>
+        <v>-480.3154847574016</v>
       </c>
       <c r="O100">
-        <v>-100.4776049514803</v>
+        <v>-96.06309695148032</v>
       </c>
       <c r="P100">
-        <v>-401.9104198059213</v>
+        <v>-384.2523878059213</v>
       </c>
       <c r="Q100">
-        <v>-314.0104198059213</v>
+        <v>-296.3523878059212</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>4.204892389893131</v>
+        <v>4.198035091852651</v>
       </c>
       <c r="T100">
-        <v>35.62826622388832</v>
+        <v>35.56714777978306</v>
       </c>
       <c r="U100">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V100">
-        <v>0.04840159870381206</v>
+        <v>0.05006902558652328</v>
       </c>
       <c r="W100">
-        <v>0.2857432922343335</v>
+        <v>0.2757432922343335</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2420079935190602</v>
+        <v>0.2503451279326163</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3666710460694832</v>
+        <v>0.3566339001086736</v>
       </c>
       <c r="C101">
-        <v>-1485.51443010713</v>
+        <v>-1464.016397191373</v>
       </c>
       <c r="D101">
-        <v>664.5625698928702</v>
+        <v>686.060602808627</v>
       </c>
       <c r="E101">
         <v>1634.477</v>
@@ -9563,37 +9563,37 @@
         <v>160.4</v>
       </c>
       <c r="M101">
-        <v>669.5511678671709</v>
+        <v>647.2533978671709</v>
       </c>
       <c r="N101">
-        <v>-509.1511678671709</v>
+        <v>-486.8533978671709</v>
       </c>
       <c r="O101">
-        <v>-101.8302335734342</v>
+        <v>-97.37067957343419</v>
       </c>
       <c r="P101">
-        <v>-407.3209342937367</v>
+        <v>-389.4827182937367</v>
       </c>
       <c r="Q101">
-        <v>-319.4209342937368</v>
+        <v>-301.5827182937367</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>8.363984779786263</v>
+        <v>8.350270183705302</v>
       </c>
       <c r="T101">
-        <v>71.25653244777665</v>
+        <v>71.13429555956611</v>
       </c>
       <c r="U101">
-        <v>0.3002771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V101">
-        <v>0.04791269366639982</v>
+        <v>0.04956327785332608</v>
       </c>
       <c r="W101">
-        <v>0.2858900992642631</v>
+        <v>0.2758900992642632</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.239563468331999</v>
+        <v>0.2478163892666303</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/cambodia/cambodia_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/cambodia/cambodia_hotel_gaming.xlsx
@@ -1127,43 +1127,43 @@
         <v>8.02</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>67.9690793808435</v>
       </c>
       <c r="G2">
         <v>2.39750302053967</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0907088199758357</v>
       </c>
       <c r="I2">
         <v>0.26430759667895</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>1657</v>
       </c>
       <c r="L2">
-        <v>2521.60380930022</v>
+        <v>2493.34652106255</v>
       </c>
       <c r="M2">
         <v>2172.6</v>
       </c>
       <c r="N2">
-        <v>2441.90380930022</v>
+        <v>2436.16952106255</v>
       </c>
       <c r="O2">
         <v>595.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>22.523</v>
       </c>
       <c r="Q2">
         <v>0.143954696162162</v>
       </c>
       <c r="R2">
-        <v>0.133129767892465</v>
+        <v>0.133335325862259</v>
       </c>
       <c r="S2">
         <v>0.104221750557897</v>
@@ -1185,13 +1185,13 @@
         <v>0.15822930238921</v>
       </c>
       <c r="X2">
-        <v>0.133129767892465</v>
+        <v>0.133835462986545</v>
       </c>
       <c r="Y2">
         <v>0.9630450888248639</v>
       </c>
       <c r="Z2">
-        <v>0.7480479046815171</v>
+        <v>0.754092736234499</v>
       </c>
       <c r="AA2">
         <v>595.3</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1331297678924646</v>
+        <v>0.1333353258622586</v>
       </c>
       <c r="C2">
-        <v>2521.603809300218</v>
+        <v>2493.346521062554</v>
       </c>
       <c r="D2">
-        <v>2441.903809300219</v>
+        <v>2436.169521062554</v>
       </c>
       <c r="E2">
-        <v>-595.3</v>
+        <v>-572.7769999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22.523</v>
       </c>
       <c r="G2">
         <v>79.7</v>
@@ -1445,28 +1445,28 @@
         <v>160.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.359896609769403</v>
       </c>
       <c r="N2">
-        <v>160.4</v>
+        <v>158.0401033902306</v>
       </c>
       <c r="O2">
-        <v>32.08000000000001</v>
+        <v>31.60802067804612</v>
       </c>
       <c r="P2">
-        <v>128.32</v>
+        <v>126.4320827121845</v>
       </c>
       <c r="Q2">
-        <v>216.22</v>
+        <v>214.3320827121845</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1331297678924646</v>
+        <v>0.1338354629865451</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7540927362344988</v>
       </c>
       <c r="U2">
         <v>0.1047771881973717</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>67.9690793808435</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1333353258622586</v>
+        <v>0.1335408838320527</v>
       </c>
       <c r="C3">
-        <v>2493.346521062554</v>
+        <v>2465.116101226411</v>
       </c>
       <c r="D3">
-        <v>2436.169521062554</v>
+        <v>2430.462101226411</v>
       </c>
       <c r="E3">
-        <v>-572.7769999999999</v>
+        <v>-550.2539999999999</v>
       </c>
       <c r="F3">
-        <v>22.523</v>
+        <v>45.04600000000001</v>
       </c>
       <c r="G3">
         <v>79.7</v>
@@ -1527,28 +1527,28 @@
         <v>160.4</v>
       </c>
       <c r="M3">
-        <v>2.359896609769403</v>
+        <v>4.719793219538806</v>
       </c>
       <c r="N3">
-        <v>158.0401033902306</v>
+        <v>155.6802067804612</v>
       </c>
       <c r="O3">
-        <v>31.60802067804612</v>
+        <v>31.13604135609224</v>
       </c>
       <c r="P3">
-        <v>126.4320827121845</v>
+        <v>124.544165424369</v>
       </c>
       <c r="Q3">
-        <v>214.3320827121845</v>
+        <v>212.444165424369</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1338354629865451</v>
+        <v>0.1345555600213212</v>
       </c>
       <c r="T3">
-        <v>0.7540927362344988</v>
+        <v>0.7602609316967253</v>
       </c>
       <c r="U3">
         <v>0.1047771881973717</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>67.9690793808435</v>
+        <v>33.98453969042175</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1335408838320527</v>
+        <v>0.1337464418018467</v>
       </c>
       <c r="C4">
-        <v>2465.116101226411</v>
+        <v>2436.912361392558</v>
       </c>
       <c r="D4">
-        <v>2430.462101226411</v>
+        <v>2424.781361392558</v>
       </c>
       <c r="E4">
-        <v>-550.2539999999999</v>
+        <v>-527.731</v>
       </c>
       <c r="F4">
-        <v>45.04600000000001</v>
+        <v>67.569</v>
       </c>
       <c r="G4">
         <v>79.7</v>
@@ -1609,28 +1609,28 @@
         <v>160.4</v>
       </c>
       <c r="M4">
-        <v>4.719793219538806</v>
+        <v>7.079689829308208</v>
       </c>
       <c r="N4">
-        <v>155.6802067804612</v>
+        <v>153.3203101706918</v>
       </c>
       <c r="O4">
-        <v>31.13604135609224</v>
+        <v>30.66406203413836</v>
       </c>
       <c r="P4">
-        <v>124.544165424369</v>
+        <v>122.6562481365534</v>
       </c>
       <c r="Q4">
-        <v>212.444165424369</v>
+        <v>210.5562481365534</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1345555600213212</v>
+        <v>0.135290504417639</v>
       </c>
       <c r="T4">
-        <v>0.7602609316967253</v>
+        <v>0.7665563064468326</v>
       </c>
       <c r="U4">
         <v>0.1047771881973717</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.98453969042175</v>
+        <v>22.65635979361451</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1337464418018467</v>
+        <v>0.1339519997716408</v>
       </c>
       <c r="C5">
-        <v>2436.912361392558</v>
+        <v>2408.735114919039</v>
       </c>
       <c r="D5">
-        <v>2424.781361392558</v>
+        <v>2419.127114919039</v>
       </c>
       <c r="E5">
-        <v>-527.731</v>
+        <v>-505.208</v>
       </c>
       <c r="F5">
-        <v>67.569</v>
+        <v>90.09200000000001</v>
       </c>
       <c r="G5">
         <v>79.7</v>
@@ -1691,28 +1691,28 @@
         <v>160.4</v>
       </c>
       <c r="M5">
-        <v>7.079689829308208</v>
+        <v>9.439586439077612</v>
       </c>
       <c r="N5">
-        <v>153.3203101706918</v>
+        <v>150.9604135609224</v>
       </c>
       <c r="O5">
-        <v>30.66406203413836</v>
+        <v>30.19208271218448</v>
       </c>
       <c r="P5">
-        <v>122.6562481365534</v>
+        <v>120.7683308487379</v>
       </c>
       <c r="Q5">
-        <v>210.5562481365534</v>
+        <v>208.6683308487379</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.135290504417639</v>
+        <v>0.1360407601555468</v>
       </c>
       <c r="T5">
-        <v>0.7665563064468326</v>
+        <v>0.7729828348375675</v>
       </c>
       <c r="U5">
         <v>0.1047771881973717</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.65635979361451</v>
+        <v>16.99226984521088</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1339519997716408</v>
+        <v>0.1341575577414348</v>
       </c>
       <c r="C6">
-        <v>2408.735114919039</v>
+        <v>2380.584176900748</v>
       </c>
       <c r="D6">
-        <v>2419.127114919039</v>
+        <v>2413.499176900748</v>
       </c>
       <c r="E6">
-        <v>-505.208</v>
+        <v>-482.6849999999999</v>
       </c>
       <c r="F6">
-        <v>90.09200000000001</v>
+        <v>112.615</v>
       </c>
       <c r="G6">
         <v>79.7</v>
@@ -1773,28 +1773,28 @@
         <v>160.4</v>
       </c>
       <c r="M6">
-        <v>9.439586439077612</v>
+        <v>11.79948304884701</v>
       </c>
       <c r="N6">
-        <v>150.9604135609224</v>
+        <v>148.600516951153</v>
       </c>
       <c r="O6">
-        <v>30.19208271218448</v>
+        <v>29.7201033902306</v>
       </c>
       <c r="P6">
-        <v>120.7683308487379</v>
+        <v>118.8804135609224</v>
       </c>
       <c r="Q6">
-        <v>208.6683308487379</v>
+        <v>206.7804135609224</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1360407601555468</v>
+        <v>0.1368068107510947</v>
       </c>
       <c r="T6">
-        <v>0.7729828348375675</v>
+        <v>0.7795446585628438</v>
       </c>
       <c r="U6">
         <v>0.1047771881973717</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.99226984521088</v>
+        <v>13.5938158761687</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1341575577414348</v>
+        <v>0.1344351157112288</v>
       </c>
       <c r="C7">
-        <v>2380.584176900748</v>
+        <v>2350.503383059505</v>
       </c>
       <c r="D7">
-        <v>2413.499176900748</v>
+        <v>2405.941383059505</v>
       </c>
       <c r="E7">
-        <v>-482.6849999999999</v>
+        <v>-460.1619999999999</v>
       </c>
       <c r="F7">
-        <v>112.615</v>
+        <v>135.138</v>
       </c>
       <c r="G7">
         <v>79.7</v>
@@ -1855,45 +1855,45 @@
         <v>160.4</v>
       </c>
       <c r="M7">
-        <v>11.79948304884701</v>
+        <v>14.36208665861642</v>
       </c>
       <c r="N7">
-        <v>148.600516951153</v>
+        <v>146.0379133413836</v>
       </c>
       <c r="O7">
-        <v>29.7201033902306</v>
+        <v>29.20758266827672</v>
       </c>
       <c r="P7">
-        <v>118.8804135609224</v>
+        <v>116.8303306731069</v>
       </c>
       <c r="Q7">
-        <v>206.7804135609224</v>
+        <v>204.7303306731069</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1368068107510947</v>
+        <v>0.1375891602954841</v>
       </c>
       <c r="T7">
-        <v>0.7795446585628438</v>
+        <v>0.7862460955588709</v>
       </c>
       <c r="U7">
-        <v>0.1047771881973717</v>
+        <v>0.1062771881973717</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.08382175055789737</v>
+        <v>0.08502175055789736</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.5938158761687</v>
+        <v>11.16829356434563</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1344351157112288</v>
+        <v>0.1347478736810229</v>
       </c>
       <c r="C8">
-        <v>2350.503383059505</v>
+        <v>2319.520626673336</v>
       </c>
       <c r="D8">
-        <v>2405.941383059505</v>
+        <v>2397.481626673336</v>
       </c>
       <c r="E8">
-        <v>-460.1619999999999</v>
+        <v>-437.639</v>
       </c>
       <c r="F8">
-        <v>135.138</v>
+        <v>157.661</v>
       </c>
       <c r="G8">
         <v>79.7</v>
@@ -1937,45 +1937,45 @@
         <v>160.4</v>
       </c>
       <c r="M8">
-        <v>14.36208665861642</v>
+        <v>17.02379146838582</v>
       </c>
       <c r="N8">
-        <v>146.0379133413836</v>
+        <v>143.3762085316142</v>
       </c>
       <c r="O8">
-        <v>29.20758266827672</v>
+        <v>28.67524170632284</v>
       </c>
       <c r="P8">
-        <v>116.8303306731069</v>
+        <v>114.7009668252914</v>
       </c>
       <c r="Q8">
-        <v>204.7303306731069</v>
+        <v>202.6009668252914</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1375891602954841</v>
+        <v>0.1383883345612582</v>
       </c>
       <c r="T8">
-        <v>0.7862460955588709</v>
+        <v>0.7930916494795437</v>
       </c>
       <c r="U8">
-        <v>0.1062771881973717</v>
+        <v>0.1079771881973717</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.08502175055789736</v>
+        <v>0.08638175055789736</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>11.16829356434563</v>
+        <v>9.422107895169667</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1347478736810229</v>
+        <v>0.134979031650817</v>
       </c>
       <c r="C9">
-        <v>2319.520626673337</v>
+        <v>2290.783195150796</v>
       </c>
       <c r="D9">
-        <v>2397.481626673337</v>
+        <v>2391.267195150797</v>
       </c>
       <c r="E9">
-        <v>-437.6389999999999</v>
+        <v>-415.1159999999999</v>
       </c>
       <c r="F9">
-        <v>157.661</v>
+        <v>180.184</v>
       </c>
       <c r="G9">
         <v>79.7</v>
@@ -2019,28 +2019,28 @@
         <v>160.4</v>
       </c>
       <c r="M9">
-        <v>17.02379146838582</v>
+        <v>19.45576167815522</v>
       </c>
       <c r="N9">
-        <v>143.3762085316142</v>
+        <v>140.9442383218448</v>
       </c>
       <c r="O9">
-        <v>28.67524170632284</v>
+        <v>28.18884766436896</v>
       </c>
       <c r="P9">
-        <v>114.7009668252914</v>
+        <v>112.7553906574758</v>
       </c>
       <c r="Q9">
-        <v>202.6009668252914</v>
+        <v>200.6553906574758</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1383883345612582</v>
+        <v>0.139204882180636</v>
       </c>
       <c r="T9">
-        <v>0.7930916494795437</v>
+        <v>0.8000860197897963</v>
       </c>
       <c r="U9">
         <v>0.1079771881973717</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.422107895169665</v>
+        <v>8.244344408273456</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.134979031650817</v>
+        <v>0.135267789620611</v>
       </c>
       <c r="C10">
-        <v>2290.783195150796</v>
+        <v>2260.542362135866</v>
       </c>
       <c r="D10">
-        <v>2391.267195150797</v>
+        <v>2383.549362135866</v>
       </c>
       <c r="E10">
-        <v>-415.1159999999999</v>
+        <v>-392.593</v>
       </c>
       <c r="F10">
-        <v>180.184</v>
+        <v>202.707</v>
       </c>
       <c r="G10">
         <v>79.7</v>
@@ -2101,45 +2101,45 @@
         <v>160.4</v>
       </c>
       <c r="M10">
-        <v>19.45576167815522</v>
+        <v>22.04989748792463</v>
       </c>
       <c r="N10">
-        <v>140.9442383218448</v>
+        <v>138.3501025120754</v>
       </c>
       <c r="O10">
-        <v>28.18884766436896</v>
+        <v>27.67002050241508</v>
       </c>
       <c r="P10">
-        <v>112.7553906574758</v>
+        <v>110.6800820096603</v>
       </c>
       <c r="Q10">
-        <v>200.6553906574758</v>
+        <v>198.5800820096603</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.139204882180636</v>
+        <v>0.1400393759015387</v>
       </c>
       <c r="T10">
-        <v>0.8000860197897963</v>
+        <v>0.80723411252445</v>
       </c>
       <c r="U10">
-        <v>0.1079771881973717</v>
+        <v>0.1087771881973717</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.08638175055789736</v>
+        <v>0.08702175055789736</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.244344408273456</v>
+        <v>7.274410236502969</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.135267789620611</v>
+        <v>0.135505347590405</v>
       </c>
       <c r="C11">
-        <v>2260.542362135866</v>
+        <v>2231.707239585956</v>
       </c>
       <c r="D11">
-        <v>2383.549362135866</v>
+        <v>2377.237239585957</v>
       </c>
       <c r="E11">
-        <v>-392.593</v>
+        <v>-370.0699999999999</v>
       </c>
       <c r="F11">
-        <v>202.707</v>
+        <v>225.23</v>
       </c>
       <c r="G11">
         <v>79.7</v>
@@ -2183,28 +2183,28 @@
         <v>160.4</v>
       </c>
       <c r="M11">
-        <v>22.04989748792463</v>
+        <v>24.49988609769403</v>
       </c>
       <c r="N11">
-        <v>138.3501025120754</v>
+        <v>135.900113902306</v>
       </c>
       <c r="O11">
-        <v>27.67002050241508</v>
+        <v>27.1800227804612</v>
       </c>
       <c r="P11">
-        <v>110.6800820096603</v>
+        <v>108.7200911218448</v>
       </c>
       <c r="Q11">
-        <v>198.5800820096603</v>
+        <v>196.6200911218448</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1400393759015387</v>
+        <v>0.1408924139273503</v>
       </c>
       <c r="T11">
-        <v>0.80723411252445</v>
+        <v>0.8145410517643182</v>
       </c>
       <c r="U11">
         <v>0.1087771881973717</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.274410236502969</v>
+        <v>6.546969212852672</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.135505347590405</v>
+        <v>0.1358309055601991</v>
       </c>
       <c r="C12">
-        <v>2231.707239585956</v>
+        <v>2200.587985614914</v>
       </c>
       <c r="D12">
-        <v>2377.237239585957</v>
+        <v>2368.640985614914</v>
       </c>
       <c r="E12">
-        <v>-370.0699999999999</v>
+        <v>-347.5469999999999</v>
       </c>
       <c r="F12">
-        <v>225.23</v>
+        <v>247.753</v>
       </c>
       <c r="G12">
         <v>79.7</v>
@@ -2265,45 +2265,45 @@
         <v>160.4</v>
       </c>
       <c r="M12">
-        <v>24.49988609769403</v>
+        <v>27.19762770746343</v>
       </c>
       <c r="N12">
-        <v>135.900113902306</v>
+        <v>133.2023722925366</v>
       </c>
       <c r="O12">
-        <v>27.1800227804612</v>
+        <v>26.64047445850732</v>
       </c>
       <c r="P12">
-        <v>108.7200911218448</v>
+        <v>106.5618978340293</v>
       </c>
       <c r="Q12">
-        <v>196.6200911218448</v>
+        <v>194.4618978340293</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1408924139273503</v>
+        <v>0.1417646213470004</v>
       </c>
       <c r="T12">
-        <v>0.8145410517643185</v>
+        <v>0.8220121918859814</v>
       </c>
       <c r="U12">
-        <v>0.1087771881973717</v>
+        <v>0.1097771881973717</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.08702175055789736</v>
+        <v>0.08782175055789737</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.546969212852672</v>
+        <v>5.897573190031713</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1358309055601991</v>
+        <v>0.1360764635299931</v>
       </c>
       <c r="C13">
-        <v>2200.587985614914</v>
+        <v>2171.622124997038</v>
       </c>
       <c r="D13">
-        <v>2368.640985614914</v>
+        <v>2362.198124997038</v>
       </c>
       <c r="E13">
-        <v>-347.5469999999999</v>
+        <v>-325.0239999999999</v>
       </c>
       <c r="F13">
-        <v>247.753</v>
+        <v>270.276</v>
       </c>
       <c r="G13">
         <v>79.7</v>
@@ -2347,28 +2347,28 @@
         <v>160.4</v>
       </c>
       <c r="M13">
-        <v>27.19762770746343</v>
+        <v>29.67013931723283</v>
       </c>
       <c r="N13">
-        <v>133.2023722925366</v>
+        <v>130.7298606827672</v>
       </c>
       <c r="O13">
-        <v>26.64047445850732</v>
+        <v>26.14597213655344</v>
       </c>
       <c r="P13">
-        <v>106.5618978340293</v>
+        <v>104.5838885462137</v>
       </c>
       <c r="Q13">
-        <v>194.4618978340293</v>
+        <v>192.4838885462137</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1417646213470004</v>
+        <v>0.1426566516625516</v>
       </c>
       <c r="T13">
-        <v>0.8220121918859814</v>
+        <v>0.8296531306467733</v>
       </c>
       <c r="U13">
         <v>0.1097771881973717</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.897573190031713</v>
+        <v>5.406108757529069</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1360764635299931</v>
+        <v>0.1363220214997872</v>
       </c>
       <c r="C14">
-        <v>2171.622124997038</v>
+        <v>2142.691219316021</v>
       </c>
       <c r="D14">
-        <v>2362.198124997038</v>
+        <v>2355.790219316021</v>
       </c>
       <c r="E14">
-        <v>-325.0239999999999</v>
+        <v>-302.5009999999999</v>
       </c>
       <c r="F14">
-        <v>270.276</v>
+        <v>292.799</v>
       </c>
       <c r="G14">
         <v>79.7</v>
@@ -2429,28 +2429,28 @@
         <v>160.4</v>
       </c>
       <c r="M14">
-        <v>29.67013931723283</v>
+        <v>32.14265092700224</v>
       </c>
       <c r="N14">
-        <v>130.7298606827672</v>
+        <v>128.2573490729978</v>
       </c>
       <c r="O14">
-        <v>26.14597213655344</v>
+        <v>25.65146981459955</v>
       </c>
       <c r="P14">
-        <v>104.5838885462137</v>
+        <v>102.6058792583982</v>
       </c>
       <c r="Q14">
-        <v>192.4838885462137</v>
+        <v>190.5058792583982</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1426566516625516</v>
+        <v>0.1435691884221385</v>
       </c>
       <c r="T14">
-        <v>0.8296531306467733</v>
+        <v>0.8374697231721808</v>
       </c>
       <c r="U14">
         <v>0.1097771881973717</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.406108757529069</v>
+        <v>4.990254237719141</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1363220214997872</v>
+        <v>0.1365675794695812</v>
       </c>
       <c r="C15">
-        <v>2142.691219316021</v>
+        <v>2113.794984875966</v>
       </c>
       <c r="D15">
-        <v>2355.790219316021</v>
+        <v>2349.416984875967</v>
       </c>
       <c r="E15">
-        <v>-302.5009999999999</v>
+        <v>-279.9779999999999</v>
       </c>
       <c r="F15">
-        <v>292.799</v>
+        <v>315.3220000000001</v>
       </c>
       <c r="G15">
         <v>79.7</v>
@@ -2511,28 +2511,28 @@
         <v>160.4</v>
       </c>
       <c r="M15">
-        <v>32.14265092700224</v>
+        <v>34.61516253677165</v>
       </c>
       <c r="N15">
-        <v>128.2573490729978</v>
+        <v>125.7848374632284</v>
       </c>
       <c r="O15">
-        <v>25.65146981459955</v>
+        <v>25.15696749264567</v>
       </c>
       <c r="P15">
-        <v>102.6058792583982</v>
+        <v>100.6278699705827</v>
       </c>
       <c r="Q15">
-        <v>190.5058792583982</v>
+        <v>188.5278699705827</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1435691884221385</v>
+        <v>0.1445029469668321</v>
       </c>
       <c r="T15">
-        <v>0.8374697231721808</v>
+        <v>0.8454680969191097</v>
       </c>
       <c r="U15">
         <v>0.1097771881973717</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.990254237719141</v>
+        <v>4.633807506453487</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1365675794695812</v>
+        <v>0.1371131374393753</v>
       </c>
       <c r="C16">
-        <v>2113.794984875966</v>
+        <v>2077.235196781597</v>
       </c>
       <c r="D16">
-        <v>2349.416984875967</v>
+        <v>2335.380196781597</v>
       </c>
       <c r="E16">
-        <v>-279.9779999999999</v>
+        <v>-257.4549999999999</v>
       </c>
       <c r="F16">
-        <v>315.3220000000001</v>
+        <v>337.8450000000001</v>
       </c>
       <c r="G16">
         <v>79.7</v>
@@ -2593,45 +2593,45 @@
         <v>160.4</v>
       </c>
       <c r="M16">
-        <v>34.61516253677165</v>
+        <v>37.93228664654105</v>
       </c>
       <c r="N16">
-        <v>125.7848374632284</v>
+        <v>122.4677133534589</v>
       </c>
       <c r="O16">
-        <v>25.15696749264567</v>
+        <v>24.49354267069179</v>
       </c>
       <c r="P16">
-        <v>100.6278699705827</v>
+        <v>97.97417068276715</v>
       </c>
       <c r="Q16">
-        <v>188.5278699705827</v>
+        <v>185.8741706827672</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1445029469668321</v>
+        <v>0.1454586763008125</v>
       </c>
       <c r="T16">
-        <v>0.8454680969191097</v>
+        <v>0.853654667695378</v>
       </c>
       <c r="U16">
-        <v>0.1097771881973717</v>
+        <v>0.1122771881973717</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.08782175055789737</v>
+        <v>0.08982175055789737</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.633807506453487</v>
+        <v>4.228587680321836</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1371131374393753</v>
+        <v>0.1378266954091693</v>
       </c>
       <c r="C17">
-        <v>2077.235196781597</v>
+        <v>2036.604090818394</v>
       </c>
       <c r="D17">
-        <v>2335.380196781597</v>
+        <v>2317.272090818394</v>
       </c>
       <c r="E17">
-        <v>-257.4549999999999</v>
+        <v>-234.9319999999999</v>
       </c>
       <c r="F17">
-        <v>337.845</v>
+        <v>360.3680000000001</v>
       </c>
       <c r="G17">
         <v>79.7</v>
@@ -2675,45 +2675,45 @@
         <v>160.4</v>
       </c>
       <c r="M17">
-        <v>37.93228664654104</v>
+        <v>41.72239375631045</v>
       </c>
       <c r="N17">
-        <v>122.467713353459</v>
+        <v>118.6776062436896</v>
       </c>
       <c r="O17">
-        <v>24.4935426706918</v>
+        <v>23.73552124873791</v>
       </c>
       <c r="P17">
-        <v>97.97417068276717</v>
+        <v>94.94208499495164</v>
       </c>
       <c r="Q17">
-        <v>185.8741706827672</v>
+        <v>182.8420849949516</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1454586763008125</v>
+        <v>0.1464371610951258</v>
       </c>
       <c r="T17">
-        <v>0.853654667695378</v>
+        <v>0.8620361568234621</v>
       </c>
       <c r="U17">
-        <v>0.1122771881973717</v>
+        <v>0.1157771881973717</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.08982175055789737</v>
+        <v>0.09262175055789737</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.228587680321837</v>
+        <v>3.844458228759699</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1378266954091693</v>
+        <v>0.1381202533789633</v>
       </c>
       <c r="C18">
-        <v>2036.604090818394</v>
+        <v>2006.712678519429</v>
       </c>
       <c r="D18">
-        <v>2317.272090818394</v>
+        <v>2309.903678519429</v>
       </c>
       <c r="E18">
-        <v>-234.9319999999999</v>
+        <v>-212.4089999999999</v>
       </c>
       <c r="F18">
-        <v>360.3680000000001</v>
+        <v>382.8910000000001</v>
       </c>
       <c r="G18">
         <v>79.7</v>
@@ -2757,28 +2757,28 @@
         <v>160.4</v>
       </c>
       <c r="M18">
-        <v>41.72239375631045</v>
+        <v>44.33004336607986</v>
       </c>
       <c r="N18">
-        <v>118.6776062436896</v>
+        <v>116.0699566339202</v>
       </c>
       <c r="O18">
-        <v>23.73552124873791</v>
+        <v>23.21399132678403</v>
       </c>
       <c r="P18">
-        <v>94.94208499495164</v>
+        <v>92.85596530713613</v>
       </c>
       <c r="Q18">
-        <v>182.8420849949516</v>
+        <v>180.7559653071361</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1464371610951258</v>
+        <v>0.1474392238362901</v>
       </c>
       <c r="T18">
-        <v>0.8620361568234621</v>
+        <v>0.8706196095449943</v>
       </c>
       <c r="U18">
         <v>0.1157771881973717</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.844458228759699</v>
+        <v>3.618313627067952</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1381202533789633</v>
+        <v>0.1388170113487574</v>
       </c>
       <c r="C19">
-        <v>2006.712678519429</v>
+        <v>1966.886996202206</v>
       </c>
       <c r="D19">
-        <v>2309.903678519429</v>
+        <v>2292.600996202207</v>
       </c>
       <c r="E19">
-        <v>-212.4089999999999</v>
+        <v>-189.8859999999999</v>
       </c>
       <c r="F19">
-        <v>382.8910000000001</v>
+        <v>405.4140000000001</v>
       </c>
       <c r="G19">
         <v>79.7</v>
@@ -2839,45 +2839,45 @@
         <v>160.4</v>
       </c>
       <c r="M19">
-        <v>44.33004336607986</v>
+        <v>48.07285217584926</v>
       </c>
       <c r="N19">
-        <v>116.0699566339202</v>
+        <v>112.3271478241507</v>
       </c>
       <c r="O19">
-        <v>23.21399132678403</v>
+        <v>22.46542956483015</v>
       </c>
       <c r="P19">
-        <v>92.85596530713613</v>
+        <v>89.8617182593206</v>
       </c>
       <c r="Q19">
-        <v>180.7559653071361</v>
+        <v>177.7617182593206</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1474392238362901</v>
+        <v>0.1484657271321169</v>
       </c>
       <c r="T19">
-        <v>0.8706196095449943</v>
+        <v>0.8794124147719297</v>
       </c>
       <c r="U19">
-        <v>0.1157771881973717</v>
+        <v>0.1185771881973717</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.09262175055789737</v>
+        <v>0.09486175055789736</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.618313627067952</v>
+        <v>3.336602525959161</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1388170113487574</v>
+        <v>0.1391329693185515</v>
       </c>
       <c r="C20">
-        <v>1966.886996202207</v>
+        <v>1936.602906400857</v>
       </c>
       <c r="D20">
-        <v>2292.600996202207</v>
+        <v>2284.839906400857</v>
       </c>
       <c r="E20">
-        <v>-189.8859999999999</v>
+        <v>-167.3629999999999</v>
       </c>
       <c r="F20">
-        <v>405.414</v>
+        <v>427.937</v>
       </c>
       <c r="G20">
         <v>79.7</v>
@@ -2921,28 +2921,28 @@
         <v>160.4</v>
       </c>
       <c r="M20">
-        <v>48.07285217584926</v>
+        <v>50.74356618561865</v>
       </c>
       <c r="N20">
-        <v>112.3271478241508</v>
+        <v>109.6564338143814</v>
       </c>
       <c r="O20">
-        <v>22.46542956483015</v>
+        <v>21.93128676287627</v>
       </c>
       <c r="P20">
-        <v>89.86171825932061</v>
+        <v>87.72514705150509</v>
       </c>
       <c r="Q20">
-        <v>177.7617182593206</v>
+        <v>175.6251470515051</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1484657271321169</v>
+        <v>0.1495175761883345</v>
       </c>
       <c r="T20">
-        <v>0.8794124147719294</v>
+        <v>0.8884223263007646</v>
       </c>
       <c r="U20">
         <v>0.1185771881973717</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.336602525959162</v>
+        <v>3.160991866698153</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1391329693185515</v>
+        <v>0.1394489272883455</v>
       </c>
       <c r="C21">
-        <v>1936.602906400857</v>
+        <v>1906.371186194079</v>
       </c>
       <c r="D21">
-        <v>2284.839906400857</v>
+        <v>2277.131186194079</v>
       </c>
       <c r="E21">
-        <v>-167.3629999999999</v>
+        <v>-144.8399999999999</v>
       </c>
       <c r="F21">
-        <v>427.937</v>
+        <v>450.46</v>
       </c>
       <c r="G21">
         <v>79.7</v>
@@ -3003,28 +3003,28 @@
         <v>160.4</v>
       </c>
       <c r="M21">
-        <v>50.74356618561865</v>
+        <v>53.41428019538806</v>
       </c>
       <c r="N21">
-        <v>109.6564338143814</v>
+        <v>106.9857198046119</v>
       </c>
       <c r="O21">
-        <v>21.93128676287627</v>
+        <v>21.39714396092239</v>
       </c>
       <c r="P21">
-        <v>87.72514705150509</v>
+        <v>85.58857584368955</v>
       </c>
       <c r="Q21">
-        <v>175.6251470515051</v>
+        <v>173.4885758436895</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1495175761883345</v>
+        <v>0.1505957214709575</v>
       </c>
       <c r="T21">
-        <v>0.8884223263007646</v>
+        <v>0.8976574856178202</v>
       </c>
       <c r="U21">
         <v>0.1185771881973717</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.160991866698153</v>
+        <v>3.002942273363246</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1394489272883455</v>
+        <v>0.1410752852581395</v>
       </c>
       <c r="C22">
-        <v>1906.371186194079</v>
+        <v>1844.977345315469</v>
       </c>
       <c r="D22">
-        <v>2277.131186194079</v>
+        <v>2238.260345315469</v>
       </c>
       <c r="E22">
-        <v>-144.8399999999999</v>
+        <v>-122.3169999999999</v>
       </c>
       <c r="F22">
-        <v>450.46</v>
+        <v>472.9830000000001</v>
       </c>
       <c r="G22">
         <v>79.7</v>
@@ -3085,45 +3085,45 @@
         <v>160.4</v>
       </c>
       <c r="M22">
-        <v>53.41428019538806</v>
+        <v>59.77426160515747</v>
       </c>
       <c r="N22">
-        <v>106.9857198046119</v>
+        <v>100.6257383948425</v>
       </c>
       <c r="O22">
-        <v>21.39714396092239</v>
+        <v>20.12514767896851</v>
       </c>
       <c r="P22">
-        <v>85.58857584368955</v>
+        <v>80.50059071587403</v>
       </c>
       <c r="Q22">
-        <v>173.4885758436895</v>
+        <v>168.400590715874</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1505957214709575</v>
+        <v>0.1517011615708621</v>
       </c>
       <c r="T22">
-        <v>0.8976574856178202</v>
+        <v>0.9071264464365736</v>
       </c>
       <c r="U22">
-        <v>0.1185771881973717</v>
+        <v>0.1263771881973717</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.09486175055789736</v>
+        <v>0.1011017505578974</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.002942273363246</v>
+        <v>2.683429216734319</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1410752852581395</v>
+        <v>0.1414536432279336</v>
       </c>
       <c r="C23">
-        <v>1844.977345315469</v>
+        <v>1813.600906893828</v>
       </c>
       <c r="D23">
-        <v>2238.260345315469</v>
+        <v>2229.406906893828</v>
       </c>
       <c r="E23">
-        <v>-122.317</v>
+        <v>-99.79399999999993</v>
       </c>
       <c r="F23">
-        <v>472.983</v>
+        <v>495.506</v>
       </c>
       <c r="G23">
         <v>79.7</v>
@@ -3167,28 +3167,28 @@
         <v>160.4</v>
       </c>
       <c r="M23">
-        <v>59.77426160515746</v>
+        <v>62.62065501492687</v>
       </c>
       <c r="N23">
-        <v>100.6257383948425</v>
+        <v>97.77934498507314</v>
       </c>
       <c r="O23">
-        <v>20.12514767896851</v>
+        <v>19.55586899701463</v>
       </c>
       <c r="P23">
-        <v>80.50059071587404</v>
+        <v>78.22347598805851</v>
       </c>
       <c r="Q23">
-        <v>168.400590715874</v>
+        <v>166.1234759880585</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1517011615708621</v>
+        <v>0.152834946288713</v>
       </c>
       <c r="T23">
-        <v>0.9071264464365736</v>
+        <v>0.9168382011224745</v>
       </c>
       <c r="U23">
         <v>0.1263771881973717</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.68342921673432</v>
+        <v>2.561455161428214</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1414536432279336</v>
+        <v>0.1425496011977276</v>
       </c>
       <c r="C24">
-        <v>1813.600906893828</v>
+        <v>1765.823681168073</v>
       </c>
       <c r="D24">
-        <v>2229.406906893828</v>
+        <v>2204.152681168073</v>
       </c>
       <c r="E24">
-        <v>-99.79399999999993</v>
+        <v>-77.27099999999984</v>
       </c>
       <c r="F24">
-        <v>495.506</v>
+        <v>518.0290000000001</v>
       </c>
       <c r="G24">
         <v>79.7</v>
@@ -3249,45 +3249,45 @@
         <v>160.4</v>
       </c>
       <c r="M24">
-        <v>62.62065501492687</v>
+        <v>67.48736152469627</v>
       </c>
       <c r="N24">
-        <v>97.77934498507314</v>
+        <v>92.91263847530374</v>
       </c>
       <c r="O24">
-        <v>19.55586899701463</v>
+        <v>18.58252769506075</v>
       </c>
       <c r="P24">
-        <v>78.22347598805851</v>
+        <v>74.33011078024299</v>
       </c>
       <c r="Q24">
-        <v>166.1234759880585</v>
+        <v>162.230110780243</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.152834946288713</v>
+        <v>0.1539981799602743</v>
       </c>
       <c r="T24">
-        <v>0.9168382011224745</v>
+        <v>0.9268022091768404</v>
       </c>
       <c r="U24">
-        <v>0.1263771881973717</v>
+        <v>0.1302771881973717</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.1011017505578974</v>
+        <v>0.1042217505578974</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.561455161428214</v>
+        <v>2.376741309427297</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1425496011977276</v>
+        <v>0.1429591591675217</v>
       </c>
       <c r="C25">
-        <v>1765.823681168073</v>
+        <v>1734.009449080949</v>
       </c>
       <c r="D25">
-        <v>2204.152681168073</v>
+        <v>2194.861449080949</v>
       </c>
       <c r="E25">
-        <v>-77.27099999999984</v>
+        <v>-54.74799999999982</v>
       </c>
       <c r="F25">
-        <v>518.0290000000001</v>
+        <v>540.5520000000001</v>
       </c>
       <c r="G25">
         <v>79.7</v>
@@ -3331,28 +3331,28 @@
         <v>160.4</v>
       </c>
       <c r="M25">
-        <v>67.48736152469627</v>
+        <v>70.42159463446568</v>
       </c>
       <c r="N25">
-        <v>92.91263847530374</v>
+        <v>89.97840536553433</v>
       </c>
       <c r="O25">
-        <v>18.58252769506075</v>
+        <v>17.99568107310687</v>
       </c>
       <c r="P25">
-        <v>74.33011078024299</v>
+        <v>71.98272429242746</v>
       </c>
       <c r="Q25">
-        <v>162.230110780243</v>
+        <v>159.8827242924275</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1539981799602743</v>
+        <v>0.1551920250442451</v>
       </c>
       <c r="T25">
-        <v>0.9268022091768404</v>
+        <v>0.937028427969479</v>
       </c>
       <c r="U25">
         <v>0.1302771881973717</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.376741309427297</v>
+        <v>2.277710421534493</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1429591591675217</v>
+        <v>0.1433687171373157</v>
       </c>
       <c r="C26">
-        <v>1734.009449080949</v>
+        <v>1702.273219416367</v>
       </c>
       <c r="D26">
-        <v>2194.861449080949</v>
+        <v>2185.648219416367</v>
       </c>
       <c r="E26">
-        <v>-54.74799999999993</v>
+        <v>-32.22499999999991</v>
       </c>
       <c r="F26">
-        <v>540.552</v>
+        <v>563.075</v>
       </c>
       <c r="G26">
         <v>79.7</v>
@@ -3413,28 +3413,28 @@
         <v>160.4</v>
       </c>
       <c r="M26">
-        <v>70.42159463446566</v>
+        <v>73.35582774423507</v>
       </c>
       <c r="N26">
-        <v>89.97840536553434</v>
+        <v>87.04417225576493</v>
       </c>
       <c r="O26">
-        <v>17.99568107310687</v>
+        <v>17.40883445115299</v>
       </c>
       <c r="P26">
-        <v>71.98272429242748</v>
+        <v>69.63533780461195</v>
       </c>
       <c r="Q26">
-        <v>159.8827242924275</v>
+        <v>157.535337804612</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1551920250442451</v>
+        <v>0.1564177059971218</v>
       </c>
       <c r="T26">
-        <v>0.9370284279694789</v>
+        <v>0.9475273459299213</v>
       </c>
       <c r="U26">
         <v>0.1302771881973717</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.277710421534493</v>
+        <v>2.186602004673114</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1433687171373157</v>
+        <v>0.1437782751071097</v>
       </c>
       <c r="C27">
-        <v>1702.273219416367</v>
+        <v>1670.614014002977</v>
       </c>
       <c r="D27">
-        <v>2185.648219416367</v>
+        <v>2176.512014002977</v>
       </c>
       <c r="E27">
-        <v>-32.22499999999991</v>
+        <v>-9.701999999999884</v>
       </c>
       <c r="F27">
-        <v>563.075</v>
+        <v>585.5980000000001</v>
       </c>
       <c r="G27">
         <v>79.7</v>
@@ -3495,28 +3495,28 @@
         <v>160.4</v>
       </c>
       <c r="M27">
-        <v>73.35582774423507</v>
+        <v>76.29006085400448</v>
       </c>
       <c r="N27">
-        <v>87.04417225576493</v>
+        <v>84.10993914599553</v>
       </c>
       <c r="O27">
-        <v>17.40883445115299</v>
+        <v>16.82198782919911</v>
       </c>
       <c r="P27">
-        <v>69.63533780461195</v>
+        <v>67.28795131679642</v>
       </c>
       <c r="Q27">
-        <v>157.535337804612</v>
+        <v>155.1879513167964</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1564177059971218</v>
+        <v>0.1576765134622384</v>
       </c>
       <c r="T27">
-        <v>0.9475273459299213</v>
+        <v>0.9583100184298351</v>
       </c>
       <c r="U27">
         <v>0.1302771881973717</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.186602004673114</v>
+        <v>2.102501927570302</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1437782751071097</v>
+        <v>0.1441878330769038</v>
       </c>
       <c r="C28">
-        <v>1670.614014002977</v>
+        <v>1639.030870956726</v>
       </c>
       <c r="D28">
-        <v>2176.512014002977</v>
+        <v>2167.451870956726</v>
       </c>
       <c r="E28">
-        <v>-9.701999999999884</v>
+        <v>12.82100000000014</v>
       </c>
       <c r="F28">
-        <v>585.5980000000001</v>
+        <v>608.1210000000001</v>
       </c>
       <c r="G28">
         <v>79.7</v>
@@ -3577,28 +3577,28 @@
         <v>160.4</v>
       </c>
       <c r="M28">
-        <v>76.29006085400448</v>
+        <v>79.22429396377389</v>
       </c>
       <c r="N28">
-        <v>84.10993914599553</v>
+        <v>81.17570603622612</v>
       </c>
       <c r="O28">
-        <v>16.82198782919911</v>
+        <v>16.23514120724522</v>
       </c>
       <c r="P28">
-        <v>67.28795131679642</v>
+        <v>64.9405648289809</v>
       </c>
       <c r="Q28">
-        <v>155.1879513167964</v>
+        <v>152.8405648289809</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1576765134622384</v>
+        <v>0.1589698088031117</v>
       </c>
       <c r="T28">
-        <v>0.9583100184298351</v>
+        <v>0.9693881066146781</v>
       </c>
       <c r="U28">
         <v>0.1302771881973717</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.102501927570302</v>
+        <v>2.024631485808438</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1441878330769038</v>
+        <v>0.1477781910466978</v>
       </c>
       <c r="C29">
-        <v>1639.030870956726</v>
+        <v>1540.198142188631</v>
       </c>
       <c r="D29">
-        <v>2167.451870956726</v>
+        <v>2091.142142188631</v>
       </c>
       <c r="E29">
-        <v>12.82100000000014</v>
+        <v>35.34400000000016</v>
       </c>
       <c r="F29">
-        <v>608.1210000000001</v>
+        <v>630.6440000000001</v>
       </c>
       <c r="G29">
         <v>79.7</v>
@@ -3659,45 +3659,45 @@
         <v>160.4</v>
       </c>
       <c r="M29">
-        <v>79.22429396377389</v>
+        <v>91.1136718735433</v>
       </c>
       <c r="N29">
-        <v>81.17570603622612</v>
+        <v>69.28632812645671</v>
       </c>
       <c r="O29">
-        <v>16.23514120724522</v>
+        <v>13.85726562529134</v>
       </c>
       <c r="P29">
-        <v>64.9405648289809</v>
+        <v>55.42906250116537</v>
       </c>
       <c r="Q29">
-        <v>152.8405648289809</v>
+        <v>143.3290625011654</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1589698088031117</v>
+        <v>0.1602990290145647</v>
       </c>
       <c r="T29">
-        <v>0.9693881066146781</v>
+        <v>0.9807739194713221</v>
       </c>
       <c r="U29">
-        <v>0.1302771881973717</v>
+        <v>0.1444771881973717</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.1042217505578974</v>
+        <v>0.1155817505578974</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.024631485808438</v>
+        <v>1.76043832612321</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1477781910466978</v>
+        <v>0.1483013490164919</v>
       </c>
       <c r="C30">
-        <v>1540.198142188631</v>
+        <v>1507.002134582827</v>
       </c>
       <c r="D30">
-        <v>2091.142142188631</v>
+        <v>2080.469134582827</v>
       </c>
       <c r="E30">
-        <v>35.34400000000016</v>
+        <v>57.86700000000019</v>
       </c>
       <c r="F30">
-        <v>630.6440000000001</v>
+        <v>653.1670000000001</v>
       </c>
       <c r="G30">
         <v>79.7</v>
@@ -3741,28 +3741,28 @@
         <v>160.4</v>
       </c>
       <c r="M30">
-        <v>91.1136718735433</v>
+        <v>94.3677315833127</v>
       </c>
       <c r="N30">
-        <v>69.28632812645671</v>
+        <v>66.0322684166873</v>
       </c>
       <c r="O30">
-        <v>13.85726562529134</v>
+        <v>13.20645368333746</v>
       </c>
       <c r="P30">
-        <v>55.42906250116537</v>
+        <v>52.82581473334984</v>
       </c>
       <c r="Q30">
-        <v>143.3290625011654</v>
+        <v>140.7258147333499</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1602990290145647</v>
+        <v>0.1616656920488755</v>
       </c>
       <c r="T30">
-        <v>0.9807739194713221</v>
+        <v>0.9924804594506885</v>
       </c>
       <c r="U30">
         <v>0.1444771881973717</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.76043832612321</v>
+        <v>1.699733556256893</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1483013490164919</v>
+        <v>0.1488245069862859</v>
       </c>
       <c r="C31">
-        <v>1507.002134582828</v>
+        <v>1473.914521943503</v>
       </c>
       <c r="D31">
-        <v>2080.469134582828</v>
+        <v>2069.904521943503</v>
       </c>
       <c r="E31">
-        <v>57.86700000000008</v>
+        <v>80.3900000000001</v>
       </c>
       <c r="F31">
-        <v>653.167</v>
+        <v>675.6900000000001</v>
       </c>
       <c r="G31">
         <v>79.7</v>
@@ -3823,28 +3823,28 @@
         <v>160.4</v>
       </c>
       <c r="M31">
-        <v>94.36773158331269</v>
+        <v>97.6217912930821</v>
       </c>
       <c r="N31">
-        <v>66.03226841668732</v>
+        <v>62.77820870691791</v>
       </c>
       <c r="O31">
-        <v>13.20645368333746</v>
+        <v>12.55564174138358</v>
       </c>
       <c r="P31">
-        <v>52.82581473334985</v>
+        <v>50.22256696553433</v>
       </c>
       <c r="Q31">
-        <v>140.7258147333499</v>
+        <v>138.1225669655343</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1616656920488755</v>
+        <v>0.1630714025984525</v>
       </c>
       <c r="T31">
-        <v>0.9924804594506885</v>
+        <v>1.004521472000894</v>
       </c>
       <c r="U31">
         <v>0.1444771881973717</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.699733556256893</v>
+        <v>1.64307577104833</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1488245069862859</v>
+        <v>0.14934766495608</v>
       </c>
       <c r="C32">
-        <v>1473.914521943503</v>
+        <v>1440.933661326107</v>
       </c>
       <c r="D32">
-        <v>2069.904521943503</v>
+        <v>2059.446661326107</v>
       </c>
       <c r="E32">
-        <v>80.3900000000001</v>
+        <v>102.9130000000001</v>
       </c>
       <c r="F32">
-        <v>675.6900000000001</v>
+        <v>698.2130000000001</v>
       </c>
       <c r="G32">
         <v>79.7</v>
@@ -3905,28 +3905,28 @@
         <v>160.4</v>
       </c>
       <c r="M32">
-        <v>97.6217912930821</v>
+        <v>100.8758510028515</v>
       </c>
       <c r="N32">
-        <v>62.77820870691791</v>
+        <v>59.5241489971485</v>
       </c>
       <c r="O32">
-        <v>12.55564174138358</v>
+        <v>11.9048297994297</v>
       </c>
       <c r="P32">
-        <v>50.22256696553433</v>
+        <v>47.6193191977188</v>
       </c>
       <c r="Q32">
-        <v>138.1225669655343</v>
+        <v>135.5193191977188</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1630714025984525</v>
+        <v>0.1645178583813504</v>
       </c>
       <c r="T32">
-        <v>1.004521472000894</v>
+        <v>1.016911499407627</v>
       </c>
       <c r="U32">
         <v>0.1444771881973717</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.64307577104833</v>
+        <v>1.590073326820964</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.14934766495608</v>
+        <v>0.149870822925874</v>
       </c>
       <c r="C33">
-        <v>1440.933661326107</v>
+        <v>1408.057942822036</v>
       </c>
       <c r="D33">
-        <v>2059.446661326107</v>
+        <v>2049.093942822037</v>
       </c>
       <c r="E33">
-        <v>102.9130000000001</v>
+        <v>125.4360000000001</v>
       </c>
       <c r="F33">
-        <v>698.2130000000001</v>
+        <v>720.7360000000001</v>
       </c>
       <c r="G33">
         <v>79.7</v>
@@ -3987,28 +3987,28 @@
         <v>160.4</v>
       </c>
       <c r="M33">
-        <v>100.8758510028515</v>
+        <v>104.1299107126209</v>
       </c>
       <c r="N33">
-        <v>59.5241489971485</v>
+        <v>56.27008928737909</v>
       </c>
       <c r="O33">
-        <v>11.9048297994297</v>
+        <v>11.25401785747582</v>
       </c>
       <c r="P33">
-        <v>47.6193191977188</v>
+        <v>45.01607142990328</v>
       </c>
       <c r="Q33">
-        <v>135.5193191977188</v>
+        <v>132.9160714299033</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1645178583813504</v>
+        <v>0.1660068569813924</v>
       </c>
       <c r="T33">
-        <v>1.016911499407627</v>
+        <v>1.029665939385147</v>
       </c>
       <c r="U33">
         <v>0.1444771881973717</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.590073326820964</v>
+        <v>1.540383535357809</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.149870822925874</v>
+        <v>0.165389180895668</v>
       </c>
       <c r="C34">
-        <v>1408.057942822036</v>
+        <v>1119.636530605377</v>
       </c>
       <c r="D34">
-        <v>2049.093942822037</v>
+        <v>1783.195530605377</v>
       </c>
       <c r="E34">
-        <v>125.4360000000001</v>
+        <v>147.9590000000002</v>
       </c>
       <c r="F34">
-        <v>720.7360000000001</v>
+        <v>743.2590000000001</v>
       </c>
       <c r="G34">
         <v>79.7</v>
@@ -4069,45 +4069,45 @@
         <v>160.4</v>
       </c>
       <c r="M34">
-        <v>104.1299107126209</v>
+        <v>149.6010816223903</v>
       </c>
       <c r="N34">
-        <v>56.27008928737909</v>
+        <v>10.79891837760968</v>
       </c>
       <c r="O34">
-        <v>11.25401785747582</v>
+        <v>2.159783675521936</v>
       </c>
       <c r="P34">
-        <v>45.01607142990328</v>
+        <v>8.639134702087745</v>
       </c>
       <c r="Q34">
-        <v>132.9160714299033</v>
+        <v>96.53913470208775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1660068569813924</v>
+        <v>0.1675403033008387</v>
       </c>
       <c r="T34">
-        <v>1.029665939385147</v>
+        <v>1.042801108914234</v>
       </c>
       <c r="U34">
-        <v>0.1444771881973717</v>
+        <v>0.2012771881973717</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.1155817505578974</v>
+        <v>0.1610217505578974</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.540383535357809</v>
+        <v>1.072184761370024</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.165389180895668</v>
+        <v>0.1663667388654621</v>
       </c>
       <c r="C35">
-        <v>1119.636530605377</v>
+        <v>1082.655339075542</v>
       </c>
       <c r="D35">
-        <v>1783.195530605377</v>
+        <v>1768.737339075542</v>
       </c>
       <c r="E35">
-        <v>147.9590000000002</v>
+        <v>170.4820000000002</v>
       </c>
       <c r="F35">
-        <v>743.2590000000001</v>
+        <v>765.7820000000002</v>
       </c>
       <c r="G35">
         <v>79.7</v>
@@ -4151,28 +4151,28 @@
         <v>160.4</v>
       </c>
       <c r="M35">
-        <v>149.6010816223903</v>
+        <v>154.1344477321597</v>
       </c>
       <c r="N35">
-        <v>10.79891837760968</v>
+        <v>6.265552267840292</v>
       </c>
       <c r="O35">
-        <v>2.159783675521936</v>
+        <v>1.253110453568058</v>
       </c>
       <c r="P35">
-        <v>8.639134702087745</v>
+        <v>5.012441814272234</v>
       </c>
       <c r="Q35">
-        <v>96.53913470208775</v>
+        <v>92.91244181427224</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1675403033008387</v>
+        <v>0.1691202176905712</v>
       </c>
       <c r="T35">
-        <v>1.042801108914234</v>
+        <v>1.056334313883597</v>
       </c>
       <c r="U35">
         <v>0.2012771881973717</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.072184761370024</v>
+        <v>1.040649915447376</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1663667388654621</v>
+        <v>0.1673442968352561</v>
       </c>
       <c r="C36">
-        <v>1082.655339075542</v>
+        <v>1045.906716588053</v>
       </c>
       <c r="D36">
-        <v>1768.737339075542</v>
+        <v>1754.511716588054</v>
       </c>
       <c r="E36">
-        <v>170.4820000000002</v>
+        <v>193.0050000000002</v>
       </c>
       <c r="F36">
-        <v>765.7820000000002</v>
+        <v>788.3050000000002</v>
       </c>
       <c r="G36">
         <v>79.7</v>
@@ -4233,28 +4233,28 @@
         <v>160.4</v>
       </c>
       <c r="M36">
-        <v>154.1344477321597</v>
+        <v>158.6678138419291</v>
       </c>
       <c r="N36">
-        <v>6.265552267840292</v>
+        <v>1.732186158070874</v>
       </c>
       <c r="O36">
-        <v>1.253110453568058</v>
+        <v>0.3464372316141748</v>
       </c>
       <c r="P36">
-        <v>5.012441814272234</v>
+        <v>1.385748926456699</v>
       </c>
       <c r="Q36">
-        <v>92.91244181427224</v>
+        <v>89.28574892645671</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1691202176905712</v>
+        <v>0.170748744830757</v>
       </c>
       <c r="T36">
-        <v>1.056334313883597</v>
+        <v>1.070283925159709</v>
       </c>
       <c r="U36">
         <v>0.2012771881973717</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.040649915447376</v>
+        <v>1.010917060720308</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1673442968352561</v>
+        <v>0.1686785169407543</v>
       </c>
       <c r="C37">
-        <v>1045.906716588053</v>
+        <v>1004.333154570508</v>
       </c>
       <c r="D37">
-        <v>1754.511716588054</v>
+        <v>1735.461154570508</v>
       </c>
       <c r="E37">
-        <v>193.0050000000002</v>
+        <v>215.5280000000002</v>
       </c>
       <c r="F37">
-        <v>788.3050000000002</v>
+        <v>810.8280000000002</v>
       </c>
       <c r="G37">
         <v>79.7</v>
@@ -4315,37 +4315,37 @@
         <v>160.4</v>
       </c>
       <c r="M37">
-        <v>158.6678138419291</v>
+        <v>163.2011799516985</v>
       </c>
       <c r="N37">
-        <v>1.732186158070874</v>
+        <v>-2.801179951698543</v>
       </c>
       <c r="O37">
-        <v>0.3464372316141748</v>
+        <v>-0.5602359903397087</v>
       </c>
       <c r="P37">
-        <v>1.385748926456699</v>
+        <v>-2.240943961358835</v>
       </c>
       <c r="Q37">
-        <v>89.28574892645671</v>
+        <v>85.65905603864117</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.170748744830757</v>
+        <v>0.1725967925523094</v>
       </c>
       <c r="T37">
-        <v>1.070283925159709</v>
+        <v>1.086113902259396</v>
       </c>
       <c r="U37">
         <v>0.2012771881973717</v>
       </c>
       <c r="V37">
-        <v>0.2</v>
+        <v>0.196567206251171</v>
       </c>
       <c r="W37">
-        <v>0.1610217505578974</v>
+        <v>0.1617126936313232</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.010917060720308</v>
+        <v>0.9828360312558549</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1686785169407543</v>
+        <v>0.1702332888227281</v>
       </c>
       <c r="C38">
-        <v>1004.333154570508</v>
+        <v>960.1258751392381</v>
       </c>
       <c r="D38">
-        <v>1735.461154570508</v>
+        <v>1713.776875139238</v>
       </c>
       <c r="E38">
-        <v>215.5280000000001</v>
+        <v>238.0510000000002</v>
       </c>
       <c r="F38">
-        <v>810.8280000000001</v>
+        <v>833.3510000000001</v>
       </c>
       <c r="G38">
         <v>79.7</v>
@@ -4397,37 +4397,37 @@
         <v>160.4</v>
       </c>
       <c r="M38">
-        <v>163.2011799516985</v>
+        <v>167.7345460614679</v>
       </c>
       <c r="N38">
-        <v>-2.801179951698515</v>
+        <v>-7.334546061467933</v>
       </c>
       <c r="O38">
-        <v>-0.5602359903397031</v>
+        <v>-1.466909212293587</v>
       </c>
       <c r="P38">
-        <v>-2.240943961358812</v>
+        <v>-5.867636849174346</v>
       </c>
       <c r="Q38">
-        <v>85.6590560386412</v>
+        <v>82.03236315082566</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1725967925523094</v>
+        <v>0.1746094400531397</v>
       </c>
       <c r="T38">
-        <v>1.086113902259396</v>
+        <v>1.103353805469862</v>
       </c>
       <c r="U38">
         <v>0.2012771881973717</v>
       </c>
       <c r="V38">
-        <v>0.1965672062511711</v>
+        <v>0.1912545790551934</v>
       </c>
       <c r="W38">
-        <v>0.1617126936313232</v>
+        <v>0.1627820042952704</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9828360312558552</v>
+        <v>0.956272895275967</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1702332888227281</v>
+        <v>0.1717880607047018</v>
       </c>
       <c r="C39">
-        <v>960.1258751392381</v>
+        <v>916.4537909915862</v>
       </c>
       <c r="D39">
-        <v>1713.776875139238</v>
+        <v>1692.627790991586</v>
       </c>
       <c r="E39">
-        <v>238.0510000000002</v>
+        <v>260.5740000000001</v>
       </c>
       <c r="F39">
-        <v>833.3510000000001</v>
+        <v>855.874</v>
       </c>
       <c r="G39">
         <v>79.7</v>
@@ -4479,37 +4479,37 @@
         <v>160.4</v>
       </c>
       <c r="M39">
-        <v>167.7345460614679</v>
+        <v>172.2679121712373</v>
       </c>
       <c r="N39">
-        <v>-7.334546061467933</v>
+        <v>-11.86791217123729</v>
       </c>
       <c r="O39">
-        <v>-1.466909212293587</v>
+        <v>-2.373582434247459</v>
       </c>
       <c r="P39">
-        <v>-5.867636849174346</v>
+        <v>-9.494329736989835</v>
       </c>
       <c r="Q39">
-        <v>82.03236315082566</v>
+        <v>78.40567026301017</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1746094400531397</v>
+        <v>0.1766870116669</v>
       </c>
       <c r="T39">
-        <v>1.103353805469862</v>
+        <v>1.121149834590344</v>
       </c>
       <c r="U39">
         <v>0.2012771881973717</v>
       </c>
       <c r="V39">
-        <v>0.1912545790551934</v>
+        <v>0.1862215638168989</v>
       </c>
       <c r="W39">
-        <v>0.1627820042952704</v>
+        <v>0.1637950354505889</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.956272895275967</v>
+        <v>0.9311078190844945</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1717880607047018</v>
+        <v>0.1733428325866755</v>
       </c>
       <c r="C40">
-        <v>916.4537909915862</v>
+        <v>873.2973297244263</v>
       </c>
       <c r="D40">
-        <v>1692.627790991586</v>
+        <v>1671.994329724426</v>
       </c>
       <c r="E40">
-        <v>260.5740000000001</v>
+        <v>283.0970000000001</v>
       </c>
       <c r="F40">
-        <v>855.874</v>
+        <v>878.397</v>
       </c>
       <c r="G40">
         <v>79.7</v>
@@ -4561,37 +4561,37 @@
         <v>160.4</v>
       </c>
       <c r="M40">
-        <v>172.2679121712373</v>
+        <v>176.8012782810067</v>
       </c>
       <c r="N40">
-        <v>-11.86791217123729</v>
+        <v>-16.40127828100671</v>
       </c>
       <c r="O40">
-        <v>-2.373582434247459</v>
+        <v>-3.280255656201343</v>
       </c>
       <c r="P40">
-        <v>-9.494329736989835</v>
+        <v>-13.12102262480537</v>
       </c>
       <c r="Q40">
-        <v>78.40567026301017</v>
+        <v>74.77897737519464</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1766870116669</v>
+        <v>0.1788327003827508</v>
       </c>
       <c r="T40">
-        <v>1.121149834590344</v>
+        <v>1.139529340075431</v>
       </c>
       <c r="U40">
         <v>0.2012771881973717</v>
       </c>
       <c r="V40">
-        <v>0.1862215638168989</v>
+        <v>0.1814466519241579</v>
       </c>
       <c r="W40">
-        <v>0.1637950354505889</v>
+        <v>0.16475611629025</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.9311078190844945</v>
+        <v>0.9072332596207895</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1733428325866755</v>
+        <v>0.1748976044686492</v>
       </c>
       <c r="C41">
-        <v>873.2973297244263</v>
+        <v>830.637861806415</v>
       </c>
       <c r="D41">
-        <v>1671.994329724426</v>
+        <v>1651.857861806415</v>
       </c>
       <c r="E41">
-        <v>283.0970000000001</v>
+        <v>305.6200000000001</v>
       </c>
       <c r="F41">
-        <v>878.397</v>
+        <v>900.9200000000001</v>
       </c>
       <c r="G41">
         <v>79.7</v>
@@ -4643,37 +4643,37 @@
         <v>160.4</v>
       </c>
       <c r="M41">
-        <v>176.8012782810067</v>
+        <v>181.3346443907761</v>
       </c>
       <c r="N41">
-        <v>-16.40127828100671</v>
+        <v>-20.93464439077613</v>
       </c>
       <c r="O41">
-        <v>-3.280255656201343</v>
+        <v>-4.186928878155226</v>
       </c>
       <c r="P41">
-        <v>-13.12102262480537</v>
+        <v>-16.7477155126209</v>
       </c>
       <c r="Q41">
-        <v>74.77897737519464</v>
+        <v>71.15228448737911</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1788327003827508</v>
+        <v>0.1810499120557967</v>
       </c>
       <c r="T41">
-        <v>1.139529340075431</v>
+        <v>1.158521495743355</v>
       </c>
       <c r="U41">
         <v>0.2012771881973717</v>
       </c>
       <c r="V41">
-        <v>0.1814466519241579</v>
+        <v>0.1769104856260539</v>
       </c>
       <c r="W41">
-        <v>0.16475611629025</v>
+        <v>0.165669143087928</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9072332596207895</v>
+        <v>0.8845524281302696</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1748976044686492</v>
+        <v>0.1764523763506229</v>
       </c>
       <c r="C42">
-        <v>830.637861806415</v>
+        <v>788.457644476808</v>
       </c>
       <c r="D42">
-        <v>1651.857861806415</v>
+        <v>1632.200644476808</v>
       </c>
       <c r="E42">
-        <v>305.6200000000001</v>
+        <v>328.1430000000001</v>
       </c>
       <c r="F42">
-        <v>900.9200000000001</v>
+        <v>923.4430000000001</v>
       </c>
       <c r="G42">
         <v>79.7</v>
@@ -4725,37 +4725,37 @@
         <v>160.4</v>
       </c>
       <c r="M42">
-        <v>181.3346443907761</v>
+        <v>185.8680105005455</v>
       </c>
       <c r="N42">
-        <v>-20.93464439077613</v>
+        <v>-25.46801050054552</v>
       </c>
       <c r="O42">
-        <v>-4.186928878155226</v>
+        <v>-5.093602100109104</v>
       </c>
       <c r="P42">
-        <v>-16.7477155126209</v>
+        <v>-20.37440840043642</v>
       </c>
       <c r="Q42">
-        <v>71.15228448737911</v>
+        <v>67.5255915995636</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1810499120557967</v>
+        <v>0.1833422834465729</v>
       </c>
       <c r="T42">
-        <v>1.158521495743355</v>
+        <v>1.178157453298327</v>
       </c>
       <c r="U42">
         <v>0.2012771881973717</v>
       </c>
       <c r="V42">
-        <v>0.1769104856260539</v>
+        <v>0.1725955957327356</v>
       </c>
       <c r="W42">
-        <v>0.165669143087928</v>
+        <v>0.1665376319930364</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8845524281302696</v>
+        <v>0.8629779786636778</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1764523763506229</v>
+        <v>0.1780071482325966</v>
       </c>
       <c r="C43">
-        <v>788.457644476808</v>
+        <v>746.7397696028165</v>
       </c>
       <c r="D43">
-        <v>1632.200644476808</v>
+        <v>1613.005769602817</v>
       </c>
       <c r="E43">
-        <v>328.1430000000001</v>
+        <v>350.6660000000002</v>
       </c>
       <c r="F43">
-        <v>923.4430000000001</v>
+        <v>945.9660000000001</v>
       </c>
       <c r="G43">
         <v>79.7</v>
@@ -4807,37 +4807,37 @@
         <v>160.4</v>
       </c>
       <c r="M43">
-        <v>185.8680105005455</v>
+        <v>190.4013766103149</v>
       </c>
       <c r="N43">
-        <v>-25.46801050054552</v>
+        <v>-30.00137661031494</v>
       </c>
       <c r="O43">
-        <v>-5.093602100109104</v>
+        <v>-6.000275322062987</v>
       </c>
       <c r="P43">
-        <v>-20.37440840043642</v>
+        <v>-24.00110128825195</v>
       </c>
       <c r="Q43">
-        <v>67.5255915995636</v>
+        <v>63.89889871174806</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1833422834465729</v>
+        <v>0.1857137021266862</v>
       </c>
       <c r="T43">
-        <v>1.178157453298327</v>
+        <v>1.198470512837954</v>
       </c>
       <c r="U43">
         <v>0.2012771881973717</v>
       </c>
       <c r="V43">
-        <v>0.1725955957327356</v>
+        <v>0.168486176786718</v>
       </c>
       <c r="W43">
-        <v>0.1665376319930364</v>
+        <v>0.1673647642836158</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8629779786636778</v>
+        <v>0.8424308839335901</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1780071482325966</v>
+        <v>0.1795619201145703</v>
       </c>
       <c r="C44">
-        <v>746.7397696028166</v>
+        <v>705.4681151734262</v>
       </c>
       <c r="D44">
-        <v>1613.005769602817</v>
+        <v>1594.257115173426</v>
       </c>
       <c r="E44">
-        <v>350.6660000000001</v>
+        <v>373.1890000000001</v>
       </c>
       <c r="F44">
-        <v>945.966</v>
+        <v>968.489</v>
       </c>
       <c r="G44">
         <v>79.7</v>
@@ -4889,37 +4889,37 @@
         <v>160.4</v>
       </c>
       <c r="M44">
-        <v>190.4013766103149</v>
+        <v>194.9347427200843</v>
       </c>
       <c r="N44">
-        <v>-30.00137661031491</v>
+        <v>-34.53474272008432</v>
       </c>
       <c r="O44">
-        <v>-6.000275322062982</v>
+        <v>-6.906948544016865</v>
       </c>
       <c r="P44">
-        <v>-24.00110128825192</v>
+        <v>-27.62779417606746</v>
       </c>
       <c r="Q44">
-        <v>63.89889871174808</v>
+        <v>60.27220582393254</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1857137021266862</v>
+        <v>0.188168328479786</v>
       </c>
       <c r="T44">
-        <v>1.198470512837954</v>
+        <v>1.219496311308795</v>
       </c>
       <c r="U44">
         <v>0.2012771881973717</v>
       </c>
       <c r="V44">
-        <v>0.1684861767867181</v>
+        <v>0.1645678936056316</v>
       </c>
       <c r="W44">
-        <v>0.1673647642836158</v>
+        <v>0.1681534253048659</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8424308839335902</v>
+        <v>0.8228394680281579</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1795619201145703</v>
+        <v>0.1811166919965441</v>
       </c>
       <c r="C45">
-        <v>705.4681151734262</v>
+        <v>664.6273001371884</v>
       </c>
       <c r="D45">
-        <v>1594.257115173426</v>
+        <v>1575.939300137188</v>
       </c>
       <c r="E45">
-        <v>373.1890000000001</v>
+        <v>395.7120000000001</v>
       </c>
       <c r="F45">
-        <v>968.489</v>
+        <v>991.0120000000001</v>
       </c>
       <c r="G45">
         <v>79.7</v>
@@ -4971,37 +4971,37 @@
         <v>160.4</v>
       </c>
       <c r="M45">
-        <v>194.9347427200843</v>
+        <v>199.4681088298537</v>
       </c>
       <c r="N45">
-        <v>-34.53474272008432</v>
+        <v>-39.06810882985371</v>
       </c>
       <c r="O45">
-        <v>-6.906948544016865</v>
+        <v>-7.813621765970743</v>
       </c>
       <c r="P45">
-        <v>-27.62779417606746</v>
+        <v>-31.25448706388297</v>
       </c>
       <c r="Q45">
-        <v>60.27220582393254</v>
+        <v>56.64551293611704</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.188168328479786</v>
+        <v>0.1907106200597821</v>
       </c>
       <c r="T45">
-        <v>1.219496311308795</v>
+        <v>1.241273031153595</v>
       </c>
       <c r="U45">
         <v>0.2012771881973717</v>
       </c>
       <c r="V45">
-        <v>0.1645678936056316</v>
+        <v>0.1608277142055036</v>
       </c>
       <c r="W45">
-        <v>0.1681534253048659</v>
+        <v>0.1689062380978774</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8228394680281579</v>
+        <v>0.804138571027518</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1811166919965441</v>
+        <v>0.2082787107889909</v>
       </c>
       <c r="C46">
-        <v>664.6273001371884</v>
+        <v>378.6501363380121</v>
       </c>
       <c r="D46">
-        <v>1575.939300137188</v>
+        <v>1312.485136338012</v>
       </c>
       <c r="E46">
-        <v>395.7120000000001</v>
+        <v>418.2350000000001</v>
       </c>
       <c r="F46">
-        <v>991.0120000000001</v>
+        <v>1013.535</v>
       </c>
       <c r="G46">
         <v>79.7</v>
@@ -5053,45 +5053,45 @@
         <v>160.4</v>
       </c>
       <c r="M46">
-        <v>199.4681088298537</v>
+        <v>258.7323649396231</v>
       </c>
       <c r="N46">
-        <v>-39.06810882985371</v>
+        <v>-98.33236493962309</v>
       </c>
       <c r="O46">
-        <v>-7.813621765970743</v>
+        <v>-19.66647298792462</v>
       </c>
       <c r="P46">
-        <v>-31.25448706388297</v>
+        <v>-78.66589195169847</v>
       </c>
       <c r="Q46">
-        <v>56.64551293611704</v>
+        <v>9.234108048301536</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1907106200597821</v>
+        <v>0.1957221711708202</v>
       </c>
       <c r="T46">
-        <v>1.241273031153595</v>
+        <v>1.284200894106724</v>
       </c>
       <c r="U46">
-        <v>0.2012771881973717</v>
+        <v>0.2552771881973717</v>
       </c>
       <c r="V46">
-        <v>0.1608277142055036</v>
+        <v>0.1239891267854568</v>
       </c>
       <c r="W46">
-        <v>0.1689062380978774</v>
+        <v>0.2236255925445328</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.804138571027518</v>
+        <v>0.619945633927284</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2082787107889909</v>
+        <v>0.2103734826709646</v>
       </c>
       <c r="C47">
-        <v>378.6501363380121</v>
+        <v>339.4211827755773</v>
       </c>
       <c r="D47">
-        <v>1312.485136338012</v>
+        <v>1295.779182775578</v>
       </c>
       <c r="E47">
-        <v>418.2350000000001</v>
+        <v>440.7580000000003</v>
       </c>
       <c r="F47">
-        <v>1013.535</v>
+        <v>1036.058</v>
       </c>
       <c r="G47">
         <v>79.7</v>
@@ -5135,37 +5135,37 @@
         <v>160.4</v>
       </c>
       <c r="M47">
-        <v>258.7323649396231</v>
+        <v>264.4819730493925</v>
       </c>
       <c r="N47">
-        <v>-98.33236493962309</v>
+        <v>-104.0819730493925</v>
       </c>
       <c r="O47">
-        <v>-19.66647298792462</v>
+        <v>-20.81639460987851</v>
       </c>
       <c r="P47">
-        <v>-78.66589195169847</v>
+        <v>-83.26557843951403</v>
       </c>
       <c r="Q47">
-        <v>9.234108048301536</v>
+        <v>4.634421560485976</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1957221711708202</v>
+        <v>0.1984985076739835</v>
       </c>
       <c r="T47">
-        <v>1.284200894106724</v>
+        <v>1.307982392145738</v>
       </c>
       <c r="U47">
         <v>0.2552771881973717</v>
       </c>
       <c r="V47">
-        <v>0.1239891267854568</v>
+        <v>0.1212937109857729</v>
       </c>
       <c r="W47">
-        <v>0.2236255925445328</v>
+        <v>0.2243136707108989</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.619945633927284</v>
+        <v>0.6064685549288646</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2103734826709646</v>
+        <v>0.2124682545529383</v>
       </c>
       <c r="C48">
-        <v>339.4211827755773</v>
+        <v>300.6121671536703</v>
       </c>
       <c r="D48">
-        <v>1295.779182775578</v>
+        <v>1279.49316715367</v>
       </c>
       <c r="E48">
-        <v>440.7580000000003</v>
+        <v>463.2810000000002</v>
       </c>
       <c r="F48">
-        <v>1036.058</v>
+        <v>1058.581</v>
       </c>
       <c r="G48">
         <v>79.7</v>
@@ -5217,37 +5217,37 @@
         <v>160.4</v>
       </c>
       <c r="M48">
-        <v>264.4819730493925</v>
+        <v>270.2315811591619</v>
       </c>
       <c r="N48">
-        <v>-104.0819730493925</v>
+        <v>-109.8315811591619</v>
       </c>
       <c r="O48">
-        <v>-20.81639460987851</v>
+        <v>-21.96631623183238</v>
       </c>
       <c r="P48">
-        <v>-83.26557843951403</v>
+        <v>-87.86526492732953</v>
       </c>
       <c r="Q48">
-        <v>4.634421560485976</v>
+        <v>0.03473507267047182</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1984985076739835</v>
+        <v>0.2013796115923606</v>
       </c>
       <c r="T48">
-        <v>1.307982392145738</v>
+        <v>1.332661305205092</v>
       </c>
       <c r="U48">
         <v>0.2552771881973717</v>
       </c>
       <c r="V48">
-        <v>0.1212937109857729</v>
+        <v>0.1187129937307565</v>
       </c>
       <c r="W48">
-        <v>0.2243136707108989</v>
+        <v>0.2249724689552919</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.6064685549288646</v>
+        <v>0.5935649686537825</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2124682545529383</v>
+        <v>0.2145630264349121</v>
       </c>
       <c r="C49">
-        <v>300.6121671536703</v>
+        <v>262.2074520271358</v>
       </c>
       <c r="D49">
-        <v>1279.49316715367</v>
+        <v>1263.611452027136</v>
       </c>
       <c r="E49">
-        <v>463.2810000000002</v>
+        <v>485.8040000000003</v>
       </c>
       <c r="F49">
-        <v>1058.581</v>
+        <v>1081.104</v>
       </c>
       <c r="G49">
         <v>79.7</v>
@@ -5299,37 +5299,37 @@
         <v>160.4</v>
       </c>
       <c r="M49">
-        <v>270.2315811591619</v>
+        <v>275.9811892689314</v>
       </c>
       <c r="N49">
-        <v>-109.8315811591619</v>
+        <v>-115.5811892689314</v>
       </c>
       <c r="O49">
-        <v>-21.96631623183238</v>
+        <v>-23.11623785378627</v>
       </c>
       <c r="P49">
-        <v>-87.86526492732953</v>
+        <v>-92.46495141514508</v>
       </c>
       <c r="Q49">
-        <v>0.03473507267047182</v>
+        <v>-4.564951415145075</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2013796115923606</v>
+        <v>0.204371527199906</v>
       </c>
       <c r="T49">
-        <v>1.332661305205092</v>
+        <v>1.358289407228266</v>
       </c>
       <c r="U49">
         <v>0.2552771881973717</v>
       </c>
       <c r="V49">
-        <v>0.1187129937307565</v>
+        <v>0.1162398063613657</v>
       </c>
       <c r="W49">
-        <v>0.2249724689552919</v>
+        <v>0.2256038172728353</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5935649686537825</v>
+        <v>0.5811990318068285</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.214563026434912</v>
+        <v>0.2166577983168858</v>
       </c>
       <c r="C50">
-        <v>262.2074520271362</v>
+        <v>224.1921668313669</v>
       </c>
       <c r="D50">
-        <v>1263.611452027136</v>
+        <v>1248.119166831367</v>
       </c>
       <c r="E50">
-        <v>485.8040000000001</v>
+        <v>508.3270000000002</v>
       </c>
       <c r="F50">
-        <v>1081.104</v>
+        <v>1103.627</v>
       </c>
       <c r="G50">
         <v>79.7</v>
@@ -5381,37 +5381,37 @@
         <v>160.4</v>
       </c>
       <c r="M50">
-        <v>275.9811892689313</v>
+        <v>281.7307973787007</v>
       </c>
       <c r="N50">
-        <v>-115.5811892689313</v>
+        <v>-121.3307973787007</v>
       </c>
       <c r="O50">
-        <v>-23.11623785378626</v>
+        <v>-24.26615947574015</v>
       </c>
       <c r="P50">
-        <v>-92.46495141514504</v>
+        <v>-97.06463790296058</v>
       </c>
       <c r="Q50">
-        <v>-4.564951415145032</v>
+        <v>-9.164637902960578</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.204371527199906</v>
+        <v>0.2074807728312767</v>
       </c>
       <c r="T50">
-        <v>1.358289407228266</v>
+        <v>1.384922532860193</v>
       </c>
       <c r="U50">
         <v>0.2552771881973717</v>
       </c>
       <c r="V50">
-        <v>0.1162398063613657</v>
+        <v>0.1138675654152154</v>
       </c>
       <c r="W50">
-        <v>0.2256038172728353</v>
+        <v>0.2262093962712952</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5811990318068286</v>
+        <v>0.5693378270760769</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2166577983168858</v>
+        <v>0.2187525701988595</v>
       </c>
       <c r="C51">
-        <v>224.1921668313669</v>
+        <v>186.5521614406714</v>
       </c>
       <c r="D51">
-        <v>1248.119166831367</v>
+        <v>1233.002161440671</v>
       </c>
       <c r="E51">
-        <v>508.3270000000002</v>
+        <v>530.8500000000001</v>
       </c>
       <c r="F51">
-        <v>1103.627</v>
+        <v>1126.15</v>
       </c>
       <c r="G51">
         <v>79.7</v>
@@ -5463,37 +5463,37 @@
         <v>160.4</v>
       </c>
       <c r="M51">
-        <v>281.7307973787007</v>
+        <v>287.4804054884701</v>
       </c>
       <c r="N51">
-        <v>-121.3307973787007</v>
+        <v>-127.0804054884701</v>
       </c>
       <c r="O51">
-        <v>-24.26615947574015</v>
+        <v>-25.41608109769403</v>
       </c>
       <c r="P51">
-        <v>-97.06463790296058</v>
+        <v>-101.6643243907761</v>
       </c>
       <c r="Q51">
-        <v>-9.164637902960578</v>
+        <v>-13.7643243907761</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2074807728312767</v>
+        <v>0.2107143882879022</v>
       </c>
       <c r="T51">
-        <v>1.384922532860193</v>
+        <v>1.412620983517397</v>
       </c>
       <c r="U51">
         <v>0.2552771881973717</v>
       </c>
       <c r="V51">
-        <v>0.1138675654152154</v>
+        <v>0.1115902141069111</v>
       </c>
       <c r="W51">
-        <v>0.2262093962712952</v>
+        <v>0.2267907521098167</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5693378270760769</v>
+        <v>0.5579510705345555</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2187525701988595</v>
+        <v>0.2208473420808332</v>
       </c>
       <c r="C52">
-        <v>186.5521614406714</v>
+        <v>149.2739630612182</v>
       </c>
       <c r="D52">
-        <v>1233.002161440671</v>
+        <v>1218.246963061218</v>
       </c>
       <c r="E52">
-        <v>530.8500000000001</v>
+        <v>553.373</v>
       </c>
       <c r="F52">
-        <v>1126.15</v>
+        <v>1148.673</v>
       </c>
       <c r="G52">
         <v>79.7</v>
@@ -5545,37 +5545,37 @@
         <v>160.4</v>
       </c>
       <c r="M52">
-        <v>287.4804054884701</v>
+        <v>293.2300135982395</v>
       </c>
       <c r="N52">
-        <v>-127.0804054884701</v>
+        <v>-132.8300135982395</v>
       </c>
       <c r="O52">
-        <v>-25.41608109769403</v>
+        <v>-26.5660027196479</v>
       </c>
       <c r="P52">
-        <v>-101.6643243907761</v>
+        <v>-106.2640108785916</v>
       </c>
       <c r="Q52">
-        <v>-13.7643243907761</v>
+        <v>-18.3640108785916</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2107143882879022</v>
+        <v>0.2140799880488798</v>
       </c>
       <c r="T52">
-        <v>1.412620983517397</v>
+        <v>1.441449983181017</v>
       </c>
       <c r="U52">
         <v>0.2552771881973717</v>
       </c>
       <c r="V52">
-        <v>0.1115902141069111</v>
+        <v>0.1094021706930501</v>
       </c>
       <c r="W52">
-        <v>0.2267907521098167</v>
+        <v>0.2273493096801609</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5579510705345555</v>
+        <v>0.5470108534652505</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2208473420808332</v>
+        <v>0.2229421139628069</v>
       </c>
       <c r="C53">
-        <v>149.2739630612182</v>
+        <v>112.3447361825192</v>
       </c>
       <c r="D53">
-        <v>1218.246963061218</v>
+        <v>1203.840736182519</v>
       </c>
       <c r="E53">
-        <v>553.373</v>
+        <v>575.8960000000002</v>
       </c>
       <c r="F53">
-        <v>1148.673</v>
+        <v>1171.196</v>
       </c>
       <c r="G53">
         <v>79.7</v>
@@ -5627,37 +5627,37 @@
         <v>160.4</v>
       </c>
       <c r="M53">
-        <v>293.2300135982395</v>
+        <v>298.9796217080089</v>
       </c>
       <c r="N53">
-        <v>-132.8300135982395</v>
+        <v>-138.5796217080089</v>
       </c>
       <c r="O53">
-        <v>-26.5660027196479</v>
+        <v>-27.71592434160179</v>
       </c>
       <c r="P53">
-        <v>-106.2640108785916</v>
+        <v>-110.8636973664072</v>
       </c>
       <c r="Q53">
-        <v>-18.3640108785916</v>
+        <v>-22.96369736640715</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2140799880488798</v>
+        <v>0.2175858211332315</v>
       </c>
       <c r="T53">
-        <v>1.441449983181017</v>
+        <v>1.471480191163955</v>
       </c>
       <c r="U53">
         <v>0.2552771881973717</v>
       </c>
       <c r="V53">
-        <v>0.1094021706930501</v>
+        <v>0.1072982827951068</v>
       </c>
       <c r="W53">
-        <v>0.2273493096801609</v>
+        <v>0.2278863842670304</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5470108534652505</v>
+        <v>0.5364914139755341</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2229421139628069</v>
+        <v>0.2250368858447806</v>
       </c>
       <c r="C54">
-        <v>112.3447361825192</v>
+        <v>75.75224533723917</v>
       </c>
       <c r="D54">
-        <v>1203.840736182519</v>
+        <v>1189.771245337239</v>
       </c>
       <c r="E54">
-        <v>575.8960000000002</v>
+        <v>598.4190000000001</v>
       </c>
       <c r="F54">
-        <v>1171.196</v>
+        <v>1193.719</v>
       </c>
       <c r="G54">
         <v>79.7</v>
@@ -5709,37 +5709,37 @@
         <v>160.4</v>
       </c>
       <c r="M54">
-        <v>298.9796217080089</v>
+        <v>304.7292298177783</v>
       </c>
       <c r="N54">
-        <v>-138.5796217080089</v>
+        <v>-144.3292298177783</v>
       </c>
       <c r="O54">
-        <v>-27.71592434160179</v>
+        <v>-28.86584596355567</v>
       </c>
       <c r="P54">
-        <v>-110.8636973664072</v>
+        <v>-115.4633838542227</v>
       </c>
       <c r="Q54">
-        <v>-22.96369736640715</v>
+        <v>-27.56338385422265</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2175858211332315</v>
+        <v>0.2212408386041513</v>
       </c>
       <c r="T54">
-        <v>1.471480191163955</v>
+        <v>1.502788280337656</v>
       </c>
       <c r="U54">
         <v>0.2552771881973717</v>
       </c>
       <c r="V54">
-        <v>0.1072982827951068</v>
+        <v>0.1052737868933123</v>
       </c>
       <c r="W54">
-        <v>0.2278863842670304</v>
+        <v>0.2284031918883576</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5364914139755341</v>
+        <v>0.5263689344665619</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2250368858447806</v>
+        <v>0.2271316577267543</v>
       </c>
       <c r="C55">
-        <v>75.75224533723917</v>
+        <v>39.4848204422276</v>
       </c>
       <c r="D55">
-        <v>1189.771245337239</v>
+        <v>1176.026820442228</v>
       </c>
       <c r="E55">
-        <v>598.4190000000001</v>
+        <v>620.9420000000002</v>
       </c>
       <c r="F55">
-        <v>1193.719</v>
+        <v>1216.242</v>
       </c>
       <c r="G55">
         <v>79.7</v>
@@ -5791,37 +5791,37 @@
         <v>160.4</v>
       </c>
       <c r="M55">
-        <v>304.7292298177783</v>
+        <v>310.4788379275478</v>
       </c>
       <c r="N55">
-        <v>-144.3292298177783</v>
+        <v>-150.0788379275478</v>
       </c>
       <c r="O55">
-        <v>-28.86584596355567</v>
+        <v>-30.01576758550955</v>
       </c>
       <c r="P55">
-        <v>-115.4633838542227</v>
+        <v>-120.0630703420382</v>
       </c>
       <c r="Q55">
-        <v>-27.56338385422265</v>
+        <v>-32.16307034203821</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2212408386041513</v>
+        <v>0.2250547698781546</v>
       </c>
       <c r="T55">
-        <v>1.502788280337656</v>
+        <v>1.535457590779779</v>
       </c>
       <c r="U55">
         <v>0.2552771881973717</v>
       </c>
       <c r="V55">
-        <v>0.1052737868933123</v>
+        <v>0.103324272321214</v>
       </c>
       <c r="W55">
-        <v>0.2284031918883576</v>
+        <v>0.2289008584866726</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5263689344665619</v>
+        <v>0.5166213616060698</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2271316577267543</v>
+        <v>0.229226429608728</v>
       </c>
       <c r="C56">
-        <v>39.4848204422276</v>
+        <v>3.531324514436164</v>
       </c>
       <c r="D56">
-        <v>1176.026820442228</v>
+        <v>1162.596324514436</v>
       </c>
       <c r="E56">
-        <v>620.9420000000002</v>
+        <v>643.4650000000001</v>
       </c>
       <c r="F56">
-        <v>1216.242</v>
+        <v>1238.765</v>
       </c>
       <c r="G56">
         <v>79.7</v>
@@ -5873,37 +5873,37 @@
         <v>160.4</v>
       </c>
       <c r="M56">
-        <v>310.4788379275478</v>
+        <v>316.2284460373172</v>
       </c>
       <c r="N56">
-        <v>-150.0788379275478</v>
+        <v>-155.8284460373171</v>
       </c>
       <c r="O56">
-        <v>-30.01576758550955</v>
+        <v>-31.16568920746343</v>
       </c>
       <c r="P56">
-        <v>-120.0630703420382</v>
+        <v>-124.6627568298537</v>
       </c>
       <c r="Q56">
-        <v>-32.16307034203821</v>
+        <v>-36.76275682985371</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2250547698781546</v>
+        <v>0.2290382092087802</v>
       </c>
       <c r="T56">
-        <v>1.535457590779779</v>
+        <v>1.569578870574886</v>
       </c>
       <c r="U56">
         <v>0.2552771881973717</v>
       </c>
       <c r="V56">
-        <v>0.103324272321214</v>
+        <v>0.101445649188101</v>
       </c>
       <c r="W56">
-        <v>0.2289008584866726</v>
+        <v>0.2293804281177762</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5166213616060698</v>
+        <v>0.507228245940505</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.229226429608728</v>
+        <v>0.2515087091838037</v>
       </c>
       <c r="C57">
-        <v>3.531324514436164</v>
+        <v>-144.9236131199561</v>
       </c>
       <c r="D57">
-        <v>1162.596324514436</v>
+        <v>1036.664386880044</v>
       </c>
       <c r="E57">
-        <v>643.4650000000001</v>
+        <v>665.9880000000003</v>
       </c>
       <c r="F57">
-        <v>1238.765</v>
+        <v>1261.288</v>
       </c>
       <c r="G57">
         <v>79.7</v>
@@ -5955,45 +5955,45 @@
         <v>160.4</v>
       </c>
       <c r="M57">
-        <v>316.2284460373172</v>
+        <v>366.1231341470866</v>
       </c>
       <c r="N57">
-        <v>-155.8284460373171</v>
+        <v>-205.7231341470866</v>
       </c>
       <c r="O57">
-        <v>-31.16568920746343</v>
+        <v>-41.14462682941732</v>
       </c>
       <c r="P57">
-        <v>-124.6627568298537</v>
+        <v>-164.5785073176693</v>
       </c>
       <c r="Q57">
-        <v>-36.76275682985371</v>
+        <v>-76.67850731766927</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2290382092087802</v>
+        <v>0.2345379587205752</v>
       </c>
       <c r="T57">
-        <v>1.569578870574886</v>
+        <v>1.616688535444686</v>
       </c>
       <c r="U57">
-        <v>0.2552771881973717</v>
+        <v>0.2902771881973717</v>
       </c>
       <c r="V57">
-        <v>0.101445649188101</v>
+        <v>0.08762079477641574</v>
       </c>
       <c r="W57">
-        <v>0.2293804281177762</v>
+        <v>0.2648428702620548</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.507228245940505</v>
+        <v>0.4381039738820787</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2515087091838037</v>
+        <v>0.2539534810657775</v>
       </c>
       <c r="C58">
-        <v>-144.9236131199561</v>
+        <v>-179.6222823958738</v>
       </c>
       <c r="D58">
-        <v>1036.664386880044</v>
+        <v>1024.488717604126</v>
       </c>
       <c r="E58">
-        <v>665.9880000000003</v>
+        <v>688.5110000000002</v>
       </c>
       <c r="F58">
-        <v>1261.288</v>
+        <v>1283.811</v>
       </c>
       <c r="G58">
         <v>79.7</v>
@@ -6037,37 +6037,37 @@
         <v>160.4</v>
       </c>
       <c r="M58">
-        <v>366.1231341470866</v>
+        <v>372.661047256856</v>
       </c>
       <c r="N58">
-        <v>-205.7231341470866</v>
+        <v>-212.261047256856</v>
       </c>
       <c r="O58">
-        <v>-41.14462682941732</v>
+        <v>-42.4522094513712</v>
       </c>
       <c r="P58">
-        <v>-164.5785073176693</v>
+        <v>-169.8088378054848</v>
       </c>
       <c r="Q58">
-        <v>-76.67850731766927</v>
+        <v>-81.90883780548481</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2345379587205752</v>
+        <v>0.2389272135745421</v>
       </c>
       <c r="T58">
-        <v>1.616688535444686</v>
+        <v>1.654285943245725</v>
       </c>
       <c r="U58">
         <v>0.2902771881973717</v>
       </c>
       <c r="V58">
-        <v>0.08762079477641574</v>
+        <v>0.0860835878505137</v>
       </c>
       <c r="W58">
-        <v>0.2648428702620548</v>
+        <v>0.2652890863661831</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4381039738820787</v>
+        <v>0.4304179392525684</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2539534810657775</v>
+        <v>0.2563982529477512</v>
       </c>
       <c r="C59">
-        <v>-179.6222823958738</v>
+        <v>-214.0382642945378</v>
       </c>
       <c r="D59">
-        <v>1024.488717604126</v>
+        <v>1012.595735705462</v>
       </c>
       <c r="E59">
-        <v>688.5110000000002</v>
+        <v>711.0340000000003</v>
       </c>
       <c r="F59">
-        <v>1283.811</v>
+        <v>1306.334</v>
       </c>
       <c r="G59">
         <v>79.7</v>
@@ -6119,37 +6119,37 @@
         <v>160.4</v>
       </c>
       <c r="M59">
-        <v>372.661047256856</v>
+        <v>379.1989603666254</v>
       </c>
       <c r="N59">
-        <v>-212.261047256856</v>
+        <v>-218.7989603666254</v>
       </c>
       <c r="O59">
-        <v>-42.4522094513712</v>
+        <v>-43.75979207332509</v>
       </c>
       <c r="P59">
-        <v>-169.8088378054848</v>
+        <v>-175.0391682933003</v>
       </c>
       <c r="Q59">
-        <v>-81.90883780548481</v>
+        <v>-87.13916829330034</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2389272135745421</v>
+        <v>0.2435254805644121</v>
       </c>
       <c r="T59">
-        <v>1.654285943245725</v>
+        <v>1.693673703799195</v>
       </c>
       <c r="U59">
         <v>0.2902771881973717</v>
       </c>
       <c r="V59">
-        <v>0.0860835878505137</v>
+        <v>0.0845993880599876</v>
       </c>
       <c r="W59">
-        <v>0.2652890863661831</v>
+        <v>0.2657199157081002</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4304179392525684</v>
+        <v>0.422996940299938</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2563982529477512</v>
+        <v>0.2588430248297249</v>
       </c>
       <c r="C60">
-        <v>-214.0382642945376</v>
+        <v>-248.1812907396081</v>
       </c>
       <c r="D60">
-        <v>1012.595735705462</v>
+        <v>1000.975709260392</v>
       </c>
       <c r="E60">
-        <v>711.0340000000001</v>
+        <v>733.557</v>
       </c>
       <c r="F60">
-        <v>1306.334</v>
+        <v>1328.857</v>
       </c>
       <c r="G60">
         <v>79.7</v>
@@ -6201,37 +6201,37 @@
         <v>160.4</v>
       </c>
       <c r="M60">
-        <v>379.1989603666254</v>
+        <v>385.7368734763947</v>
       </c>
       <c r="N60">
-        <v>-218.7989603666254</v>
+        <v>-225.3368734763947</v>
       </c>
       <c r="O60">
-        <v>-43.75979207332508</v>
+        <v>-45.06737469527895</v>
       </c>
       <c r="P60">
-        <v>-175.0391682933003</v>
+        <v>-180.2694987811158</v>
       </c>
       <c r="Q60">
-        <v>-87.13916829330029</v>
+        <v>-92.36949878111579</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2435254805644121</v>
+        <v>0.2483480532611051</v>
       </c>
       <c r="T60">
-        <v>1.693673703799194</v>
+        <v>1.734982818526004</v>
       </c>
       <c r="U60">
         <v>0.2902771881973717</v>
       </c>
       <c r="V60">
-        <v>0.08459938805998761</v>
+        <v>0.08316550012676749</v>
       </c>
       <c r="W60">
-        <v>0.2657199157081002</v>
+        <v>0.2661361406655455</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4229969402999381</v>
+        <v>0.4158275006338374</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2588430248297249</v>
+        <v>0.2612877967116987</v>
       </c>
       <c r="C61">
-        <v>-248.1812907396081</v>
+        <v>-282.0606520086992</v>
       </c>
       <c r="D61">
-        <v>1000.975709260392</v>
+        <v>989.6193479913009</v>
       </c>
       <c r="E61">
-        <v>733.557</v>
+        <v>756.0800000000002</v>
       </c>
       <c r="F61">
-        <v>1328.857</v>
+        <v>1351.38</v>
       </c>
       <c r="G61">
         <v>79.7</v>
@@ -6283,37 +6283,37 @@
         <v>160.4</v>
       </c>
       <c r="M61">
-        <v>385.7368734763947</v>
+        <v>392.2747865861642</v>
       </c>
       <c r="N61">
-        <v>-225.3368734763947</v>
+        <v>-231.8747865861642</v>
       </c>
       <c r="O61">
-        <v>-45.06737469527895</v>
+        <v>-46.37495731723283</v>
       </c>
       <c r="P61">
-        <v>-180.2694987811158</v>
+        <v>-185.4998292689313</v>
       </c>
       <c r="Q61">
-        <v>-92.36949878111579</v>
+        <v>-97.59982926893133</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2483480532611051</v>
+        <v>0.2534117545926327</v>
       </c>
       <c r="T61">
-        <v>1.734982818526004</v>
+        <v>1.778357388989154</v>
       </c>
       <c r="U61">
         <v>0.2902771881973717</v>
       </c>
       <c r="V61">
-        <v>0.08316550012676749</v>
+        <v>0.08177940845798803</v>
       </c>
       <c r="W61">
-        <v>0.2661361406655455</v>
+        <v>0.2665384914577426</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4158275006338374</v>
+        <v>0.4088970422899402</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2612877967116987</v>
+        <v>0.2637325685936724</v>
       </c>
       <c r="C62">
-        <v>-282.0606520086992</v>
+        <v>-315.6852215053502</v>
       </c>
       <c r="D62">
-        <v>989.6193479913009</v>
+        <v>978.5177784946497</v>
       </c>
       <c r="E62">
-        <v>756.0800000000002</v>
+        <v>778.6030000000001</v>
       </c>
       <c r="F62">
-        <v>1351.38</v>
+        <v>1373.903</v>
       </c>
       <c r="G62">
         <v>79.7</v>
@@ -6365,37 +6365,37 @@
         <v>160.4</v>
       </c>
       <c r="M62">
-        <v>392.2747865861642</v>
+        <v>398.8126996959336</v>
       </c>
       <c r="N62">
-        <v>-231.8747865861642</v>
+        <v>-238.4126996959336</v>
       </c>
       <c r="O62">
-        <v>-46.37495731723283</v>
+        <v>-47.68253993918672</v>
       </c>
       <c r="P62">
-        <v>-185.4998292689313</v>
+        <v>-190.7301597567469</v>
       </c>
       <c r="Q62">
-        <v>-97.59982926893133</v>
+        <v>-102.8301597567469</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2534117545926327</v>
+        <v>0.2587351329155207</v>
       </c>
       <c r="T62">
-        <v>1.778357388989154</v>
+        <v>1.823956296399132</v>
       </c>
       <c r="U62">
         <v>0.2902771881973717</v>
       </c>
       <c r="V62">
-        <v>0.08177940845798803</v>
+        <v>0.08043876241769314</v>
       </c>
       <c r="W62">
-        <v>0.2665384914577426</v>
+        <v>0.2669276504206873</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4088970422899402</v>
+        <v>0.4021938120884657</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2637325685936724</v>
+        <v>0.2661773404756461</v>
       </c>
       <c r="C63">
-        <v>-315.6852215053502</v>
+        <v>-349.0634788821383</v>
       </c>
       <c r="D63">
-        <v>978.5177784946497</v>
+        <v>967.662521117862</v>
       </c>
       <c r="E63">
-        <v>778.6030000000001</v>
+        <v>801.1260000000002</v>
       </c>
       <c r="F63">
-        <v>1373.903</v>
+        <v>1396.426</v>
       </c>
       <c r="G63">
         <v>79.7</v>
@@ -6447,37 +6447,37 @@
         <v>160.4</v>
       </c>
       <c r="M63">
-        <v>398.8126996959336</v>
+        <v>405.350612805703</v>
       </c>
       <c r="N63">
-        <v>-238.4126996959336</v>
+        <v>-244.950612805703</v>
       </c>
       <c r="O63">
-        <v>-47.68253993918672</v>
+        <v>-48.9901225611406</v>
       </c>
       <c r="P63">
-        <v>-190.7301597567469</v>
+        <v>-195.9604902445624</v>
       </c>
       <c r="Q63">
-        <v>-102.8301597567469</v>
+        <v>-108.0604902445624</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2587351329155207</v>
+        <v>0.2643386890448766</v>
       </c>
       <c r="T63">
-        <v>1.823956296399132</v>
+        <v>1.871955146304373</v>
       </c>
       <c r="U63">
         <v>0.2902771881973717</v>
       </c>
       <c r="V63">
-        <v>0.08043876241769314</v>
+        <v>0.07914136302385938</v>
       </c>
       <c r="W63">
-        <v>0.2669276504206873</v>
+        <v>0.2673042558686984</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4021938120884657</v>
+        <v>0.3957068151192968</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2661773404756461</v>
+        <v>0.2686221123576198</v>
       </c>
       <c r="C64">
-        <v>-349.0634788821383</v>
+        <v>-382.203531641569</v>
       </c>
       <c r="D64">
-        <v>967.662521117862</v>
+        <v>957.045468358431</v>
       </c>
       <c r="E64">
-        <v>801.1260000000002</v>
+        <v>823.6490000000001</v>
       </c>
       <c r="F64">
-        <v>1396.426</v>
+        <v>1418.949</v>
       </c>
       <c r="G64">
         <v>79.7</v>
@@ -6529,37 +6529,37 @@
         <v>160.4</v>
       </c>
       <c r="M64">
-        <v>405.350612805703</v>
+        <v>411.8885259154724</v>
       </c>
       <c r="N64">
-        <v>-244.950612805703</v>
+        <v>-251.4885259154724</v>
       </c>
       <c r="O64">
-        <v>-48.9901225611406</v>
+        <v>-50.29770518309448</v>
       </c>
       <c r="P64">
-        <v>-195.9604902445624</v>
+        <v>-201.1908207323779</v>
       </c>
       <c r="Q64">
-        <v>-108.0604902445624</v>
+        <v>-113.2908207323779</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2643386890448766</v>
+        <v>0.2702451401001434</v>
       </c>
       <c r="T64">
-        <v>1.871955146304373</v>
+        <v>1.922548528636923</v>
       </c>
       <c r="U64">
         <v>0.2902771881973717</v>
       </c>
       <c r="V64">
-        <v>0.07914136302385938</v>
+        <v>0.07788515091236956</v>
       </c>
       <c r="W64">
-        <v>0.2673042558686984</v>
+        <v>0.2676689055882011</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3957068151192968</v>
+        <v>0.3894257545618477</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2686221123576198</v>
+        <v>0.2710668842395935</v>
       </c>
       <c r="C65">
-        <v>-382.203531641569</v>
+        <v>-415.1131353303942</v>
       </c>
       <c r="D65">
-        <v>957.045468358431</v>
+        <v>946.658864669606</v>
       </c>
       <c r="E65">
-        <v>823.6490000000001</v>
+        <v>846.1720000000003</v>
       </c>
       <c r="F65">
-        <v>1418.949</v>
+        <v>1441.472</v>
       </c>
       <c r="G65">
         <v>79.7</v>
@@ -6611,37 +6611,37 @@
         <v>160.4</v>
       </c>
       <c r="M65">
-        <v>411.8885259154724</v>
+        <v>418.4264390252418</v>
       </c>
       <c r="N65">
-        <v>-251.4885259154724</v>
+        <v>-258.0264390252419</v>
       </c>
       <c r="O65">
-        <v>-50.29770518309448</v>
+        <v>-51.60528780504838</v>
       </c>
       <c r="P65">
-        <v>-201.1908207323779</v>
+        <v>-206.4211512201935</v>
       </c>
       <c r="Q65">
-        <v>-113.2908207323779</v>
+        <v>-118.5211512201935</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2702451401001434</v>
+        <v>0.2764797273251475</v>
       </c>
       <c r="T65">
-        <v>1.922548528636923</v>
+        <v>1.975952654432394</v>
       </c>
       <c r="U65">
         <v>0.2902771881973717</v>
       </c>
       <c r="V65">
-        <v>0.07788515091236956</v>
+        <v>0.07666819542936376</v>
       </c>
       <c r="W65">
-        <v>0.2676689055882011</v>
+        <v>0.2680221600039694</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3894257545618477</v>
+        <v>0.3833409771468187</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2710668842395935</v>
+        <v>0.2735116561215672</v>
       </c>
       <c r="C66">
-        <v>-415.1131353303942</v>
+        <v>-447.7997124330516</v>
       </c>
       <c r="D66">
-        <v>946.658864669606</v>
+        <v>936.4952875669485</v>
       </c>
       <c r="E66">
-        <v>846.1720000000003</v>
+        <v>868.6950000000002</v>
       </c>
       <c r="F66">
-        <v>1441.472</v>
+        <v>1463.995</v>
       </c>
       <c r="G66">
         <v>79.7</v>
@@ -6693,37 +6693,37 @@
         <v>160.4</v>
       </c>
       <c r="M66">
-        <v>418.4264390252418</v>
+        <v>424.9643521350112</v>
       </c>
       <c r="N66">
-        <v>-258.0264390252419</v>
+        <v>-264.5643521350112</v>
       </c>
       <c r="O66">
-        <v>-51.60528780504838</v>
+        <v>-52.91287042700224</v>
       </c>
       <c r="P66">
-        <v>-206.4211512201935</v>
+        <v>-211.6514817080089</v>
       </c>
       <c r="Q66">
-        <v>-118.5211512201935</v>
+        <v>-123.7514817080089</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2764797273251475</v>
+        <v>0.2830705766772946</v>
       </c>
       <c r="T66">
-        <v>1.975952654432394</v>
+        <v>2.032408444559034</v>
       </c>
       <c r="U66">
         <v>0.2902771881973717</v>
       </c>
       <c r="V66">
-        <v>0.07666819542936376</v>
+        <v>0.07548868473045049</v>
       </c>
       <c r="W66">
-        <v>0.2680221600039694</v>
+        <v>0.2683645450530986</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3833409771468187</v>
+        <v>0.3774434236522525</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2735116561215672</v>
+        <v>0.2759564280035409</v>
       </c>
       <c r="C67">
-        <v>-447.7997124330516</v>
+        <v>-480.2703700609731</v>
       </c>
       <c r="D67">
-        <v>936.4952875669485</v>
+        <v>926.5476299390272</v>
       </c>
       <c r="E67">
-        <v>868.6950000000002</v>
+        <v>891.2180000000003</v>
       </c>
       <c r="F67">
-        <v>1463.995</v>
+        <v>1486.518</v>
       </c>
       <c r="G67">
         <v>79.7</v>
@@ -6775,37 +6775,37 @@
         <v>160.4</v>
       </c>
       <c r="M67">
-        <v>424.9643521350112</v>
+        <v>431.5022652447806</v>
       </c>
       <c r="N67">
-        <v>-264.5643521350112</v>
+        <v>-271.1022652447806</v>
       </c>
       <c r="O67">
-        <v>-52.91287042700224</v>
+        <v>-54.22045304895612</v>
       </c>
       <c r="P67">
-        <v>-211.6514817080089</v>
+        <v>-216.8818121958245</v>
       </c>
       <c r="Q67">
-        <v>-123.7514817080089</v>
+        <v>-128.9818121958245</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2830705766772946</v>
+        <v>0.2900491230501561</v>
       </c>
       <c r="T67">
-        <v>2.032408444559034</v>
+        <v>2.092185163516652</v>
       </c>
       <c r="U67">
         <v>0.2902771881973717</v>
       </c>
       <c r="V67">
-        <v>0.07548868473045049</v>
+        <v>0.0743449167799891</v>
       </c>
       <c r="W67">
-        <v>0.2683645450530986</v>
+        <v>0.2686965547977089</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3774434236522525</v>
+        <v>0.3717245838999456</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2759564280035409</v>
+        <v>0.2784011998855147</v>
       </c>
       <c r="C68">
-        <v>-480.2703700609731</v>
+        <v>-512.5319165263365</v>
       </c>
       <c r="D68">
-        <v>926.5476299390272</v>
+        <v>916.8090834736636</v>
       </c>
       <c r="E68">
-        <v>891.2180000000003</v>
+        <v>913.7410000000002</v>
       </c>
       <c r="F68">
-        <v>1486.518</v>
+        <v>1509.041</v>
       </c>
       <c r="G68">
         <v>79.7</v>
@@ -6857,37 +6857,37 @@
         <v>160.4</v>
       </c>
       <c r="M68">
-        <v>431.5022652447806</v>
+        <v>438.0401783545501</v>
       </c>
       <c r="N68">
-        <v>-271.1022652447806</v>
+        <v>-277.64017835455</v>
       </c>
       <c r="O68">
-        <v>-54.22045304895612</v>
+        <v>-55.52803567091001</v>
       </c>
       <c r="P68">
-        <v>-216.8818121958245</v>
+        <v>-222.11214268364</v>
       </c>
       <c r="Q68">
-        <v>-128.9818121958245</v>
+        <v>-134.21214268364</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2900491230501561</v>
+        <v>0.2974506116274337</v>
       </c>
       <c r="T68">
-        <v>2.092185163516652</v>
+        <v>2.155584713926248</v>
       </c>
       <c r="U68">
         <v>0.2902771881973717</v>
       </c>
       <c r="V68">
-        <v>0.0743449167799891</v>
+        <v>0.07323529115640719</v>
       </c>
       <c r="W68">
-        <v>0.2686965547977089</v>
+        <v>0.269018653803674</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3717245838999456</v>
+        <v>0.3661764557820359</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2784011998855147</v>
+        <v>0.2808459717674884</v>
       </c>
       <c r="C69">
-        <v>-512.5319165263365</v>
+        <v>-544.590876881495</v>
       </c>
       <c r="D69">
-        <v>916.8090834736636</v>
+        <v>907.2731231185053</v>
       </c>
       <c r="E69">
-        <v>913.7410000000002</v>
+        <v>936.2640000000004</v>
       </c>
       <c r="F69">
-        <v>1509.041</v>
+        <v>1531.564</v>
       </c>
       <c r="G69">
         <v>79.7</v>
@@ -6939,37 +6939,37 @@
         <v>160.4</v>
       </c>
       <c r="M69">
-        <v>438.0401783545501</v>
+        <v>444.5780914643195</v>
       </c>
       <c r="N69">
-        <v>-277.64017835455</v>
+        <v>-284.1780914643194</v>
       </c>
       <c r="O69">
-        <v>-55.52803567091001</v>
+        <v>-56.83561829286389</v>
       </c>
       <c r="P69">
-        <v>-222.11214268364</v>
+        <v>-227.3424731714555</v>
       </c>
       <c r="Q69">
-        <v>-134.21214268364</v>
+        <v>-139.4424731714555</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2974506116274337</v>
+        <v>0.305314693240791</v>
       </c>
       <c r="T69">
-        <v>2.155584713926248</v>
+        <v>2.222946736236443</v>
       </c>
       <c r="U69">
         <v>0.2902771881973717</v>
       </c>
       <c r="V69">
-        <v>0.07323529115640719</v>
+        <v>0.07215830158057766</v>
       </c>
       <c r="W69">
-        <v>0.269018653803674</v>
+        <v>0.2693312793094637</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3661764557820359</v>
+        <v>0.3607915079028884</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2808459717674884</v>
+        <v>0.2832907436494622</v>
       </c>
       <c r="C70">
-        <v>-544.590876881495</v>
+        <v>-576.453507498613</v>
       </c>
       <c r="D70">
-        <v>907.2731231185053</v>
+        <v>897.9334925013871</v>
       </c>
       <c r="E70">
-        <v>936.2640000000004</v>
+        <v>958.7870000000003</v>
       </c>
       <c r="F70">
-        <v>1531.564</v>
+        <v>1554.087</v>
       </c>
       <c r="G70">
         <v>79.7</v>
@@ -7021,37 +7021,37 @@
         <v>160.4</v>
       </c>
       <c r="M70">
-        <v>444.5780914643195</v>
+        <v>451.1160045740888</v>
       </c>
       <c r="N70">
-        <v>-284.1780914643194</v>
+        <v>-290.7160045740889</v>
       </c>
       <c r="O70">
-        <v>-56.83561829286389</v>
+        <v>-58.14320091481778</v>
       </c>
       <c r="P70">
-        <v>-227.3424731714555</v>
+        <v>-232.5728036592711</v>
       </c>
       <c r="Q70">
-        <v>-139.4424731714555</v>
+        <v>-144.6728036592711</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.305314693240791</v>
+        <v>0.3136861349582359</v>
       </c>
       <c r="T70">
-        <v>2.222946736236443</v>
+        <v>2.294654695469877</v>
       </c>
       <c r="U70">
         <v>0.2902771881973717</v>
       </c>
       <c r="V70">
-        <v>0.07215830158057766</v>
+        <v>0.07111252909390263</v>
       </c>
       <c r="W70">
-        <v>0.2693312793094637</v>
+        <v>0.2696348432063899</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3607915079028884</v>
+        <v>0.3555626454695131</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2832907436494622</v>
+        <v>0.2857355155314358</v>
       </c>
       <c r="C71">
-        <v>-576.453507498613</v>
+        <v>-608.1258097579621</v>
       </c>
       <c r="D71">
-        <v>897.9334925013871</v>
+        <v>888.7841902420382</v>
       </c>
       <c r="E71">
-        <v>958.7870000000003</v>
+        <v>981.3100000000004</v>
       </c>
       <c r="F71">
-        <v>1554.087</v>
+        <v>1576.61</v>
       </c>
       <c r="G71">
         <v>79.7</v>
@@ -7103,37 +7103,37 @@
         <v>160.4</v>
       </c>
       <c r="M71">
-        <v>451.1160045740888</v>
+        <v>457.6539176838583</v>
       </c>
       <c r="N71">
-        <v>-290.7160045740889</v>
+        <v>-297.2539176838583</v>
       </c>
       <c r="O71">
-        <v>-58.14320091481778</v>
+        <v>-59.45078353677166</v>
       </c>
       <c r="P71">
-        <v>-232.5728036592711</v>
+        <v>-237.8031341470866</v>
       </c>
       <c r="Q71">
-        <v>-144.6728036592711</v>
+        <v>-149.9031341470866</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3136861349582359</v>
+        <v>0.3226156727901771</v>
       </c>
       <c r="T71">
-        <v>2.294654695469877</v>
+        <v>2.371143185318873</v>
       </c>
       <c r="U71">
         <v>0.2902771881973717</v>
       </c>
       <c r="V71">
-        <v>0.07111252909390263</v>
+        <v>0.07009663582113258</v>
       </c>
       <c r="W71">
-        <v>0.2696348432063899</v>
+        <v>0.2699297338491182</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3555626454695131</v>
+        <v>0.350483179105663</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2857355155314358</v>
+        <v>0.2881802874134095</v>
       </c>
       <c r="C72">
-        <v>-608.1258097579621</v>
+        <v>-639.6135429078173</v>
       </c>
       <c r="D72">
-        <v>888.7841902420382</v>
+        <v>879.8194570921829</v>
       </c>
       <c r="E72">
-        <v>981.3100000000004</v>
+        <v>1003.833</v>
       </c>
       <c r="F72">
-        <v>1576.61</v>
+        <v>1599.133</v>
       </c>
       <c r="G72">
         <v>79.7</v>
@@ -7185,37 +7185,37 @@
         <v>160.4</v>
       </c>
       <c r="M72">
-        <v>457.6539176838583</v>
+        <v>464.1918307936277</v>
       </c>
       <c r="N72">
-        <v>-297.2539176838583</v>
+        <v>-303.7918307936277</v>
       </c>
       <c r="O72">
-        <v>-59.45078353677166</v>
+        <v>-60.75836615872554</v>
       </c>
       <c r="P72">
-        <v>-237.8031341470866</v>
+        <v>-243.0334646349021</v>
       </c>
       <c r="Q72">
-        <v>-149.9031341470866</v>
+        <v>-155.1334646349021</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3226156727901771</v>
+        <v>0.3321610408174245</v>
       </c>
       <c r="T72">
-        <v>2.371143185318873</v>
+        <v>2.452906743433317</v>
       </c>
       <c r="U72">
         <v>0.2902771881973717</v>
       </c>
       <c r="V72">
-        <v>0.07009663582113258</v>
+        <v>0.06910935926027156</v>
       </c>
       <c r="W72">
-        <v>0.2699297338491182</v>
+        <v>0.2702163177131781</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.350483179105663</v>
+        <v>0.3455467963013578</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2881802874134095</v>
+        <v>0.2906250592953832</v>
       </c>
       <c r="C73">
-        <v>-639.6135429078171</v>
+        <v>-670.9222361538555</v>
       </c>
       <c r="D73">
-        <v>879.8194570921829</v>
+        <v>871.0337638461447</v>
       </c>
       <c r="E73">
-        <v>1003.833</v>
+        <v>1026.356</v>
       </c>
       <c r="F73">
-        <v>1599.133</v>
+        <v>1621.656</v>
       </c>
       <c r="G73">
         <v>79.7</v>
@@ -7267,37 +7267,37 @@
         <v>160.4</v>
       </c>
       <c r="M73">
-        <v>464.1918307936276</v>
+        <v>470.729743903397</v>
       </c>
       <c r="N73">
-        <v>-303.7918307936276</v>
+        <v>-310.329743903397</v>
       </c>
       <c r="O73">
-        <v>-60.75836615872552</v>
+        <v>-62.06594878067941</v>
       </c>
       <c r="P73">
-        <v>-243.0334646349021</v>
+        <v>-248.2637951227176</v>
       </c>
       <c r="Q73">
-        <v>-155.1334646349021</v>
+        <v>-160.3637951227176</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3321610408174245</v>
+        <v>0.3423882208466182</v>
       </c>
       <c r="T73">
-        <v>2.452906743433316</v>
+        <v>2.540510555698792</v>
       </c>
       <c r="U73">
         <v>0.2902771881973717</v>
       </c>
       <c r="V73">
-        <v>0.06910935926027156</v>
+        <v>0.06814950704832334</v>
       </c>
       <c r="W73">
-        <v>0.2702163177131781</v>
+        <v>0.2704949409143474</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3455467963013579</v>
+        <v>0.3407475352416168</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2906250592953832</v>
+        <v>0.293069831177357</v>
       </c>
       <c r="C74">
-        <v>-670.9222361538555</v>
+        <v>-702.0572000313791</v>
       </c>
       <c r="D74">
-        <v>871.0337638461447</v>
+        <v>862.4217999686209</v>
       </c>
       <c r="E74">
-        <v>1026.356</v>
+        <v>1048.879</v>
       </c>
       <c r="F74">
-        <v>1621.656</v>
+        <v>1644.179</v>
       </c>
       <c r="G74">
         <v>79.7</v>
@@ -7349,37 +7349,37 @@
         <v>160.4</v>
       </c>
       <c r="M74">
-        <v>470.729743903397</v>
+        <v>477.2676570131664</v>
       </c>
       <c r="N74">
-        <v>-310.329743903397</v>
+        <v>-316.8676570131664</v>
       </c>
       <c r="O74">
-        <v>-62.06594878067941</v>
+        <v>-63.37353140263329</v>
       </c>
       <c r="P74">
-        <v>-248.2637951227176</v>
+        <v>-253.4941256105331</v>
       </c>
       <c r="Q74">
-        <v>-160.3637951227176</v>
+        <v>-165.5941256105331</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3423882208466182</v>
+        <v>0.3533729697668633</v>
       </c>
       <c r="T74">
-        <v>2.540510555698792</v>
+        <v>2.634603539243191</v>
       </c>
       <c r="U74">
         <v>0.2902771881973717</v>
       </c>
       <c r="V74">
-        <v>0.06814950704832334</v>
+        <v>0.06721595215725044</v>
       </c>
       <c r="W74">
-        <v>0.2704949409143474</v>
+        <v>0.270765930603156</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3407475352416168</v>
+        <v>0.3360797607862521</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.293069831177357</v>
+        <v>0.2955146030593306</v>
       </c>
       <c r="C75">
-        <v>-702.0572000313791</v>
+        <v>-733.0235371095216</v>
       </c>
       <c r="D75">
-        <v>862.4217999686209</v>
+        <v>853.9784628904786</v>
       </c>
       <c r="E75">
-        <v>1048.879</v>
+        <v>1071.402</v>
       </c>
       <c r="F75">
-        <v>1644.179</v>
+        <v>1666.702</v>
       </c>
       <c r="G75">
         <v>79.7</v>
@@ -7431,37 +7431,37 @@
         <v>160.4</v>
       </c>
       <c r="M75">
-        <v>477.2676570131664</v>
+        <v>483.8055701229359</v>
       </c>
       <c r="N75">
-        <v>-316.8676570131664</v>
+        <v>-323.4055701229358</v>
       </c>
       <c r="O75">
-        <v>-63.37353140263329</v>
+        <v>-64.68111402458717</v>
       </c>
       <c r="P75">
-        <v>-253.4941256105331</v>
+        <v>-258.7244560983487</v>
       </c>
       <c r="Q75">
-        <v>-165.5941256105331</v>
+        <v>-170.8244560983487</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3533729697668633</v>
+        <v>0.3652026993732811</v>
       </c>
       <c r="T75">
-        <v>2.634603539243191</v>
+        <v>2.735934444598699</v>
       </c>
       <c r="U75">
         <v>0.2902771881973717</v>
       </c>
       <c r="V75">
-        <v>0.06721595215725044</v>
+        <v>0.06630762847944975</v>
       </c>
       <c r="W75">
-        <v>0.270765930603156</v>
+        <v>0.2710295962463211</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3360797607862521</v>
+        <v>0.3315381423972488</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2955146030593306</v>
+        <v>0.2979593749413044</v>
       </c>
       <c r="C76">
-        <v>-733.0235371095216</v>
+        <v>-763.8261520727636</v>
       </c>
       <c r="D76">
-        <v>853.9784628904786</v>
+        <v>845.6988479272364</v>
       </c>
       <c r="E76">
-        <v>1071.402</v>
+        <v>1093.925</v>
       </c>
       <c r="F76">
-        <v>1666.702</v>
+        <v>1689.225</v>
       </c>
       <c r="G76">
         <v>79.7</v>
@@ -7513,37 +7513,37 @@
         <v>160.4</v>
       </c>
       <c r="M76">
-        <v>483.8055701229359</v>
+        <v>490.3434832327052</v>
       </c>
       <c r="N76">
-        <v>-323.4055701229358</v>
+        <v>-329.9434832327053</v>
       </c>
       <c r="O76">
-        <v>-64.68111402458717</v>
+        <v>-65.98869664654106</v>
       </c>
       <c r="P76">
-        <v>-258.7244560983487</v>
+        <v>-263.9547865861642</v>
       </c>
       <c r="Q76">
-        <v>-170.8244560983487</v>
+        <v>-176.0547865861642</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3652026993732811</v>
+        <v>0.3779788073482124</v>
       </c>
       <c r="T76">
-        <v>2.735934444598699</v>
+        <v>2.845371822382647</v>
       </c>
       <c r="U76">
         <v>0.2902771881973717</v>
       </c>
       <c r="V76">
-        <v>0.06630762847944975</v>
+        <v>0.06542352676639042</v>
       </c>
       <c r="W76">
-        <v>0.2710295962463211</v>
+        <v>0.2712862308056684</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3315381423972488</v>
+        <v>0.327117633831952</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2979593749413044</v>
+        <v>0.3004041468232781</v>
       </c>
       <c r="C77">
-        <v>-763.8261520727636</v>
+        <v>-794.4697612216207</v>
       </c>
       <c r="D77">
-        <v>845.6988479272364</v>
+        <v>837.5782387783793</v>
       </c>
       <c r="E77">
-        <v>1093.925</v>
+        <v>1116.448</v>
       </c>
       <c r="F77">
-        <v>1689.225</v>
+        <v>1711.748</v>
       </c>
       <c r="G77">
         <v>79.7</v>
@@ -7595,37 +7595,37 @@
         <v>160.4</v>
       </c>
       <c r="M77">
-        <v>490.3434832327052</v>
+        <v>496.8813963424746</v>
       </c>
       <c r="N77">
-        <v>-329.9434832327053</v>
+        <v>-336.4813963424746</v>
       </c>
       <c r="O77">
-        <v>-65.98869664654106</v>
+        <v>-67.29627926849491</v>
       </c>
       <c r="P77">
-        <v>-263.9547865861642</v>
+        <v>-269.1851170739797</v>
       </c>
       <c r="Q77">
-        <v>-176.0547865861642</v>
+        <v>-181.2851170739796</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3779788073482124</v>
+        <v>0.3918195909877212</v>
       </c>
       <c r="T77">
-        <v>2.845371822382647</v>
+        <v>2.963928981648591</v>
       </c>
       <c r="U77">
         <v>0.2902771881973717</v>
       </c>
       <c r="V77">
-        <v>0.06542352676639042</v>
+        <v>0.06456269088788529</v>
       </c>
       <c r="W77">
-        <v>0.2712862308056684</v>
+        <v>0.2715361118239803</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.327117633831952</v>
+        <v>0.3228134544394264</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3004041468232781</v>
+        <v>0.3028489187052519</v>
       </c>
       <c r="C78">
-        <v>-794.4697612216207</v>
+        <v>-824.9589014311678</v>
       </c>
       <c r="D78">
-        <v>837.5782387783793</v>
+        <v>829.6120985688324</v>
       </c>
       <c r="E78">
-        <v>1116.448</v>
+        <v>1138.971</v>
       </c>
       <c r="F78">
-        <v>1711.748</v>
+        <v>1734.271</v>
       </c>
       <c r="G78">
         <v>79.7</v>
@@ -7677,37 +7677,37 @@
         <v>160.4</v>
       </c>
       <c r="M78">
-        <v>496.8813963424746</v>
+        <v>503.4193094522441</v>
       </c>
       <c r="N78">
-        <v>-336.4813963424746</v>
+        <v>-343.0193094522441</v>
       </c>
       <c r="O78">
-        <v>-67.29627926849491</v>
+        <v>-68.60386189044883</v>
       </c>
       <c r="P78">
-        <v>-269.1851170739797</v>
+        <v>-274.4154475617953</v>
       </c>
       <c r="Q78">
-        <v>-181.2851170739796</v>
+        <v>-186.5154475617953</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3918195909877212</v>
+        <v>0.4068639210306657</v>
       </c>
       <c r="T78">
-        <v>2.963928981648591</v>
+        <v>3.092795459111573</v>
       </c>
       <c r="U78">
         <v>0.2902771881973717</v>
       </c>
       <c r="V78">
-        <v>0.06456269088788529</v>
+        <v>0.0637242143828478</v>
       </c>
       <c r="W78">
-        <v>0.2715361118239803</v>
+        <v>0.2717795024262321</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3228134544394264</v>
+        <v>0.3186210719142389</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3028489187052519</v>
+        <v>0.3052936905872256</v>
       </c>
       <c r="C79">
-        <v>-824.9589014311678</v>
+        <v>-855.2979386031562</v>
       </c>
       <c r="D79">
-        <v>829.6120985688324</v>
+        <v>821.7960613968438</v>
       </c>
       <c r="E79">
-        <v>1138.971</v>
+        <v>1161.494</v>
       </c>
       <c r="F79">
-        <v>1734.271</v>
+        <v>1756.794</v>
       </c>
       <c r="G79">
         <v>79.7</v>
@@ -7759,37 +7759,37 @@
         <v>160.4</v>
       </c>
       <c r="M79">
-        <v>503.4193094522441</v>
+        <v>509.9572225620134</v>
       </c>
       <c r="N79">
-        <v>-343.0193094522441</v>
+        <v>-349.5572225620134</v>
       </c>
       <c r="O79">
-        <v>-68.60386189044883</v>
+        <v>-69.91144451240268</v>
       </c>
       <c r="P79">
-        <v>-274.4154475617953</v>
+        <v>-279.6457780496107</v>
       </c>
       <c r="Q79">
-        <v>-186.5154475617953</v>
+        <v>-191.7457780496107</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4068639210306657</v>
+        <v>0.4232759174411505</v>
       </c>
       <c r="T79">
-        <v>3.092795459111573</v>
+        <v>3.233377070889372</v>
       </c>
       <c r="U79">
         <v>0.2902771881973717</v>
       </c>
       <c r="V79">
-        <v>0.0637242143828478</v>
+        <v>0.06290723727537541</v>
       </c>
       <c r="W79">
-        <v>0.2717795024262321</v>
+        <v>0.2720166522438108</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3186210719142389</v>
+        <v>0.3145361863768771</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3052936905872256</v>
+        <v>0.3077384624691992</v>
       </c>
       <c r="C80">
-        <v>-855.2979386031562</v>
+        <v>-885.4910756448136</v>
       </c>
       <c r="D80">
-        <v>821.7960613968438</v>
+        <v>814.1259243551866</v>
       </c>
       <c r="E80">
-        <v>1161.494</v>
+        <v>1184.017</v>
       </c>
       <c r="F80">
-        <v>1756.794</v>
+        <v>1779.317</v>
       </c>
       <c r="G80">
         <v>79.7</v>
@@ -7841,37 +7841,37 @@
         <v>160.4</v>
       </c>
       <c r="M80">
-        <v>509.9572225620134</v>
+        <v>516.4951356717829</v>
       </c>
       <c r="N80">
-        <v>-349.5572225620134</v>
+        <v>-356.0951356717829</v>
       </c>
       <c r="O80">
-        <v>-69.91144451240268</v>
+        <v>-71.21902713435659</v>
       </c>
       <c r="P80">
-        <v>-279.6457780496107</v>
+        <v>-284.8761085374264</v>
       </c>
       <c r="Q80">
-        <v>-191.7457780496107</v>
+        <v>-196.9761085374264</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4232759174411505</v>
+        <v>0.4412509611288243</v>
       </c>
       <c r="T80">
-        <v>3.233377070889372</v>
+        <v>3.387347407598389</v>
       </c>
       <c r="U80">
         <v>0.2902771881973717</v>
       </c>
       <c r="V80">
-        <v>0.06290723727537541</v>
+        <v>0.06211094313264912</v>
       </c>
       <c r="W80">
-        <v>0.2720166522438108</v>
+        <v>0.2722477982685395</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3145361863768771</v>
+        <v>0.3105547156632456</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3077384624691992</v>
+        <v>0.310183234351173</v>
       </c>
       <c r="C81">
-        <v>-885.4910756448136</v>
+        <v>-915.5423600049547</v>
       </c>
       <c r="D81">
-        <v>814.1259243551866</v>
+        <v>806.5976399950454</v>
       </c>
       <c r="E81">
-        <v>1184.017</v>
+        <v>1206.54</v>
       </c>
       <c r="F81">
-        <v>1779.317</v>
+        <v>1801.84</v>
       </c>
       <c r="G81">
         <v>79.7</v>
@@ -7923,37 +7923,37 @@
         <v>160.4</v>
       </c>
       <c r="M81">
-        <v>516.4951356717829</v>
+        <v>523.0330487815522</v>
       </c>
       <c r="N81">
-        <v>-356.0951356717829</v>
+        <v>-362.6330487815522</v>
       </c>
       <c r="O81">
-        <v>-71.21902713435659</v>
+        <v>-72.52660975631045</v>
       </c>
       <c r="P81">
-        <v>-284.8761085374264</v>
+        <v>-290.1064390252418</v>
       </c>
       <c r="Q81">
-        <v>-196.9761085374264</v>
+        <v>-202.2064390252418</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4412509611288243</v>
+        <v>0.4610235091852656</v>
       </c>
       <c r="T81">
-        <v>3.387347407598389</v>
+        <v>3.556714777978309</v>
       </c>
       <c r="U81">
         <v>0.2902771881973717</v>
       </c>
       <c r="V81">
-        <v>0.06211094313264912</v>
+        <v>0.06133455634349103</v>
       </c>
       <c r="W81">
-        <v>0.2722477982685395</v>
+        <v>0.2724731656426498</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3105547156632456</v>
+        <v>0.306672781717455</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.310183234351173</v>
+        <v>0.3126280062331467</v>
       </c>
       <c r="C82">
-        <v>-915.5423600049547</v>
+        <v>-945.4556907958058</v>
       </c>
       <c r="D82">
-        <v>806.5976399950454</v>
+        <v>799.2073092041944</v>
       </c>
       <c r="E82">
-        <v>1206.54</v>
+        <v>1229.063</v>
       </c>
       <c r="F82">
-        <v>1801.84</v>
+        <v>1824.363</v>
       </c>
       <c r="G82">
         <v>79.7</v>
@@ -8005,37 +8005,37 @@
         <v>160.4</v>
       </c>
       <c r="M82">
-        <v>523.0330487815522</v>
+        <v>529.5709618913216</v>
       </c>
       <c r="N82">
-        <v>-362.6330487815522</v>
+        <v>-369.1709618913217</v>
       </c>
       <c r="O82">
-        <v>-72.52660975631045</v>
+        <v>-73.83419237826433</v>
       </c>
       <c r="P82">
-        <v>-290.1064390252418</v>
+        <v>-295.3367695130573</v>
       </c>
       <c r="Q82">
-        <v>-202.2064390252418</v>
+        <v>-207.4367695130573</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4610235091852656</v>
+        <v>0.4828773780897532</v>
       </c>
       <c r="T82">
-        <v>3.556714777978309</v>
+        <v>3.743910292608747</v>
       </c>
       <c r="U82">
         <v>0.2902771881973717</v>
       </c>
       <c r="V82">
-        <v>0.06133455634349103</v>
+        <v>0.06057733959850965</v>
       </c>
       <c r="W82">
-        <v>0.2724731656426498</v>
+        <v>0.272692968390239</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.306672781717455</v>
+        <v>0.3028866979925482</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3126280062331467</v>
+        <v>0.3150727781151205</v>
       </c>
       <c r="C83">
-        <v>-945.4556907958058</v>
+        <v>-975.2348255268664</v>
       </c>
       <c r="D83">
-        <v>799.2073092041944</v>
+        <v>791.9511744731337</v>
       </c>
       <c r="E83">
-        <v>1229.063</v>
+        <v>1251.586</v>
       </c>
       <c r="F83">
-        <v>1824.363</v>
+        <v>1846.886</v>
       </c>
       <c r="G83">
         <v>79.7</v>
@@ -8087,37 +8087,37 @@
         <v>160.4</v>
       </c>
       <c r="M83">
-        <v>529.5709618913216</v>
+        <v>536.1088750010911</v>
       </c>
       <c r="N83">
-        <v>-369.1709618913217</v>
+        <v>-375.7088750010911</v>
       </c>
       <c r="O83">
-        <v>-73.83419237826433</v>
+        <v>-75.14177500021822</v>
       </c>
       <c r="P83">
-        <v>-295.3367695130573</v>
+        <v>-300.5671000008729</v>
       </c>
       <c r="Q83">
-        <v>-207.4367695130573</v>
+        <v>-212.6671000008729</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4828773780897532</v>
+        <v>0.5071594546502951</v>
       </c>
       <c r="T83">
-        <v>3.743910292608747</v>
+        <v>3.951905308864788</v>
       </c>
       <c r="U83">
         <v>0.2902771881973717</v>
       </c>
       <c r="V83">
-        <v>0.06057733959850965</v>
+        <v>0.05983859155462538</v>
       </c>
       <c r="W83">
-        <v>0.272692968390239</v>
+        <v>0.2729074100952041</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3028866979925482</v>
+        <v>0.2991929577731268</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3150727781151205</v>
+        <v>0.3175175499970941</v>
       </c>
       <c r="C84">
-        <v>-975.2348255268664</v>
+        <v>-1004.883386475243</v>
       </c>
       <c r="D84">
-        <v>791.9511744731337</v>
+        <v>784.8256135247568</v>
       </c>
       <c r="E84">
-        <v>1251.586</v>
+        <v>1274.109</v>
       </c>
       <c r="F84">
-        <v>1846.886</v>
+        <v>1869.409</v>
       </c>
       <c r="G84">
         <v>79.7</v>
@@ -8169,37 +8169,37 @@
         <v>160.4</v>
       </c>
       <c r="M84">
-        <v>536.1088750010911</v>
+        <v>542.6467881108605</v>
       </c>
       <c r="N84">
-        <v>-375.7088750010911</v>
+        <v>-382.2467881108605</v>
       </c>
       <c r="O84">
-        <v>-75.14177500021822</v>
+        <v>-76.4493576221721</v>
       </c>
       <c r="P84">
-        <v>-300.5671000008729</v>
+        <v>-305.7974304886884</v>
       </c>
       <c r="Q84">
-        <v>-212.6671000008729</v>
+        <v>-217.8974304886884</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5071594546502951</v>
+        <v>0.5342982461003125</v>
       </c>
       <c r="T84">
-        <v>3.951905308864788</v>
+        <v>4.184370327033306</v>
       </c>
       <c r="U84">
         <v>0.2902771881973717</v>
       </c>
       <c r="V84">
-        <v>0.05983859155462538</v>
+        <v>0.05911764466842508</v>
       </c>
       <c r="W84">
-        <v>0.2729074100952041</v>
+        <v>0.2731166845301699</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2991929577731268</v>
+        <v>0.2955882233421253</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3175175499970941</v>
+        <v>0.3199623218790679</v>
       </c>
       <c r="C85">
-        <v>-1004.883386475243</v>
+        <v>-1034.404866715152</v>
       </c>
       <c r="D85">
-        <v>784.8256135247568</v>
+        <v>777.8271332848481</v>
       </c>
       <c r="E85">
-        <v>1274.109</v>
+        <v>1296.632</v>
       </c>
       <c r="F85">
-        <v>1869.409</v>
+        <v>1891.932</v>
       </c>
       <c r="G85">
         <v>79.7</v>
@@ -8251,37 +8251,37 @@
         <v>160.4</v>
       </c>
       <c r="M85">
-        <v>542.6467881108605</v>
+        <v>549.1847012206299</v>
       </c>
       <c r="N85">
-        <v>-382.2467881108605</v>
+        <v>-388.7847012206299</v>
       </c>
       <c r="O85">
-        <v>-76.4493576221721</v>
+        <v>-77.75694024412599</v>
       </c>
       <c r="P85">
-        <v>-305.7974304886884</v>
+        <v>-311.0277609765039</v>
       </c>
       <c r="Q85">
-        <v>-217.8974304886884</v>
+        <v>-223.1277609765039</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5342982461003125</v>
+        <v>0.5648293864815821</v>
       </c>
       <c r="T85">
-        <v>4.184370327033306</v>
+        <v>4.445893472472888</v>
       </c>
       <c r="U85">
         <v>0.2902771881973717</v>
       </c>
       <c r="V85">
-        <v>0.05911764466842508</v>
+        <v>0.05841386318427715</v>
       </c>
       <c r="W85">
-        <v>0.2731166845301699</v>
+        <v>0.2733209762404938</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2955882233421253</v>
+        <v>0.2920693159213857</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3199623218790678</v>
+        <v>0.3224070937610416</v>
       </c>
       <c r="C86">
-        <v>-1034.404866715152</v>
+        <v>-1063.802635827667</v>
       </c>
       <c r="D86">
-        <v>777.8271332848483</v>
+        <v>770.952364172333</v>
       </c>
       <c r="E86">
-        <v>1296.632</v>
+        <v>1319.155</v>
       </c>
       <c r="F86">
-        <v>1891.932</v>
+        <v>1914.455</v>
       </c>
       <c r="G86">
         <v>79.7</v>
@@ -8333,37 +8333,37 @@
         <v>160.4</v>
       </c>
       <c r="M86">
-        <v>549.1847012206298</v>
+        <v>555.7226143303993</v>
       </c>
       <c r="N86">
-        <v>-388.7847012206298</v>
+        <v>-395.3226143303993</v>
       </c>
       <c r="O86">
-        <v>-77.75694024412597</v>
+        <v>-79.06452286607987</v>
       </c>
       <c r="P86">
-        <v>-311.0277609765038</v>
+        <v>-316.2580914643195</v>
       </c>
       <c r="Q86">
-        <v>-223.1277609765038</v>
+        <v>-228.3580914643195</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5648293864815817</v>
+        <v>0.5994313455803539</v>
       </c>
       <c r="T86">
-        <v>4.445893472472885</v>
+        <v>4.742286370637744</v>
       </c>
       <c r="U86">
         <v>0.2902771881973717</v>
       </c>
       <c r="V86">
-        <v>0.05841386318427717</v>
+        <v>0.05772664126446213</v>
       </c>
       <c r="W86">
-        <v>0.2733209762404937</v>
+        <v>0.2735204610870453</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2920693159213857</v>
+        <v>0.2886332063223106</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3224070937610416</v>
+        <v>0.3248518656430153</v>
       </c>
       <c r="C87">
-        <v>-1063.802635827667</v>
+        <v>-1093.079945310338</v>
       </c>
       <c r="D87">
-        <v>770.952364172333</v>
+        <v>764.1980546896618</v>
       </c>
       <c r="E87">
-        <v>1319.155</v>
+        <v>1341.678</v>
       </c>
       <c r="F87">
-        <v>1914.455</v>
+        <v>1936.978</v>
       </c>
       <c r="G87">
         <v>79.7</v>
@@ -8415,37 +8415,37 @@
         <v>160.4</v>
       </c>
       <c r="M87">
-        <v>555.7226143303993</v>
+        <v>562.2605274401686</v>
       </c>
       <c r="N87">
-        <v>-395.3226143303993</v>
+        <v>-401.8605274401687</v>
       </c>
       <c r="O87">
-        <v>-79.06452286607987</v>
+        <v>-80.37210548803374</v>
       </c>
       <c r="P87">
-        <v>-316.2580914643195</v>
+        <v>-321.4884219521349</v>
       </c>
       <c r="Q87">
-        <v>-228.3580914643195</v>
+        <v>-233.5884219521349</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5994313455803539</v>
+        <v>0.6389764416932363</v>
       </c>
       <c r="T87">
-        <v>4.742286370637744</v>
+        <v>5.081021111397583</v>
       </c>
       <c r="U87">
         <v>0.2902771881973717</v>
       </c>
       <c r="V87">
-        <v>0.05772664126446213</v>
+        <v>0.05705540124975909</v>
       </c>
       <c r="W87">
-        <v>0.2735204610870453</v>
+        <v>0.2737153067511188</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2886332063223106</v>
+        <v>0.2852770062487954</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3248518656430153</v>
+        <v>0.3272966375249889</v>
       </c>
       <c r="C88">
-        <v>-1093.079945310338</v>
+        <v>-1122.23993370491</v>
       </c>
       <c r="D88">
-        <v>764.1980546896618</v>
+        <v>757.5610662950903</v>
       </c>
       <c r="E88">
-        <v>1341.678</v>
+        <v>1364.201</v>
       </c>
       <c r="F88">
-        <v>1936.978</v>
+        <v>1959.501</v>
       </c>
       <c r="G88">
         <v>79.7</v>
@@ -8497,37 +8497,37 @@
         <v>160.4</v>
       </c>
       <c r="M88">
-        <v>562.2605274401686</v>
+        <v>568.7984405499381</v>
       </c>
       <c r="N88">
-        <v>-401.8605274401687</v>
+        <v>-408.3984405499381</v>
       </c>
       <c r="O88">
-        <v>-80.37210548803374</v>
+        <v>-81.67968810998762</v>
       </c>
       <c r="P88">
-        <v>-321.4884219521349</v>
+        <v>-326.7187524399504</v>
       </c>
       <c r="Q88">
-        <v>-233.5884219521349</v>
+        <v>-238.8187524399504</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6389764416932363</v>
+        <v>0.6846053987465621</v>
       </c>
       <c r="T88">
-        <v>5.081021111397583</v>
+        <v>5.471868889197397</v>
       </c>
       <c r="U88">
         <v>0.2902771881973717</v>
       </c>
       <c r="V88">
-        <v>0.05705540124975909</v>
+        <v>0.05639959203999174</v>
       </c>
       <c r="W88">
-        <v>0.2737153067511188</v>
+        <v>0.273905673204524</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2852770062487954</v>
+        <v>0.2819979601999586</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3272966375249889</v>
+        <v>0.3297414094069627</v>
       </c>
       <c r="C89">
-        <v>-1122.23993370491</v>
+        <v>-1151.285631460142</v>
       </c>
       <c r="D89">
-        <v>757.5610662950903</v>
+        <v>751.0383685398581</v>
       </c>
       <c r="E89">
-        <v>1364.201</v>
+        <v>1386.724</v>
       </c>
       <c r="F89">
-        <v>1959.501</v>
+        <v>1982.024</v>
       </c>
       <c r="G89">
         <v>79.7</v>
@@ -8579,37 +8579,37 @@
         <v>160.4</v>
       </c>
       <c r="M89">
-        <v>568.7984405499381</v>
+        <v>575.3363536597075</v>
       </c>
       <c r="N89">
-        <v>-408.3984405499381</v>
+        <v>-414.9363536597075</v>
       </c>
       <c r="O89">
-        <v>-81.67968810998762</v>
+        <v>-82.98727073194151</v>
       </c>
       <c r="P89">
-        <v>-326.7187524399504</v>
+        <v>-331.949082927766</v>
       </c>
       <c r="Q89">
-        <v>-238.8187524399504</v>
+        <v>-244.049082927766</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6846053987465621</v>
+        <v>0.7378391819754424</v>
       </c>
       <c r="T89">
-        <v>5.471868889197397</v>
+        <v>5.927857963297181</v>
       </c>
       <c r="U89">
         <v>0.2902771881973717</v>
       </c>
       <c r="V89">
-        <v>0.05639959203999174</v>
+        <v>0.05575868758499183</v>
       </c>
       <c r="W89">
-        <v>0.273905673204524</v>
+        <v>0.2740917131476246</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2819979601999586</v>
+        <v>0.2787934379249591</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3297414094069627</v>
+        <v>0.3321861812889364</v>
       </c>
       <c r="C90">
-        <v>-1151.285631460142</v>
+        <v>-1180.219965545557</v>
       </c>
       <c r="D90">
-        <v>751.0383685398581</v>
+        <v>744.6270344544429</v>
       </c>
       <c r="E90">
-        <v>1386.724</v>
+        <v>1409.247</v>
       </c>
       <c r="F90">
-        <v>1982.024</v>
+        <v>2004.547</v>
       </c>
       <c r="G90">
         <v>79.7</v>
@@ -8661,37 +8661,37 @@
         <v>160.4</v>
       </c>
       <c r="M90">
-        <v>575.3363536597075</v>
+        <v>581.8742667694769</v>
       </c>
       <c r="N90">
-        <v>-414.9363536597075</v>
+        <v>-421.4742667694769</v>
       </c>
       <c r="O90">
-        <v>-82.98727073194151</v>
+        <v>-84.29485335389539</v>
       </c>
       <c r="P90">
-        <v>-331.949082927766</v>
+        <v>-337.1794134155815</v>
       </c>
       <c r="Q90">
-        <v>-244.049082927766</v>
+        <v>-249.2794134155815</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7378391819754424</v>
+        <v>0.8007518348823008</v>
       </c>
       <c r="T90">
-        <v>5.927857963297181</v>
+        <v>6.466754141778743</v>
       </c>
       <c r="U90">
         <v>0.2902771881973717</v>
       </c>
       <c r="V90">
-        <v>0.05575868758499183</v>
+        <v>0.05513218547729529</v>
       </c>
       <c r="W90">
-        <v>0.2740917131476246</v>
+        <v>0.2742735724178464</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2787934379249591</v>
+        <v>0.2756609273864764</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3321861812889364</v>
+        <v>0.3346309531709102</v>
       </c>
       <c r="C91">
-        <v>-1180.219965545557</v>
+        <v>-1209.045763830873</v>
       </c>
       <c r="D91">
-        <v>744.6270344544429</v>
+        <v>738.3242361691269</v>
       </c>
       <c r="E91">
-        <v>1409.247</v>
+        <v>1431.77</v>
       </c>
       <c r="F91">
-        <v>2004.547</v>
+        <v>2027.07</v>
       </c>
       <c r="G91">
         <v>79.7</v>
@@ -8743,37 +8743,37 @@
         <v>160.4</v>
       </c>
       <c r="M91">
-        <v>581.8742667694769</v>
+        <v>588.4121798792463</v>
       </c>
       <c r="N91">
-        <v>-421.4742667694769</v>
+        <v>-428.0121798792463</v>
       </c>
       <c r="O91">
-        <v>-84.29485335389539</v>
+        <v>-85.60243597584927</v>
       </c>
       <c r="P91">
-        <v>-337.1794134155815</v>
+        <v>-342.409743903397</v>
       </c>
       <c r="Q91">
-        <v>-249.2794134155815</v>
+        <v>-254.509743903397</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8007518348823008</v>
+        <v>0.8762470183705311</v>
       </c>
       <c r="T91">
-        <v>6.466754141778743</v>
+        <v>7.113429555956619</v>
       </c>
       <c r="U91">
         <v>0.2902771881973717</v>
       </c>
       <c r="V91">
-        <v>0.05513218547729529</v>
+        <v>0.05451960563865868</v>
       </c>
       <c r="W91">
-        <v>0.2742735724178464</v>
+        <v>0.2744513903709523</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2756609273864764</v>
+        <v>0.2725980281932934</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3346309531709102</v>
+        <v>0.3370757250528839</v>
       </c>
       <c r="C92">
-        <v>-1209.045763830873</v>
+        <v>-1237.765759244886</v>
       </c>
       <c r="D92">
-        <v>738.3242361691269</v>
+        <v>732.1272407551143</v>
       </c>
       <c r="E92">
-        <v>1431.77</v>
+        <v>1454.293</v>
       </c>
       <c r="F92">
-        <v>2027.07</v>
+        <v>2049.593</v>
       </c>
       <c r="G92">
         <v>79.7</v>
@@ -8825,37 +8825,37 @@
         <v>160.4</v>
       </c>
       <c r="M92">
-        <v>588.4121798792463</v>
+        <v>594.9500929890157</v>
       </c>
       <c r="N92">
-        <v>-428.0121798792463</v>
+        <v>-434.5500929890158</v>
       </c>
       <c r="O92">
-        <v>-85.60243597584927</v>
+        <v>-86.91001859780316</v>
       </c>
       <c r="P92">
-        <v>-342.409743903397</v>
+        <v>-347.6400743912126</v>
       </c>
       <c r="Q92">
-        <v>-254.509743903397</v>
+        <v>-259.7400743912126</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8762470183705311</v>
+        <v>0.9685189093005901</v>
       </c>
       <c r="T92">
-        <v>7.113429555956619</v>
+        <v>7.903810617729577</v>
       </c>
       <c r="U92">
         <v>0.2902771881973717</v>
       </c>
       <c r="V92">
-        <v>0.05451960563865868</v>
+        <v>0.05392048909317892</v>
       </c>
       <c r="W92">
-        <v>0.2744513903709523</v>
+        <v>0.2746253002371767</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2725980281932934</v>
+        <v>0.2696024454658945</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3370757250528839</v>
+        <v>0.3395204969348576</v>
       </c>
       <c r="C93">
-        <v>-1237.765759244886</v>
+        <v>-1266.382593726659</v>
       </c>
       <c r="D93">
-        <v>732.1272407551143</v>
+        <v>726.0334062733415</v>
       </c>
       <c r="E93">
-        <v>1454.293</v>
+        <v>1476.816</v>
       </c>
       <c r="F93">
-        <v>2049.593</v>
+        <v>2072.116</v>
       </c>
       <c r="G93">
         <v>79.7</v>
@@ -8907,37 +8907,37 @@
         <v>160.4</v>
       </c>
       <c r="M93">
-        <v>594.9500929890157</v>
+        <v>601.4880060987851</v>
       </c>
       <c r="N93">
-        <v>-434.5500929890158</v>
+        <v>-441.0880060987852</v>
       </c>
       <c r="O93">
-        <v>-86.91001859780316</v>
+        <v>-88.21760121975704</v>
       </c>
       <c r="P93">
-        <v>-347.6400743912126</v>
+        <v>-352.8704048790281</v>
       </c>
       <c r="Q93">
-        <v>-259.7400743912126</v>
+        <v>-264.9704048790281</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9685189093005901</v>
+        <v>1.083858772963164</v>
       </c>
       <c r="T93">
-        <v>7.903810617729577</v>
+        <v>8.891786944945776</v>
       </c>
       <c r="U93">
         <v>0.2902771881973717</v>
       </c>
       <c r="V93">
-        <v>0.05392048909317892</v>
+        <v>0.05333439682042697</v>
       </c>
       <c r="W93">
-        <v>0.2746253002371767</v>
+        <v>0.2747954294541353</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2696024454658945</v>
+        <v>0.2666719841021348</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3395204969348576</v>
+        <v>0.3419652688168313</v>
       </c>
       <c r="C94">
-        <v>-1266.382593726659</v>
+        <v>-1294.89882198101</v>
       </c>
       <c r="D94">
-        <v>726.0334062733415</v>
+        <v>720.0401780189896</v>
       </c>
       <c r="E94">
-        <v>1476.816</v>
+        <v>1499.339</v>
       </c>
       <c r="F94">
-        <v>2072.116</v>
+        <v>2094.639</v>
       </c>
       <c r="G94">
         <v>79.7</v>
@@ -8989,37 +8989,37 @@
         <v>160.4</v>
       </c>
       <c r="M94">
-        <v>601.4880060987851</v>
+        <v>608.0259192085545</v>
       </c>
       <c r="N94">
-        <v>-441.0880060987852</v>
+        <v>-447.6259192085545</v>
       </c>
       <c r="O94">
-        <v>-88.21760121975704</v>
+        <v>-89.5251838417109</v>
       </c>
       <c r="P94">
-        <v>-352.8704048790281</v>
+        <v>-358.1007353668436</v>
       </c>
       <c r="Q94">
-        <v>-264.9704048790281</v>
+        <v>-270.2007353668436</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.083858772963164</v>
+        <v>1.232152883386474</v>
       </c>
       <c r="T94">
-        <v>8.891786944945776</v>
+        <v>10.16204222279517</v>
       </c>
       <c r="U94">
         <v>0.2902771881973717</v>
       </c>
       <c r="V94">
-        <v>0.05333439682042697</v>
+        <v>0.05276090868257292</v>
       </c>
       <c r="W94">
-        <v>0.2747954294541353</v>
+        <v>0.2749618999782562</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2666719841021348</v>
+        <v>0.2638045434128645</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3419652688168313</v>
+        <v>0.3444100406988051</v>
       </c>
       <c r="C95">
-        <v>-1294.89882198101</v>
+        <v>-1323.316915049525</v>
       </c>
       <c r="D95">
-        <v>720.0401780189896</v>
+        <v>714.1450849504757</v>
       </c>
       <c r="E95">
-        <v>1499.339</v>
+        <v>1521.862</v>
       </c>
       <c r="F95">
-        <v>2094.639</v>
+        <v>2117.162</v>
       </c>
       <c r="G95">
         <v>79.7</v>
@@ -9071,37 +9071,37 @@
         <v>160.4</v>
       </c>
       <c r="M95">
-        <v>608.0259192085545</v>
+        <v>614.5638323183239</v>
       </c>
       <c r="N95">
-        <v>-447.6259192085545</v>
+        <v>-454.1638323183239</v>
       </c>
       <c r="O95">
-        <v>-89.5251838417109</v>
+        <v>-90.83276646366478</v>
       </c>
       <c r="P95">
-        <v>-358.1007353668436</v>
+        <v>-363.3310658546591</v>
       </c>
       <c r="Q95">
-        <v>-270.2007353668436</v>
+        <v>-275.4310658546591</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.232152883386474</v>
+        <v>1.429878363950886</v>
       </c>
       <c r="T95">
-        <v>10.16204222279517</v>
+        <v>11.85571592659437</v>
       </c>
       <c r="U95">
         <v>0.2902771881973717</v>
       </c>
       <c r="V95">
-        <v>0.05276090868257292</v>
+        <v>0.05219962241999235</v>
       </c>
       <c r="W95">
-        <v>0.2749618999782562</v>
+        <v>0.2751248285763319</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2638045434128645</v>
+        <v>0.2609981120999617</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3444100406988051</v>
+        <v>0.3468548125807788</v>
       </c>
       <c r="C96">
-        <v>-1323.316915049525</v>
+        <v>-1351.639263707564</v>
       </c>
       <c r="D96">
-        <v>714.1450849504757</v>
+        <v>708.3457362924363</v>
       </c>
       <c r="E96">
-        <v>1521.862</v>
+        <v>1544.385</v>
       </c>
       <c r="F96">
-        <v>2117.162</v>
+        <v>2139.685</v>
       </c>
       <c r="G96">
         <v>79.7</v>
@@ -9153,37 +9153,37 @@
         <v>160.4</v>
       </c>
       <c r="M96">
-        <v>614.5638323183239</v>
+        <v>621.1017454280934</v>
       </c>
       <c r="N96">
-        <v>-454.1638323183239</v>
+        <v>-460.7017454280934</v>
       </c>
       <c r="O96">
-        <v>-90.83276646366478</v>
+        <v>-92.14034908561869</v>
       </c>
       <c r="P96">
-        <v>-363.3310658546591</v>
+        <v>-368.5613963424747</v>
       </c>
       <c r="Q96">
-        <v>-275.4310658546591</v>
+        <v>-280.6613963424747</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.429878363950886</v>
+        <v>1.706694036741064</v>
       </c>
       <c r="T96">
-        <v>11.85571592659437</v>
+        <v>14.22685911191325</v>
       </c>
       <c r="U96">
         <v>0.2902771881973717</v>
       </c>
       <c r="V96">
-        <v>0.05219962241999235</v>
+        <v>0.05165015271030822</v>
       </c>
       <c r="W96">
-        <v>0.2751248285763319</v>
+        <v>0.2752843270986586</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2609981120999617</v>
+        <v>0.258250763551541</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3468548125807788</v>
+        <v>0.3492995844627525</v>
       </c>
       <c r="C97">
-        <v>-1351.639263707564</v>
+        <v>-1379.868181697103</v>
       </c>
       <c r="D97">
-        <v>708.3457362924363</v>
+        <v>702.639818302897</v>
       </c>
       <c r="E97">
-        <v>1544.385</v>
+        <v>1566.908000000001</v>
       </c>
       <c r="F97">
-        <v>2139.685</v>
+        <v>2162.208000000001</v>
       </c>
       <c r="G97">
         <v>79.7</v>
@@ -9235,37 +9235,37 @@
         <v>160.4</v>
       </c>
       <c r="M97">
-        <v>621.1017454280934</v>
+        <v>627.6396585378628</v>
       </c>
       <c r="N97">
-        <v>-460.7017454280934</v>
+        <v>-467.2396585378629</v>
       </c>
       <c r="O97">
-        <v>-92.14034908561869</v>
+        <v>-93.44793170757258</v>
       </c>
       <c r="P97">
-        <v>-368.5613963424747</v>
+        <v>-373.7917268302903</v>
       </c>
       <c r="Q97">
-        <v>-280.6613963424747</v>
+        <v>-285.8917268302903</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.706694036741064</v>
+        <v>2.121917545926331</v>
       </c>
       <c r="T97">
-        <v>14.22685911191325</v>
+        <v>17.78357388989157</v>
       </c>
       <c r="U97">
         <v>0.2902771881973717</v>
       </c>
       <c r="V97">
-        <v>0.05165015271030822</v>
+        <v>0.05111213028624251</v>
       </c>
       <c r="W97">
-        <v>0.2752843270986586</v>
+        <v>0.2754405027351035</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.258250763551541</v>
+        <v>0.2555606514312124</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3492995844627524</v>
+        <v>0.3517443563447261</v>
       </c>
       <c r="C98">
-        <v>-1379.868181697103</v>
+        <v>-1408.005908804559</v>
       </c>
       <c r="D98">
-        <v>702.6398183028973</v>
+        <v>697.0250911954408</v>
       </c>
       <c r="E98">
-        <v>1566.908</v>
+        <v>1589.431</v>
       </c>
       <c r="F98">
-        <v>2162.208</v>
+        <v>2184.731</v>
       </c>
       <c r="G98">
         <v>79.7</v>
@@ -9317,37 +9317,37 @@
         <v>160.4</v>
       </c>
       <c r="M98">
-        <v>627.6396585378627</v>
+        <v>634.1775716476321</v>
       </c>
       <c r="N98">
-        <v>-467.2396585378627</v>
+        <v>-473.7775716476322</v>
       </c>
       <c r="O98">
-        <v>-93.44793170757255</v>
+        <v>-94.75551432952643</v>
       </c>
       <c r="P98">
-        <v>-373.7917268302902</v>
+        <v>-379.0220573181057</v>
       </c>
       <c r="Q98">
-        <v>-285.8917268302902</v>
+        <v>-291.1220573181057</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.121917545926325</v>
+        <v>2.813956727901767</v>
       </c>
       <c r="T98">
-        <v>17.78357388989153</v>
+        <v>23.7114318531887</v>
       </c>
       <c r="U98">
         <v>0.2902771881973717</v>
       </c>
       <c r="V98">
-        <v>0.05111213028624251</v>
+        <v>0.05058520110803383</v>
       </c>
       <c r="W98">
-        <v>0.2754405027351035</v>
+        <v>0.275593458255333</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2555606514312125</v>
+        <v>0.2529260055401691</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3517443563447261</v>
+        <v>0.3541891282266999</v>
       </c>
       <c r="C99">
-        <v>-1408.005908804559</v>
+        <v>-1436.054613792227</v>
       </c>
       <c r="D99">
-        <v>697.0250911954408</v>
+        <v>691.499386207773</v>
       </c>
       <c r="E99">
-        <v>1589.431</v>
+        <v>1611.954</v>
       </c>
       <c r="F99">
-        <v>2184.731</v>
+        <v>2207.254</v>
       </c>
       <c r="G99">
         <v>79.7</v>
@@ -9399,37 +9399,37 @@
         <v>160.4</v>
       </c>
       <c r="M99">
-        <v>634.1775716476321</v>
+        <v>640.7154847574016</v>
       </c>
       <c r="N99">
-        <v>-473.7775716476322</v>
+        <v>-480.3154847574016</v>
       </c>
       <c r="O99">
-        <v>-94.75551432952643</v>
+        <v>-96.06309695148032</v>
       </c>
       <c r="P99">
-        <v>-379.0220573181057</v>
+        <v>-384.2523878059213</v>
       </c>
       <c r="Q99">
-        <v>-291.1220573181057</v>
+        <v>-296.3523878059212</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.813956727901767</v>
+        <v>4.198035091852651</v>
       </c>
       <c r="T99">
-        <v>23.7114318531887</v>
+        <v>35.56714777978306</v>
       </c>
       <c r="U99">
         <v>0.2902771881973717</v>
       </c>
       <c r="V99">
-        <v>0.05058520110803383</v>
+        <v>0.05006902558652328</v>
       </c>
       <c r="W99">
-        <v>0.275593458255333</v>
+        <v>0.2757432922343335</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2529260055401691</v>
+        <v>0.2503451279326163</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3541891282266999</v>
+        <v>0.3566339001086736</v>
       </c>
       <c r="C100">
-        <v>-1436.054613792227</v>
+        <v>-1464.016397191373</v>
       </c>
       <c r="D100">
-        <v>691.499386207773</v>
+        <v>686.060602808627</v>
       </c>
       <c r="E100">
-        <v>1611.954</v>
+        <v>1634.477</v>
       </c>
       <c r="F100">
-        <v>2207.254</v>
+        <v>2229.777</v>
       </c>
       <c r="G100">
         <v>79.7</v>
@@ -9481,37 +9481,37 @@
         <v>160.4</v>
       </c>
       <c r="M100">
-        <v>640.7154847574016</v>
+        <v>647.2533978671709</v>
       </c>
       <c r="N100">
-        <v>-480.3154847574016</v>
+        <v>-486.8533978671709</v>
       </c>
       <c r="O100">
-        <v>-96.06309695148032</v>
+        <v>-97.37067957343419</v>
       </c>
       <c r="P100">
-        <v>-384.2523878059213</v>
+        <v>-389.4827182937367</v>
       </c>
       <c r="Q100">
-        <v>-296.3523878059212</v>
+        <v>-301.5827182937367</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.198035091852651</v>
+        <v>8.350270183705302</v>
       </c>
       <c r="T100">
-        <v>35.56714777978306</v>
+        <v>71.13429555956611</v>
       </c>
       <c r="U100">
         <v>0.2902771881973717</v>
       </c>
       <c r="V100">
-        <v>0.05006902558652328</v>
+        <v>0.04956327785332608</v>
       </c>
       <c r="W100">
-        <v>0.2757432922343335</v>
+        <v>0.2758900992642632</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2503451279326163</v>
+        <v>0.2478163892666303</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3566339001086736</v>
-      </c>
-      <c r="C101">
-        <v>-1464.016397191373</v>
-      </c>
-      <c r="D101">
-        <v>686.060602808627</v>
-      </c>
-      <c r="E101">
-        <v>1634.477</v>
-      </c>
-      <c r="F101">
-        <v>2229.777</v>
-      </c>
-      <c r="G101">
-        <v>79.7</v>
-      </c>
-      <c r="H101">
-        <v>1657</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>248.3</v>
-      </c>
-      <c r="K101">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>160.4</v>
-      </c>
-      <c r="M101">
-        <v>647.2533978671709</v>
-      </c>
-      <c r="N101">
-        <v>-486.8533978671709</v>
-      </c>
-      <c r="O101">
-        <v>-97.37067957343419</v>
-      </c>
-      <c r="P101">
-        <v>-389.4827182937367</v>
-      </c>
-      <c r="Q101">
-        <v>-301.5827182937367</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.350270183705302</v>
-      </c>
-      <c r="T101">
-        <v>71.13429555956611</v>
-      </c>
-      <c r="U101">
-        <v>0.2902771881973717</v>
-      </c>
-      <c r="V101">
-        <v>0.04956327785332608</v>
-      </c>
-      <c r="W101">
-        <v>0.2758900992642632</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2478163892666303</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
